--- a/output/census_targets_wide.xlsx
+++ b/output/census_targets_wide.xlsx
@@ -1346,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BY126"/>
+  <dimension ref="A1:BY127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:77" s="1" customFormat="1">
@@ -27147,220 +27147,220 @@
         <v>2020</v>
       </c>
       <c r="B122">
-        <v>2978014</v>
+        <v>3319039</v>
       </c>
       <c r="C122">
-        <v>2847322</v>
+        <v>3277018</v>
       </c>
       <c r="D122">
-        <v>2844826</v>
+        <v>3261824</v>
       </c>
       <c r="E122">
-        <v>3144834</v>
+        <v>3322005</v>
       </c>
       <c r="F122">
-        <v>3114496</v>
+        <v>3347840</v>
       </c>
       <c r="G122">
-        <v>2913013</v>
+        <v>3180411</v>
       </c>
       <c r="H122">
-        <v>2697547</v>
+        <v>2938654</v>
       </c>
       <c r="I122">
-        <v>2567674</v>
+        <v>2806656</v>
       </c>
       <c r="J122">
-        <v>2935302</v>
+        <v>3213851</v>
       </c>
       <c r="K122">
-        <v>2427593</v>
+        <v>2679582</v>
       </c>
       <c r="L122">
-        <v>2407649</v>
+        <v>2635800</v>
       </c>
       <c r="M122">
-        <v>2200106</v>
+        <v>2402462</v>
       </c>
       <c r="N122">
-        <v>1796493</v>
+        <v>1944510</v>
       </c>
       <c r="O122">
-        <v>1352527</v>
+        <v>1442968</v>
       </c>
       <c r="Q122">
-        <v>2872823</v>
+        <v>3157774</v>
       </c>
       <c r="R122">
-        <v>3088504</v>
+        <v>3439419</v>
       </c>
       <c r="S122">
-        <v>2905870</v>
+        <v>3356445</v>
       </c>
       <c r="T122">
-        <v>2851654</v>
+        <v>3252682</v>
       </c>
       <c r="U122">
-        <v>3117483</v>
+        <v>3192584</v>
       </c>
       <c r="V122">
-        <v>2986220</v>
+        <v>3084161</v>
       </c>
       <c r="W122">
-        <v>2718550</v>
+        <v>2868725</v>
       </c>
       <c r="X122">
-        <v>2451434</v>
+        <v>2617123</v>
       </c>
       <c r="Y122">
-        <v>2323687</v>
+        <v>2500278</v>
       </c>
       <c r="Z122">
-        <v>3052214</v>
+        <v>3333821</v>
       </c>
       <c r="AA122">
-        <v>2198209</v>
+        <v>2374130</v>
       </c>
       <c r="AB122">
-        <v>2137832</v>
+        <v>2297208</v>
       </c>
       <c r="AC122">
-        <v>1890849</v>
+        <v>2030045</v>
       </c>
       <c r="AD122">
-        <v>1443974</v>
+        <v>1562160</v>
       </c>
       <c r="AE122">
-        <v>1040012</v>
+        <v>1101198</v>
       </c>
       <c r="AG122">
-        <v>2985409</v>
+        <v>3273907</v>
       </c>
       <c r="AH122">
-        <v>7608532</v>
+        <v>7180842</v>
       </c>
       <c r="AI122">
-        <v>7673356</v>
+        <v>7462719</v>
       </c>
       <c r="AJ122">
-        <v>7622404</v>
+        <v>7605004</v>
       </c>
       <c r="AK122">
-        <v>8033246</v>
+        <v>7657754</v>
       </c>
       <c r="AL122">
-        <v>8160272</v>
+        <v>7894093</v>
       </c>
       <c r="AM122">
-        <v>8073360</v>
+        <v>7796461</v>
       </c>
       <c r="AN122">
-        <v>7595580</v>
+        <v>7334016</v>
       </c>
       <c r="AO122">
-        <v>7589407</v>
+        <v>7341533</v>
       </c>
       <c r="AP122">
-        <v>6999605</v>
+        <v>6604685</v>
       </c>
       <c r="AQ122">
-        <v>7981424</v>
+        <v>7812472</v>
       </c>
       <c r="AR122">
-        <v>8766199</v>
+        <v>8664112</v>
       </c>
       <c r="AS122">
-        <v>8601794</v>
+        <v>8636571</v>
       </c>
       <c r="AT122">
-        <v>7646132</v>
+        <v>7739444</v>
       </c>
       <c r="AU122">
-        <v>6414135</v>
+        <v>6543336</v>
       </c>
       <c r="AW122">
-        <v>6558095</v>
+        <v>6200604</v>
       </c>
       <c r="AX122">
-        <v>8022075</v>
+        <v>7559123</v>
       </c>
       <c r="AY122">
-        <v>8039914</v>
+        <v>7793163</v>
       </c>
       <c r="AZ122">
-        <v>7811627</v>
+        <v>7741941</v>
       </c>
       <c r="BA122">
-        <v>8252448</v>
+        <v>7798267</v>
       </c>
       <c r="BB122">
-        <v>8439355</v>
+        <v>7999132</v>
       </c>
       <c r="BC122">
-        <v>8394210</v>
+        <v>7858737</v>
       </c>
       <c r="BD122">
-        <v>7859397</v>
+        <v>7355069</v>
       </c>
       <c r="BE122">
-        <v>7810312</v>
+        <v>7319852</v>
       </c>
       <c r="BF122">
-        <v>7360660</v>
+        <v>6936439</v>
       </c>
       <c r="BG122">
-        <v>8163657</v>
+        <v>7735333</v>
       </c>
       <c r="BH122">
-        <v>8715485</v>
+        <v>8397258</v>
       </c>
       <c r="BI122">
-        <v>8333984</v>
+        <v>8165156</v>
       </c>
       <c r="BJ122">
-        <v>7109917</v>
+        <v>7094256</v>
       </c>
       <c r="BK122">
-        <v>5767338</v>
+        <v>5813002</v>
       </c>
       <c r="BM122">
-        <v>6877962</v>
+        <v>6501642</v>
       </c>
       <c r="BN122">
-        <v>858334</v>
+        <v>907625</v>
       </c>
       <c r="BO122">
-        <v>564899</v>
+        <v>585938</v>
       </c>
       <c r="BP122">
-        <v>572637</v>
+        <v>584388</v>
       </c>
       <c r="BQ122">
-        <v>621161</v>
+        <v>651149</v>
       </c>
       <c r="BR122">
-        <v>375301</v>
+        <v>385654</v>
       </c>
       <c r="BS122">
-        <v>290174</v>
+        <v>294031</v>
       </c>
       <c r="BT122">
-        <v>4443861</v>
+        <v>4596310</v>
       </c>
       <c r="BU122">
-        <v>2965525</v>
+        <v>3081096</v>
       </c>
       <c r="BV122">
-        <v>3314758</v>
+        <v>3447683</v>
       </c>
       <c r="BW122">
-        <v>3737490</v>
+        <v>3842861</v>
       </c>
       <c r="BX122">
-        <v>2254607</v>
+        <v>2338618</v>
       </c>
       <c r="BY122">
-        <v>1890296</v>
+        <v>1991780</v>
       </c>
     </row>
     <row r="123" spans="1:77">
@@ -27368,220 +27368,220 @@
         <v>2021</v>
       </c>
       <c r="B123">
-        <v>2977271</v>
+        <v>3315205</v>
       </c>
       <c r="C123">
-        <v>2866116</v>
+        <v>3240515</v>
       </c>
       <c r="D123">
-        <v>2856601</v>
+        <v>3342039</v>
       </c>
       <c r="E123">
-        <v>3073974</v>
+        <v>3274116</v>
       </c>
       <c r="F123">
-        <v>3192722</v>
+        <v>3400730</v>
       </c>
       <c r="G123">
-        <v>2939732</v>
+        <v>3209420</v>
       </c>
       <c r="H123">
-        <v>2760072</v>
+        <v>3009204</v>
       </c>
       <c r="I123">
-        <v>2543413</v>
+        <v>2776835</v>
       </c>
       <c r="J123">
-        <v>2950977</v>
+        <v>3218998</v>
       </c>
       <c r="K123">
-        <v>2469200</v>
+        <v>2721580</v>
       </c>
       <c r="L123">
-        <v>2404287</v>
+        <v>2639879</v>
       </c>
       <c r="M123">
-        <v>2231270</v>
+        <v>2438493</v>
       </c>
       <c r="N123">
-        <v>1856864</v>
+        <v>2016153</v>
       </c>
       <c r="O123">
-        <v>1441074</v>
+        <v>1542259</v>
       </c>
       <c r="Q123">
-        <v>2839561</v>
+        <v>3131227</v>
       </c>
       <c r="R123">
-        <v>3095629</v>
+        <v>3438868</v>
       </c>
       <c r="S123">
-        <v>2927679</v>
+        <v>3329921</v>
       </c>
       <c r="T123">
-        <v>2863487</v>
+        <v>3333527</v>
       </c>
       <c r="U123">
-        <v>3054691</v>
+        <v>3174930</v>
       </c>
       <c r="V123">
-        <v>3072803</v>
+        <v>3144450</v>
       </c>
       <c r="W123">
-        <v>2756928</v>
+        <v>2903419</v>
       </c>
       <c r="X123">
-        <v>2513545</v>
+        <v>2678269</v>
       </c>
       <c r="Y123">
-        <v>2296706</v>
+        <v>2470024</v>
       </c>
       <c r="Z123">
-        <v>3062576</v>
+        <v>3336746</v>
       </c>
       <c r="AA123">
-        <v>2231266</v>
+        <v>2407215</v>
       </c>
       <c r="AB123">
-        <v>2134111</v>
+        <v>2298634</v>
       </c>
       <c r="AC123">
-        <v>1919310</v>
+        <v>2059527</v>
       </c>
       <c r="AD123">
-        <v>1498792</v>
+        <v>1622822</v>
       </c>
       <c r="AE123">
-        <v>1098950</v>
+        <v>1170621</v>
       </c>
       <c r="AG123">
-        <v>2952870</v>
+        <v>3248921</v>
       </c>
       <c r="AH123">
-        <v>7491695</v>
+        <v>7077664</v>
       </c>
       <c r="AI123">
-        <v>7671093</v>
+        <v>7327193</v>
       </c>
       <c r="AJ123">
-        <v>7644967</v>
+        <v>7732992</v>
       </c>
       <c r="AK123">
-        <v>7900700</v>
+        <v>7539071</v>
       </c>
       <c r="AL123">
-        <v>8212413</v>
+        <v>7917212</v>
       </c>
       <c r="AM123">
-        <v>8080945</v>
+        <v>7814331</v>
       </c>
       <c r="AN123">
-        <v>7745388</v>
+        <v>7478357</v>
       </c>
       <c r="AO123">
-        <v>7363109</v>
+        <v>7117642</v>
       </c>
       <c r="AP123">
-        <v>6973538</v>
+        <v>6568089</v>
       </c>
       <c r="AQ123">
-        <v>8000939</v>
+        <v>7811099</v>
       </c>
       <c r="AR123">
-        <v>8534068</v>
+        <v>8412815</v>
       </c>
       <c r="AS123">
-        <v>8665957</v>
+        <v>8675611</v>
       </c>
       <c r="AT123">
-        <v>7780808</v>
+        <v>7865745</v>
       </c>
       <c r="AU123">
-        <v>6706045</v>
+        <v>6832052</v>
       </c>
       <c r="AW123">
-        <v>6373721</v>
+        <v>6038914</v>
       </c>
       <c r="AX123">
-        <v>7902714</v>
+        <v>7445514</v>
       </c>
       <c r="AY123">
-        <v>8040389</v>
+        <v>7689989</v>
       </c>
       <c r="AZ123">
-        <v>7831885</v>
+        <v>7844068</v>
       </c>
       <c r="BA123">
-        <v>8117877</v>
+        <v>7687047</v>
       </c>
       <c r="BB123">
-        <v>8458045</v>
+        <v>8020863</v>
       </c>
       <c r="BC123">
-        <v>8396599</v>
+        <v>7878179</v>
       </c>
       <c r="BD123">
-        <v>8022194</v>
+        <v>7501551</v>
       </c>
       <c r="BE123">
-        <v>7558584</v>
+        <v>7088221</v>
       </c>
       <c r="BF123">
-        <v>7323207</v>
+        <v>6893275</v>
       </c>
       <c r="BG123">
-        <v>8195959</v>
+        <v>7732177</v>
       </c>
       <c r="BH123">
-        <v>8494299</v>
+        <v>8155780</v>
       </c>
       <c r="BI123">
-        <v>8404374</v>
+        <v>8197769</v>
       </c>
       <c r="BJ123">
-        <v>7237355</v>
+        <v>7196203</v>
       </c>
       <c r="BK123">
-        <v>6004931</v>
+        <v>6045949</v>
       </c>
       <c r="BM123">
-        <v>6686054</v>
+        <v>6334305</v>
       </c>
       <c r="BN123">
-        <v>892020</v>
+        <v>946804</v>
       </c>
       <c r="BO123">
-        <v>583847</v>
+        <v>610354</v>
       </c>
       <c r="BP123">
-        <v>587541</v>
+        <v>600401</v>
       </c>
       <c r="BQ123">
-        <v>644221</v>
+        <v>678762</v>
       </c>
       <c r="BR123">
-        <v>387487</v>
+        <v>401203</v>
       </c>
       <c r="BS123">
-        <v>304286</v>
+        <v>307920</v>
       </c>
       <c r="BT123">
-        <v>4541992</v>
+        <v>4698333</v>
       </c>
       <c r="BU123">
-        <v>3029877</v>
+        <v>3154268</v>
       </c>
       <c r="BV123">
-        <v>3277910</v>
+        <v>3429420</v>
       </c>
       <c r="BW123">
-        <v>3817568</v>
+        <v>3928650</v>
       </c>
       <c r="BX123">
-        <v>2301383</v>
+        <v>2390858</v>
       </c>
       <c r="BY123">
-        <v>1899313</v>
+        <v>2008983</v>
       </c>
     </row>
     <row r="124" spans="1:77">
@@ -27589,220 +27589,220 @@
         <v>2022</v>
       </c>
       <c r="B124">
-        <v>2981148</v>
+        <v>3305773</v>
       </c>
       <c r="C124">
-        <v>2942028</v>
+        <v>3288423</v>
       </c>
       <c r="D124">
-        <v>2907602</v>
+        <v>3421396</v>
       </c>
       <c r="E124">
-        <v>3070942</v>
+        <v>3301562</v>
       </c>
       <c r="F124">
-        <v>3299652</v>
+        <v>3480762</v>
       </c>
       <c r="G124">
-        <v>2994610</v>
+        <v>3259368</v>
       </c>
       <c r="H124">
-        <v>2834540</v>
+        <v>3087109</v>
       </c>
       <c r="I124">
-        <v>2563239</v>
+        <v>2792407</v>
       </c>
       <c r="J124">
-        <v>2982426</v>
+        <v>3245448</v>
       </c>
       <c r="K124">
-        <v>2519732</v>
+        <v>2772046</v>
       </c>
       <c r="L124">
-        <v>2394403</v>
+        <v>2634936</v>
       </c>
       <c r="M124">
-        <v>2261940</v>
+        <v>2467550</v>
       </c>
       <c r="N124">
-        <v>1927874</v>
+        <v>2101691</v>
       </c>
       <c r="O124">
-        <v>1493245</v>
+        <v>1603385</v>
       </c>
       <c r="Q124">
-        <v>2848542</v>
+        <v>3148748</v>
       </c>
       <c r="R124">
-        <v>3100710</v>
+        <v>3429617</v>
       </c>
       <c r="S124">
-        <v>3018504</v>
+        <v>3394687</v>
       </c>
       <c r="T124">
-        <v>2918561</v>
+        <v>3418806</v>
       </c>
       <c r="U124">
-        <v>3044228</v>
+        <v>3219215</v>
       </c>
       <c r="V124">
-        <v>3191898</v>
+        <v>3241085</v>
       </c>
       <c r="W124">
-        <v>2821923</v>
+        <v>2962575</v>
       </c>
       <c r="X124">
-        <v>2596816</v>
+        <v>2752956</v>
       </c>
       <c r="Y124">
-        <v>2307627</v>
+        <v>2478160</v>
       </c>
       <c r="Z124">
-        <v>3094964</v>
+        <v>3364101</v>
       </c>
       <c r="AA124">
-        <v>2271750</v>
+        <v>2446821</v>
       </c>
       <c r="AB124">
-        <v>2119431</v>
+        <v>2287936</v>
       </c>
       <c r="AC124">
-        <v>1947491</v>
+        <v>2084975</v>
       </c>
       <c r="AD124">
-        <v>1563651</v>
+        <v>1693806</v>
       </c>
       <c r="AE124">
-        <v>1130521</v>
+        <v>1214865</v>
       </c>
       <c r="AG124">
-        <v>2958226</v>
+        <v>3265815</v>
       </c>
       <c r="AH124">
-        <v>7356992</v>
+        <v>6961511</v>
       </c>
       <c r="AI124">
-        <v>7741953</v>
+        <v>7339574</v>
       </c>
       <c r="AJ124">
-        <v>7689210</v>
+        <v>7794721</v>
       </c>
       <c r="AK124">
-        <v>7835078</v>
+        <v>7508775</v>
       </c>
       <c r="AL124">
-        <v>8287217</v>
+        <v>7961631</v>
       </c>
       <c r="AM124">
-        <v>8087644</v>
+        <v>7834491</v>
       </c>
       <c r="AN124">
-        <v>7881505</v>
+        <v>7607728</v>
       </c>
       <c r="AO124">
-        <v>7307866</v>
+        <v>7062433</v>
       </c>
       <c r="AP124">
-        <v>6941953</v>
+        <v>6540261</v>
       </c>
       <c r="AQ124">
-        <v>7946345</v>
+        <v>7742469</v>
       </c>
       <c r="AR124">
-        <v>8295682</v>
+        <v>8166992</v>
       </c>
       <c r="AS124">
-        <v>8659593</v>
+        <v>8628035</v>
       </c>
       <c r="AT124">
-        <v>7917246</v>
+        <v>8003142</v>
       </c>
       <c r="AU124">
-        <v>6666002</v>
+        <v>6793663</v>
       </c>
       <c r="AW124">
-        <v>6300928</v>
+        <v>5977579</v>
       </c>
       <c r="AX124">
-        <v>7757405</v>
+        <v>7320287</v>
       </c>
       <c r="AY124">
-        <v>8126268</v>
+        <v>7727625</v>
       </c>
       <c r="AZ124">
-        <v>7898714</v>
+        <v>7917058</v>
       </c>
       <c r="BA124">
-        <v>8047652</v>
+        <v>7667598</v>
       </c>
       <c r="BB124">
-        <v>8513318</v>
+        <v>8072972</v>
       </c>
       <c r="BC124">
-        <v>8398982</v>
+        <v>7908391</v>
       </c>
       <c r="BD124">
-        <v>8169329</v>
+        <v>7631604</v>
       </c>
       <c r="BE124">
-        <v>7495021</v>
+        <v>7031172</v>
       </c>
       <c r="BF124">
-        <v>7289474</v>
+        <v>6863028</v>
       </c>
       <c r="BG124">
-        <v>8137461</v>
+        <v>7654921</v>
       </c>
       <c r="BH124">
-        <v>8266232</v>
+        <v>7915006</v>
       </c>
       <c r="BI124">
-        <v>8396779</v>
+        <v>8147485</v>
       </c>
       <c r="BJ124">
-        <v>7370679</v>
+        <v>7309092</v>
       </c>
       <c r="BK124">
-        <v>5935492</v>
+        <v>5990160</v>
       </c>
       <c r="BM124">
-        <v>6603258</v>
+        <v>6265788</v>
       </c>
       <c r="BN124">
-        <v>969215</v>
+        <v>1029032</v>
       </c>
       <c r="BO124">
-        <v>611127</v>
+        <v>642091</v>
       </c>
       <c r="BP124">
-        <v>608210</v>
+        <v>623420</v>
       </c>
       <c r="BQ124">
-        <v>703458</v>
+        <v>738938</v>
       </c>
       <c r="BR124">
-        <v>406269</v>
+        <v>423113</v>
       </c>
       <c r="BS124">
-        <v>322234</v>
+        <v>326924</v>
       </c>
       <c r="BT124">
-        <v>4965371</v>
+        <v>5107957</v>
       </c>
       <c r="BU124">
-        <v>3141896</v>
+        <v>3273386</v>
       </c>
       <c r="BV124">
-        <v>3258757</v>
+        <v>3429046</v>
       </c>
       <c r="BW124">
-        <v>4207648</v>
+        <v>4285358</v>
       </c>
       <c r="BX124">
-        <v>2391096</v>
+        <v>2485058</v>
       </c>
       <c r="BY124">
-        <v>1915046</v>
+        <v>2033273</v>
       </c>
     </row>
     <row r="125" spans="1:77">
@@ -27810,220 +27810,220 @@
         <v>2023</v>
       </c>
       <c r="B125">
-        <v>2989192</v>
+        <v>3298227</v>
       </c>
       <c r="C125">
-        <v>3029909</v>
+        <v>3370034</v>
       </c>
       <c r="D125">
-        <v>2975153</v>
+        <v>3479102</v>
       </c>
       <c r="E125">
-        <v>3102289</v>
+        <v>3373740</v>
       </c>
       <c r="F125">
-        <v>3398683</v>
+        <v>3562553</v>
       </c>
       <c r="G125">
-        <v>3081448</v>
+        <v>3335535</v>
       </c>
       <c r="H125">
-        <v>2919679</v>
+        <v>3176663</v>
       </c>
       <c r="I125">
-        <v>2606947</v>
+        <v>2829725</v>
       </c>
       <c r="J125">
-        <v>3014802</v>
+        <v>3276490</v>
       </c>
       <c r="K125">
-        <v>2556916</v>
+        <v>2807580</v>
       </c>
       <c r="L125">
-        <v>2392101</v>
+        <v>2633154</v>
       </c>
       <c r="M125">
-        <v>2303379</v>
+        <v>2513203</v>
       </c>
       <c r="N125">
-        <v>1997193</v>
+        <v>2181443</v>
       </c>
       <c r="O125">
-        <v>1553692</v>
+        <v>1674638</v>
       </c>
       <c r="Q125">
-        <v>2863270</v>
+        <v>3172842</v>
       </c>
       <c r="R125">
-        <v>3110390</v>
+        <v>3423700</v>
       </c>
       <c r="S125">
-        <v>3121932</v>
+        <v>3483647</v>
       </c>
       <c r="T125">
-        <v>2994062</v>
+        <v>3499152</v>
       </c>
       <c r="U125">
-        <v>3063226</v>
+        <v>3302733</v>
       </c>
       <c r="V125">
-        <v>3304540</v>
+        <v>3342842</v>
       </c>
       <c r="W125">
-        <v>2921951</v>
+        <v>3049753</v>
       </c>
       <c r="X125">
-        <v>2692046</v>
+        <v>2844058</v>
       </c>
       <c r="Y125">
-        <v>2347603</v>
+        <v>2510324</v>
       </c>
       <c r="Z125">
-        <v>3126608</v>
+        <v>3393870</v>
       </c>
       <c r="AA125">
-        <v>2299588</v>
+        <v>2474924</v>
       </c>
       <c r="AB125">
-        <v>2113486</v>
+        <v>2280744</v>
       </c>
       <c r="AC125">
-        <v>1982978</v>
+        <v>2124331</v>
       </c>
       <c r="AD125">
-        <v>1629310</v>
+        <v>1762646</v>
       </c>
       <c r="AE125">
-        <v>1176071</v>
+        <v>1270697</v>
       </c>
       <c r="AG125">
-        <v>2972133</v>
+        <v>3291794</v>
       </c>
       <c r="AH125">
-        <v>7231190</v>
+        <v>6852366</v>
       </c>
       <c r="AI125">
-        <v>7806292</v>
+        <v>7385791</v>
       </c>
       <c r="AJ125">
-        <v>7761304</v>
+        <v>7802741</v>
       </c>
       <c r="AK125">
-        <v>7825119</v>
+        <v>7572146</v>
       </c>
       <c r="AL125">
-        <v>8330381</v>
+        <v>7979431</v>
       </c>
       <c r="AM125">
-        <v>8128700</v>
+        <v>7879644</v>
       </c>
       <c r="AN125">
-        <v>8017712</v>
+        <v>7742849</v>
       </c>
       <c r="AO125">
-        <v>7363861</v>
+        <v>7109592</v>
       </c>
       <c r="AP125">
-        <v>6898111</v>
+        <v>6509212</v>
       </c>
       <c r="AQ125">
-        <v>7848994</v>
+        <v>7633721</v>
       </c>
       <c r="AR125">
-        <v>8074306</v>
+        <v>7932771</v>
       </c>
       <c r="AS125">
-        <v>8628762</v>
+        <v>8573831</v>
       </c>
       <c r="AT125">
-        <v>8045592</v>
+        <v>8115202</v>
       </c>
       <c r="AU125">
-        <v>6777456</v>
+        <v>6896266</v>
       </c>
       <c r="AW125">
-        <v>6250439</v>
+        <v>5928911</v>
       </c>
       <c r="AX125">
-        <v>7612889</v>
+        <v>7200572</v>
       </c>
       <c r="AY125">
-        <v>8199992</v>
+        <v>7771087</v>
       </c>
       <c r="AZ125">
-        <v>7992784</v>
+        <v>7959586</v>
       </c>
       <c r="BA125">
-        <v>8036804</v>
+        <v>7743176</v>
       </c>
       <c r="BB125">
-        <v>8559725</v>
+        <v>8110615</v>
       </c>
       <c r="BC125">
-        <v>8427717</v>
+        <v>7962491</v>
       </c>
       <c r="BD125">
-        <v>8313744</v>
+        <v>7771696</v>
       </c>
       <c r="BE125">
-        <v>7561581</v>
+        <v>7083961</v>
       </c>
       <c r="BF125">
-        <v>7244532</v>
+        <v>6830240</v>
       </c>
       <c r="BG125">
-        <v>8023092</v>
+        <v>7536867</v>
       </c>
       <c r="BH125">
-        <v>8072545</v>
+        <v>7696748</v>
       </c>
       <c r="BI125">
-        <v>8370316</v>
+        <v>8098375</v>
       </c>
       <c r="BJ125">
-        <v>7509031</v>
+        <v>7411166</v>
       </c>
       <c r="BK125">
-        <v>6028411</v>
+        <v>6068975</v>
       </c>
       <c r="BM125">
-        <v>6546555</v>
+        <v>6212990</v>
       </c>
       <c r="BN125">
-        <v>1044411</v>
+        <v>1112160</v>
       </c>
       <c r="BO125">
-        <v>647020</v>
+        <v>683382</v>
       </c>
       <c r="BP125">
-        <v>638732</v>
+        <v>658276</v>
       </c>
       <c r="BQ125">
-        <v>758641</v>
+        <v>799345</v>
       </c>
       <c r="BR125">
-        <v>431729</v>
+        <v>452271</v>
       </c>
       <c r="BS125">
-        <v>345547</v>
+        <v>351862</v>
       </c>
       <c r="BT125">
-        <v>5176771</v>
+        <v>5318526</v>
       </c>
       <c r="BU125">
-        <v>3336808</v>
+        <v>3479137</v>
       </c>
       <c r="BV125">
-        <v>3295561</v>
+        <v>3482829</v>
       </c>
       <c r="BW125">
-        <v>4400281</v>
+        <v>4474797</v>
       </c>
       <c r="BX125">
-        <v>2559737</v>
+        <v>2659629</v>
       </c>
       <c r="BY125">
-        <v>1974713</v>
+        <v>2101909</v>
       </c>
     </row>
     <row r="126" spans="1:77">
@@ -28031,220 +28031,441 @@
         <v>2024</v>
       </c>
       <c r="B126">
-        <v>3026213</v>
+        <v>3313471</v>
       </c>
       <c r="C126">
-        <v>3095871</v>
+        <v>3427969</v>
       </c>
       <c r="D126">
-        <v>3065072</v>
+        <v>3531522</v>
       </c>
       <c r="E126">
-        <v>3161824</v>
+        <v>3488225</v>
       </c>
       <c r="F126">
-        <v>3478965</v>
+        <v>3629028</v>
       </c>
       <c r="G126">
-        <v>3218295</v>
+        <v>3452135</v>
       </c>
       <c r="H126">
-        <v>2992184</v>
+        <v>3246788</v>
       </c>
       <c r="I126">
-        <v>2683874</v>
+        <v>2906049</v>
       </c>
       <c r="J126">
-        <v>3042432</v>
+        <v>3307160</v>
       </c>
       <c r="K126">
-        <v>2586070</v>
+        <v>2823743</v>
       </c>
       <c r="L126">
-        <v>2397467</v>
+        <v>2637257</v>
       </c>
       <c r="M126">
-        <v>2343894</v>
+        <v>2558637</v>
       </c>
       <c r="N126">
-        <v>2059823</v>
+        <v>2251901</v>
       </c>
       <c r="O126">
-        <v>1621638</v>
+        <v>1751543</v>
       </c>
       <c r="Q126">
-        <v>2883861</v>
+        <v>3192211</v>
       </c>
       <c r="R126">
-        <v>3150607</v>
+        <v>3440787</v>
       </c>
       <c r="S126">
-        <v>3201528</v>
+        <v>3548898</v>
       </c>
       <c r="T126">
-        <v>3092971</v>
+        <v>3580114</v>
       </c>
       <c r="U126">
-        <v>3114314</v>
+        <v>3432680</v>
       </c>
       <c r="V126">
-        <v>3393829</v>
+        <v>3432206</v>
       </c>
       <c r="W126">
-        <v>3069319</v>
+        <v>3178461</v>
       </c>
       <c r="X126">
-        <v>2778692</v>
+        <v>2925431</v>
       </c>
       <c r="Y126">
-        <v>2420893</v>
+        <v>2578826</v>
       </c>
       <c r="Z126">
-        <v>3150458</v>
+        <v>3420009</v>
       </c>
       <c r="AA126">
-        <v>2319463</v>
+        <v>2488103</v>
       </c>
       <c r="AB126">
-        <v>2117742</v>
+        <v>2282966</v>
       </c>
       <c r="AC126">
-        <v>2017791</v>
+        <v>2163478</v>
       </c>
       <c r="AD126">
-        <v>1688221</v>
+        <v>1822275</v>
       </c>
       <c r="AE126">
-        <v>1230392</v>
+        <v>1332302</v>
       </c>
       <c r="AG126">
-        <v>2994505</v>
+        <v>3316944</v>
       </c>
       <c r="AH126">
-        <v>7173793</v>
+        <v>6798625</v>
       </c>
       <c r="AI126">
-        <v>7805446</v>
+        <v>7382613</v>
       </c>
       <c r="AJ126">
-        <v>7850038</v>
+        <v>7783780</v>
       </c>
       <c r="AK126">
-        <v>7861138</v>
+        <v>7726819</v>
       </c>
       <c r="AL126">
-        <v>8355022</v>
+        <v>7986169</v>
       </c>
       <c r="AM126">
-        <v>8227071</v>
+        <v>7977477</v>
       </c>
       <c r="AN126">
-        <v>8111908</v>
+        <v>7838249</v>
       </c>
       <c r="AO126">
-        <v>7476517</v>
+        <v>7219782</v>
       </c>
       <c r="AP126">
-        <v>6835598</v>
+        <v>6470059</v>
       </c>
       <c r="AQ126">
-        <v>7706146</v>
+        <v>7471879</v>
       </c>
       <c r="AR126">
-        <v>7910029</v>
+        <v>7755434</v>
       </c>
       <c r="AS126">
-        <v>8594795</v>
+        <v>8519313</v>
       </c>
       <c r="AT126">
-        <v>8132063</v>
+        <v>8181847</v>
       </c>
       <c r="AU126">
-        <v>6931769</v>
+        <v>7040814</v>
       </c>
       <c r="AW126">
-        <v>6214410</v>
+        <v>5896171</v>
       </c>
       <c r="AX126">
-        <v>7550541</v>
+        <v>7139389</v>
       </c>
       <c r="AY126">
-        <v>8204566</v>
+        <v>7763395</v>
       </c>
       <c r="AZ126">
-        <v>8103136</v>
+        <v>7983813</v>
       </c>
       <c r="BA126">
-        <v>8073972</v>
+        <v>7905154</v>
       </c>
       <c r="BB126">
-        <v>8590078</v>
+        <v>8139777</v>
       </c>
       <c r="BC126">
-        <v>8518338</v>
+        <v>8075311</v>
       </c>
       <c r="BD126">
-        <v>8414236</v>
+        <v>7877160</v>
       </c>
       <c r="BE126">
-        <v>7685888</v>
+        <v>7198440</v>
       </c>
       <c r="BF126">
-        <v>7169184</v>
+        <v>6781387</v>
       </c>
       <c r="BG126">
-        <v>7864860</v>
+        <v>7374854</v>
       </c>
       <c r="BH126">
-        <v>7932179</v>
+        <v>7534883</v>
       </c>
       <c r="BI126">
-        <v>8344891</v>
+        <v>8048526</v>
       </c>
       <c r="BJ126">
-        <v>7609364</v>
+        <v>7476258</v>
       </c>
       <c r="BK126">
-        <v>6171692</v>
+        <v>6192166</v>
       </c>
       <c r="BM126">
-        <v>6506538</v>
+        <v>6179409</v>
       </c>
       <c r="BN126">
-        <v>1129789</v>
+        <v>1206291</v>
       </c>
       <c r="BO126">
-        <v>685438</v>
+        <v>726141</v>
       </c>
       <c r="BP126">
-        <v>672763</v>
+        <v>697294</v>
       </c>
       <c r="BQ126">
-        <v>818902</v>
+        <v>867087</v>
       </c>
       <c r="BR126">
-        <v>458578</v>
+        <v>481956</v>
       </c>
       <c r="BS126">
-        <v>371347</v>
+        <v>379928</v>
       </c>
       <c r="BT126">
-        <v>5427669</v>
+        <v>5569866</v>
       </c>
       <c r="BU126">
-        <v>3479986</v>
+        <v>3628543</v>
       </c>
       <c r="BV126">
-        <v>3348367</v>
+        <v>3553038</v>
       </c>
       <c r="BW126">
-        <v>4616966</v>
+        <v>4688689</v>
       </c>
       <c r="BX126">
-        <v>2682485</v>
+        <v>2785965</v>
       </c>
       <c r="BY126">
-        <v>2042666</v>
+        <v>2178677</v>
+      </c>
+    </row>
+    <row r="127" spans="1:77">
+      <c r="A127">
+        <v>2025</v>
+      </c>
+      <c r="B127">
+        <v>3328839</v>
+      </c>
+      <c r="C127">
+        <v>3448757</v>
+      </c>
+      <c r="D127">
+        <v>3506989</v>
+      </c>
+      <c r="E127">
+        <v>3596243</v>
+      </c>
+      <c r="F127">
+        <v>3629100</v>
+      </c>
+      <c r="G127">
+        <v>3551538</v>
+      </c>
+      <c r="H127">
+        <v>3289670</v>
+      </c>
+      <c r="I127">
+        <v>2989696</v>
+      </c>
+      <c r="J127">
+        <v>3309315</v>
+      </c>
+      <c r="K127">
+        <v>2819013</v>
+      </c>
+      <c r="L127">
+        <v>2663595</v>
+      </c>
+      <c r="M127">
+        <v>2579412</v>
+      </c>
+      <c r="N127">
+        <v>2309949</v>
+      </c>
+      <c r="O127">
+        <v>1827370</v>
+      </c>
+      <c r="Q127">
+        <v>3186914</v>
+      </c>
+      <c r="R127">
+        <v>3455218</v>
+      </c>
+      <c r="S127">
+        <v>3569968</v>
+      </c>
+      <c r="T127">
+        <v>3575032</v>
+      </c>
+      <c r="U127">
+        <v>3554560</v>
+      </c>
+      <c r="V127">
+        <v>3453677</v>
+      </c>
+      <c r="W127">
+        <v>3285432</v>
+      </c>
+      <c r="X127">
+        <v>2979044</v>
+      </c>
+      <c r="Y127">
+        <v>2655167</v>
+      </c>
+      <c r="Z127">
+        <v>3420002</v>
+      </c>
+      <c r="AA127">
+        <v>2481448</v>
+      </c>
+      <c r="AB127">
+        <v>2308074</v>
+      </c>
+      <c r="AC127">
+        <v>2180652</v>
+      </c>
+      <c r="AD127">
+        <v>1871663</v>
+      </c>
+      <c r="AE127">
+        <v>1397171</v>
+      </c>
+      <c r="AG127">
+        <v>3314820</v>
+      </c>
+      <c r="AH127">
+        <v>6751993</v>
+      </c>
+      <c r="AI127">
+        <v>7327381</v>
+      </c>
+      <c r="AJ127">
+        <v>7657457</v>
+      </c>
+      <c r="AK127">
+        <v>7883906</v>
+      </c>
+      <c r="AL127">
+        <v>7900311</v>
+      </c>
+      <c r="AM127">
+        <v>8048058</v>
+      </c>
+      <c r="AN127">
+        <v>7880818</v>
+      </c>
+      <c r="AO127">
+        <v>7349297</v>
+      </c>
+      <c r="AP127">
+        <v>6376887</v>
+      </c>
+      <c r="AQ127">
+        <v>7283359</v>
+      </c>
+      <c r="AR127">
+        <v>7671649</v>
+      </c>
+      <c r="AS127">
+        <v>8388786</v>
+      </c>
+      <c r="AT127">
+        <v>8222525</v>
+      </c>
+      <c r="AU127">
+        <v>7205304</v>
+      </c>
+      <c r="AW127">
+        <v>5854961</v>
+      </c>
+      <c r="AX127">
+        <v>7084055</v>
+      </c>
+      <c r="AY127">
+        <v>7690043</v>
+      </c>
+      <c r="AZ127">
+        <v>7890502</v>
+      </c>
+      <c r="BA127">
+        <v>8056424</v>
+      </c>
+      <c r="BB127">
+        <v>8063986</v>
+      </c>
+      <c r="BC127">
+        <v>8149205</v>
+      </c>
+      <c r="BD127">
+        <v>7926955</v>
+      </c>
+      <c r="BE127">
+        <v>7335201</v>
+      </c>
+      <c r="BF127">
+        <v>6681517</v>
+      </c>
+      <c r="BG127">
+        <v>7185099</v>
+      </c>
+      <c r="BH127">
+        <v>7467077</v>
+      </c>
+      <c r="BI127">
+        <v>7927536</v>
+      </c>
+      <c r="BJ127">
+        <v>7517322</v>
+      </c>
+      <c r="BK127">
+        <v>6336847</v>
+      </c>
+      <c r="BM127">
+        <v>6135172</v>
+      </c>
+      <c r="BN127">
+        <v>1305553</v>
+      </c>
+      <c r="BO127">
+        <v>768711</v>
+      </c>
+      <c r="BP127">
+        <v>743142</v>
+      </c>
+      <c r="BQ127">
+        <v>939624</v>
+      </c>
+      <c r="BR127">
+        <v>511579</v>
+      </c>
+      <c r="BS127">
+        <v>411647</v>
+      </c>
+      <c r="BT127">
+        <v>5818059</v>
+      </c>
+      <c r="BU127">
+        <v>3751791</v>
+      </c>
+      <c r="BV127">
+        <v>3631143</v>
+      </c>
+      <c r="BW127">
+        <v>4896355</v>
+      </c>
+      <c r="BX127">
+        <v>2896229</v>
+      </c>
+      <c r="BY127">
+        <v>2255104</v>
       </c>
     </row>
   </sheetData>
@@ -28254,7 +28475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DE66"/>
+  <dimension ref="A1:DE67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:109" s="1" customFormat="1">
@@ -48331,328 +48552,328 @@
         <v>2020</v>
       </c>
       <c r="B62">
-        <v>1623626</v>
+        <v>1611371</v>
       </c>
       <c r="C62">
-        <v>1572382</v>
+        <v>1619412</v>
       </c>
       <c r="D62">
-        <v>1602524</v>
+        <v>1637919</v>
       </c>
       <c r="E62">
-        <v>1791749</v>
+        <v>1680846</v>
       </c>
       <c r="F62">
-        <v>1726634</v>
+        <v>1675685</v>
       </c>
       <c r="G62">
-        <v>1581726</v>
+        <v>1571357</v>
       </c>
       <c r="H62">
-        <v>1494207</v>
+        <v>1474043</v>
       </c>
       <c r="I62">
-        <v>1443293</v>
+        <v>1416084</v>
       </c>
       <c r="J62">
-        <v>1539983</v>
+        <v>1521668</v>
       </c>
       <c r="K62">
-        <v>1432604</v>
+        <v>1424639</v>
       </c>
       <c r="L62">
-        <v>1478806</v>
+        <v>1479614</v>
       </c>
       <c r="M62">
-        <v>1362923</v>
+        <v>1377675</v>
       </c>
       <c r="N62">
-        <v>1098096</v>
+        <v>1116825</v>
       </c>
       <c r="O62">
-        <v>813232</v>
+        <v>819030</v>
       </c>
       <c r="P62">
-        <v>517957</v>
+        <v>520034</v>
       </c>
       <c r="Q62">
-        <v>341411</v>
+        <v>338333</v>
       </c>
       <c r="R62">
-        <v>339782</v>
+        <v>341153</v>
       </c>
       <c r="S62">
-        <v>1495727</v>
+        <v>1482812</v>
       </c>
       <c r="T62">
-        <v>1676381</v>
+        <v>1669902</v>
       </c>
       <c r="U62">
-        <v>1604820</v>
+        <v>1663777</v>
       </c>
       <c r="V62">
-        <v>1597646</v>
+        <v>1612695</v>
       </c>
       <c r="W62">
-        <v>1783313</v>
+        <v>1582108</v>
       </c>
       <c r="X62">
-        <v>1654999</v>
+        <v>1520300</v>
       </c>
       <c r="Y62">
-        <v>1466889</v>
+        <v>1401191</v>
       </c>
       <c r="Z62">
-        <v>1349423</v>
+        <v>1306689</v>
       </c>
       <c r="AA62">
-        <v>1289609</v>
+        <v>1256168</v>
       </c>
       <c r="AB62">
-        <v>1585782</v>
+        <v>1567854</v>
       </c>
       <c r="AC62">
-        <v>1286720</v>
+        <v>1259726</v>
       </c>
       <c r="AD62">
-        <v>1303736</v>
+        <v>1285247</v>
       </c>
       <c r="AE62">
-        <v>1162373</v>
+        <v>1162024</v>
       </c>
       <c r="AF62">
-        <v>865802</v>
+        <v>887661</v>
       </c>
       <c r="AG62">
-        <v>600789</v>
+        <v>608612</v>
       </c>
       <c r="AH62">
-        <v>348458</v>
+        <v>351481</v>
       </c>
       <c r="AI62">
-        <v>203554</v>
+        <v>202217</v>
       </c>
       <c r="AJ62">
-        <v>149722</v>
+        <v>152411</v>
       </c>
       <c r="AK62">
-        <v>1534848</v>
+        <v>1522684</v>
       </c>
       <c r="AL62">
-        <v>1354388</v>
+        <v>1707668</v>
       </c>
       <c r="AM62">
-        <v>1274940</v>
+        <v>1657606</v>
       </c>
       <c r="AN62">
-        <v>1242302</v>
+        <v>1623905</v>
       </c>
       <c r="AO62">
-        <v>1353085</v>
+        <v>1641159</v>
       </c>
       <c r="AP62">
-        <v>1387862</v>
+        <v>1672155</v>
       </c>
       <c r="AQ62">
-        <v>1331287</v>
+        <v>1609054</v>
       </c>
       <c r="AR62">
-        <v>1203340</v>
+        <v>1464611</v>
       </c>
       <c r="AS62">
-        <v>1124381</v>
+        <v>1390572</v>
       </c>
       <c r="AT62">
-        <v>1395319</v>
+        <v>1692183</v>
       </c>
       <c r="AU62">
-        <v>994989</v>
+        <v>1254943</v>
       </c>
       <c r="AV62">
-        <v>928843</v>
+        <v>1156186</v>
       </c>
       <c r="AW62">
-        <v>837183</v>
+        <v>1024787</v>
       </c>
       <c r="AX62">
-        <v>698397</v>
+        <v>827685</v>
       </c>
       <c r="AY62">
-        <v>539295</v>
+        <v>623938</v>
       </c>
       <c r="AZ62">
-        <v>340377</v>
+        <v>387591</v>
       </c>
       <c r="BA62">
-        <v>223488</v>
+        <v>247605</v>
       </c>
       <c r="BB62">
-        <v>232855</v>
+        <v>243235</v>
       </c>
       <c r="BC62">
-        <v>1377096</v>
+        <v>1674962</v>
       </c>
       <c r="BD62">
-        <v>1412123</v>
+        <v>1769517</v>
       </c>
       <c r="BE62">
-        <v>1301050</v>
+        <v>1692668</v>
       </c>
       <c r="BF62">
-        <v>1254008</v>
+        <v>1639987</v>
       </c>
       <c r="BG62">
-        <v>1334170</v>
+        <v>1610476</v>
       </c>
       <c r="BH62">
-        <v>1331221</v>
+        <v>1563861</v>
       </c>
       <c r="BI62">
-        <v>1251661</v>
+        <v>1467534</v>
       </c>
       <c r="BJ62">
-        <v>1102011</v>
+        <v>1310434</v>
       </c>
       <c r="BK62">
-        <v>1034078</v>
+        <v>1244110</v>
       </c>
       <c r="BL62">
-        <v>1466432</v>
+        <v>1765967</v>
       </c>
       <c r="BM62">
-        <v>911489</v>
+        <v>1114404</v>
       </c>
       <c r="BN62">
-        <v>834096</v>
+        <v>1011961</v>
       </c>
       <c r="BO62">
-        <v>728476</v>
+        <v>868021</v>
       </c>
       <c r="BP62">
-        <v>578172</v>
+        <v>674499</v>
       </c>
       <c r="BQ62">
-        <v>439223</v>
+        <v>492586</v>
       </c>
       <c r="BR62">
-        <v>272703</v>
+        <v>299668</v>
       </c>
       <c r="BS62">
-        <v>171747</v>
+        <v>183437</v>
       </c>
       <c r="BT62">
-        <v>140452</v>
+        <v>141620</v>
       </c>
       <c r="BU62">
-        <v>1450561</v>
+        <v>1751223</v>
       </c>
       <c r="BV62">
-        <v>7608532</v>
+        <v>7180842</v>
       </c>
       <c r="BW62">
-        <v>7673356</v>
+        <v>7462719</v>
       </c>
       <c r="BX62">
-        <v>7622404</v>
+        <v>7605004</v>
       </c>
       <c r="BY62">
-        <v>8033246</v>
+        <v>7657754</v>
       </c>
       <c r="BZ62">
-        <v>8160272</v>
+        <v>7894093</v>
       </c>
       <c r="CA62">
-        <v>8073360</v>
+        <v>7796461</v>
       </c>
       <c r="CB62">
-        <v>7595580</v>
+        <v>7334016</v>
       </c>
       <c r="CC62">
-        <v>7589407</v>
+        <v>7341533</v>
       </c>
       <c r="CD62">
-        <v>6999605</v>
+        <v>6604685</v>
       </c>
       <c r="CE62">
-        <v>7981424</v>
+        <v>7812472</v>
       </c>
       <c r="CF62">
-        <v>8766199</v>
+        <v>8664112</v>
       </c>
       <c r="CG62">
-        <v>8601794</v>
+        <v>8636571</v>
       </c>
       <c r="CH62">
-        <v>7646132</v>
+        <v>7739444</v>
       </c>
       <c r="CI62">
-        <v>6414135</v>
+        <v>6543336</v>
       </c>
       <c r="CJ62">
-        <v>4443861</v>
+        <v>4596310</v>
       </c>
       <c r="CK62">
-        <v>2965525</v>
+        <v>3081096</v>
       </c>
       <c r="CL62">
-        <v>3314758</v>
+        <v>3447683</v>
       </c>
       <c r="CM62">
-        <v>6558095</v>
+        <v>6200604</v>
       </c>
       <c r="CN62">
-        <v>8022075</v>
+        <v>7559123</v>
       </c>
       <c r="CO62">
-        <v>8039914</v>
+        <v>7793163</v>
       </c>
       <c r="CP62">
-        <v>7811627</v>
+        <v>7741941</v>
       </c>
       <c r="CQ62">
-        <v>8252448</v>
+        <v>7798267</v>
       </c>
       <c r="CR62">
-        <v>8439355</v>
+        <v>7999132</v>
       </c>
       <c r="CS62">
-        <v>8394210</v>
+        <v>7858737</v>
       </c>
       <c r="CT62">
-        <v>7859397</v>
+        <v>7355069</v>
       </c>
       <c r="CU62">
-        <v>7810312</v>
+        <v>7319852</v>
       </c>
       <c r="CV62">
-        <v>7360660</v>
+        <v>6936439</v>
       </c>
       <c r="CW62">
-        <v>8163657</v>
+        <v>7735333</v>
       </c>
       <c r="CX62">
-        <v>8715485</v>
+        <v>8397258</v>
       </c>
       <c r="CY62">
-        <v>8333984</v>
+        <v>8165156</v>
       </c>
       <c r="CZ62">
-        <v>7109917</v>
+        <v>7094256</v>
       </c>
       <c r="DA62">
-        <v>5767338</v>
+        <v>5813002</v>
       </c>
       <c r="DB62">
-        <v>3737490</v>
+        <v>3842861</v>
       </c>
       <c r="DC62">
-        <v>2254607</v>
+        <v>2338618</v>
       </c>
       <c r="DD62">
-        <v>1890296</v>
+        <v>1991780</v>
       </c>
       <c r="DE62">
-        <v>6877962</v>
+        <v>6501642</v>
       </c>
     </row>
     <row r="63" spans="1:109">
@@ -48660,328 +48881,328 @@
         <v>2021</v>
       </c>
       <c r="B63">
-        <v>1611447</v>
+        <v>1604031</v>
       </c>
       <c r="C63">
-        <v>1574279</v>
+        <v>1584574</v>
       </c>
       <c r="D63">
-        <v>1604252</v>
+        <v>1682543</v>
       </c>
       <c r="E63">
-        <v>1737417</v>
+        <v>1640723</v>
       </c>
       <c r="F63">
-        <v>1779878</v>
+        <v>1705324</v>
       </c>
       <c r="G63">
-        <v>1591000</v>
+        <v>1581120</v>
       </c>
       <c r="H63">
-        <v>1526230</v>
+        <v>1508357</v>
       </c>
       <c r="I63">
-        <v>1411143</v>
+        <v>1384867</v>
       </c>
       <c r="J63">
-        <v>1539083</v>
+        <v>1516578</v>
       </c>
       <c r="K63">
-        <v>1440086</v>
+        <v>1426333</v>
       </c>
       <c r="L63">
-        <v>1465890</v>
+        <v>1466581</v>
       </c>
       <c r="M63">
-        <v>1379872</v>
+        <v>1391844</v>
       </c>
       <c r="N63">
-        <v>1129999</v>
+        <v>1148626</v>
       </c>
       <c r="O63">
-        <v>866544</v>
+        <v>875123</v>
       </c>
       <c r="P63">
-        <v>531821</v>
+        <v>534775</v>
       </c>
       <c r="Q63">
-        <v>348507</v>
+        <v>347406</v>
       </c>
       <c r="R63">
-        <v>342065</v>
+        <v>341725</v>
       </c>
       <c r="S63">
-        <v>1483827</v>
+        <v>1473677</v>
       </c>
       <c r="T63">
-        <v>1667055</v>
+        <v>1661813</v>
       </c>
       <c r="U63">
-        <v>1606607</v>
+        <v>1634465</v>
       </c>
       <c r="V63">
-        <v>1599593</v>
+        <v>1659879</v>
       </c>
       <c r="W63">
-        <v>1729638</v>
+        <v>1558318</v>
       </c>
       <c r="X63">
-        <v>1715925</v>
+        <v>1551734</v>
       </c>
       <c r="Y63">
-        <v>1481558</v>
+        <v>1409994</v>
       </c>
       <c r="Z63">
-        <v>1382214</v>
+        <v>1335929</v>
       </c>
       <c r="AA63">
-        <v>1257526</v>
+        <v>1224520</v>
       </c>
       <c r="AB63">
-        <v>1580136</v>
+        <v>1559775</v>
       </c>
       <c r="AC63">
-        <v>1289000</v>
+        <v>1258066</v>
       </c>
       <c r="AD63">
-        <v>1289382</v>
+        <v>1269639</v>
       </c>
       <c r="AE63">
-        <v>1176773</v>
+        <v>1171459</v>
       </c>
       <c r="AF63">
-        <v>894264</v>
+        <v>914206</v>
       </c>
       <c r="AG63">
-        <v>635718</v>
+        <v>646483</v>
       </c>
       <c r="AH63">
-        <v>356967</v>
+        <v>361447</v>
       </c>
       <c r="AI63">
-        <v>206791</v>
+        <v>206849</v>
       </c>
       <c r="AJ63">
-        <v>153628</v>
+        <v>155205</v>
       </c>
       <c r="AK63">
-        <v>1525554</v>
+        <v>1515040</v>
       </c>
       <c r="AL63">
-        <v>1365824</v>
+        <v>1711174</v>
       </c>
       <c r="AM63">
-        <v>1291837</v>
+        <v>1655941</v>
       </c>
       <c r="AN63">
-        <v>1252349</v>
+        <v>1659496</v>
       </c>
       <c r="AO63">
-        <v>1336557</v>
+        <v>1633393</v>
       </c>
       <c r="AP63">
-        <v>1412844</v>
+        <v>1695406</v>
       </c>
       <c r="AQ63">
-        <v>1348732</v>
+        <v>1628300</v>
       </c>
       <c r="AR63">
-        <v>1233842</v>
+        <v>1500847</v>
       </c>
       <c r="AS63">
-        <v>1132270</v>
+        <v>1391968</v>
       </c>
       <c r="AT63">
-        <v>1411894</v>
+        <v>1702420</v>
       </c>
       <c r="AU63">
-        <v>1029114</v>
+        <v>1295247</v>
       </c>
       <c r="AV63">
-        <v>938397</v>
+        <v>1173298</v>
       </c>
       <c r="AW63">
-        <v>851398</v>
+        <v>1046649</v>
       </c>
       <c r="AX63">
-        <v>726865</v>
+        <v>867527</v>
       </c>
       <c r="AY63">
-        <v>574530</v>
+        <v>667136</v>
       </c>
       <c r="AZ63">
-        <v>360199</v>
+        <v>412029</v>
       </c>
       <c r="BA63">
-        <v>235340</v>
+        <v>262948</v>
       </c>
       <c r="BB63">
-        <v>245476</v>
+        <v>258676</v>
       </c>
       <c r="BC63">
-        <v>1355734</v>
+        <v>1657550</v>
       </c>
       <c r="BD63">
-        <v>1428574</v>
+        <v>1777055</v>
       </c>
       <c r="BE63">
-        <v>1321072</v>
+        <v>1695456</v>
       </c>
       <c r="BF63">
-        <v>1263894</v>
+        <v>1673648</v>
       </c>
       <c r="BG63">
-        <v>1325053</v>
+        <v>1616612</v>
       </c>
       <c r="BH63">
-        <v>1356878</v>
+        <v>1592716</v>
       </c>
       <c r="BI63">
-        <v>1275370</v>
+        <v>1493425</v>
       </c>
       <c r="BJ63">
-        <v>1131331</v>
+        <v>1342340</v>
       </c>
       <c r="BK63">
-        <v>1039180</v>
+        <v>1245504</v>
       </c>
       <c r="BL63">
-        <v>1482440</v>
+        <v>1776971</v>
       </c>
       <c r="BM63">
-        <v>942266</v>
+        <v>1149149</v>
       </c>
       <c r="BN63">
-        <v>844729</v>
+        <v>1028995</v>
       </c>
       <c r="BO63">
-        <v>742537</v>
+        <v>888068</v>
       </c>
       <c r="BP63">
-        <v>604528</v>
+        <v>708616</v>
       </c>
       <c r="BQ63">
-        <v>463232</v>
+        <v>524138</v>
       </c>
       <c r="BR63">
-        <v>287254</v>
+        <v>317315</v>
       </c>
       <c r="BS63">
-        <v>180696</v>
+        <v>194354</v>
       </c>
       <c r="BT63">
-        <v>150658</v>
+        <v>152715</v>
       </c>
       <c r="BU63">
-        <v>1427316</v>
+        <v>1733881</v>
       </c>
       <c r="BV63">
-        <v>7491695</v>
+        <v>7077664</v>
       </c>
       <c r="BW63">
-        <v>7671093</v>
+        <v>7327193</v>
       </c>
       <c r="BX63">
-        <v>7644967</v>
+        <v>7732992</v>
       </c>
       <c r="BY63">
-        <v>7900700</v>
+        <v>7539071</v>
       </c>
       <c r="BZ63">
-        <v>8212413</v>
+        <v>7917212</v>
       </c>
       <c r="CA63">
-        <v>8080945</v>
+        <v>7814331</v>
       </c>
       <c r="CB63">
-        <v>7745388</v>
+        <v>7478357</v>
       </c>
       <c r="CC63">
-        <v>7363109</v>
+        <v>7117642</v>
       </c>
       <c r="CD63">
-        <v>6973538</v>
+        <v>6568089</v>
       </c>
       <c r="CE63">
-        <v>8000939</v>
+        <v>7811099</v>
       </c>
       <c r="CF63">
-        <v>8534068</v>
+        <v>8412815</v>
       </c>
       <c r="CG63">
-        <v>8665957</v>
+        <v>8675611</v>
       </c>
       <c r="CH63">
-        <v>7780808</v>
+        <v>7865745</v>
       </c>
       <c r="CI63">
-        <v>6706045</v>
+        <v>6832052</v>
       </c>
       <c r="CJ63">
-        <v>4541992</v>
+        <v>4698333</v>
       </c>
       <c r="CK63">
-        <v>3029877</v>
+        <v>3154268</v>
       </c>
       <c r="CL63">
-        <v>3277910</v>
+        <v>3429420</v>
       </c>
       <c r="CM63">
-        <v>6373721</v>
+        <v>6038914</v>
       </c>
       <c r="CN63">
-        <v>7902714</v>
+        <v>7445514</v>
       </c>
       <c r="CO63">
-        <v>8040389</v>
+        <v>7689989</v>
       </c>
       <c r="CP63">
-        <v>7831885</v>
+        <v>7844068</v>
       </c>
       <c r="CQ63">
-        <v>8117877</v>
+        <v>7687047</v>
       </c>
       <c r="CR63">
-        <v>8458045</v>
+        <v>8020863</v>
       </c>
       <c r="CS63">
-        <v>8396599</v>
+        <v>7878179</v>
       </c>
       <c r="CT63">
-        <v>8022194</v>
+        <v>7501551</v>
       </c>
       <c r="CU63">
-        <v>7558584</v>
+        <v>7088221</v>
       </c>
       <c r="CV63">
-        <v>7323207</v>
+        <v>6893275</v>
       </c>
       <c r="CW63">
-        <v>8195959</v>
+        <v>7732177</v>
       </c>
       <c r="CX63">
-        <v>8494299</v>
+        <v>8155780</v>
       </c>
       <c r="CY63">
-        <v>8404374</v>
+        <v>8197769</v>
       </c>
       <c r="CZ63">
-        <v>7237355</v>
+        <v>7196203</v>
       </c>
       <c r="DA63">
-        <v>6004931</v>
+        <v>6045949</v>
       </c>
       <c r="DB63">
-        <v>3817568</v>
+        <v>3928650</v>
       </c>
       <c r="DC63">
-        <v>2301383</v>
+        <v>2390858</v>
       </c>
       <c r="DD63">
-        <v>1899313</v>
+        <v>2008983</v>
       </c>
       <c r="DE63">
-        <v>6686054</v>
+        <v>6334305</v>
       </c>
     </row>
     <row r="64" spans="1:109">
@@ -48989,328 +49210,328 @@
         <v>2022</v>
       </c>
       <c r="B64">
-        <v>1595801</v>
+        <v>1589153</v>
       </c>
       <c r="C64">
-        <v>1602211</v>
+        <v>1590576</v>
       </c>
       <c r="D64">
-        <v>1610486</v>
+        <v>1709446</v>
       </c>
       <c r="E64">
-        <v>1702090</v>
+        <v>1624414</v>
       </c>
       <c r="F64">
-        <v>1835047</v>
+        <v>1736590</v>
       </c>
       <c r="G64">
-        <v>1611007</v>
+        <v>1598236</v>
       </c>
       <c r="H64">
-        <v>1553583</v>
+        <v>1536309</v>
       </c>
       <c r="I64">
-        <v>1408788</v>
+        <v>1383895</v>
       </c>
       <c r="J64">
-        <v>1544117</v>
+        <v>1521563</v>
       </c>
       <c r="K64">
-        <v>1446446</v>
+        <v>1428074</v>
       </c>
       <c r="L64">
-        <v>1444813</v>
+        <v>1445001</v>
       </c>
       <c r="M64">
-        <v>1389913</v>
+        <v>1396251</v>
       </c>
       <c r="N64">
-        <v>1170606</v>
+        <v>1190378</v>
       </c>
       <c r="O64">
-        <v>893117</v>
+        <v>905144</v>
       </c>
       <c r="P64">
-        <v>573392</v>
+        <v>574840</v>
       </c>
       <c r="Q64">
-        <v>360140</v>
+        <v>359947</v>
       </c>
       <c r="R64">
-        <v>347328</v>
+        <v>346096</v>
       </c>
       <c r="S64">
-        <v>1486705</v>
+        <v>1477760</v>
       </c>
       <c r="T64">
-        <v>1649686</v>
+        <v>1643403</v>
       </c>
       <c r="U64">
-        <v>1640385</v>
+        <v>1648469</v>
       </c>
       <c r="V64">
-        <v>1607726</v>
+        <v>1690368</v>
       </c>
       <c r="W64">
-        <v>1692496</v>
+        <v>1558565</v>
       </c>
       <c r="X64">
-        <v>1781682</v>
+        <v>1588425</v>
       </c>
       <c r="Y64">
-        <v>1509795</v>
+        <v>1430017</v>
       </c>
       <c r="Z64">
-        <v>1413999</v>
+        <v>1361267</v>
       </c>
       <c r="AA64">
-        <v>1252548</v>
+        <v>1219473</v>
       </c>
       <c r="AB64">
-        <v>1583646</v>
+        <v>1563810</v>
       </c>
       <c r="AC64">
-        <v>1291173</v>
+        <v>1256619</v>
       </c>
       <c r="AD64">
-        <v>1266145</v>
+        <v>1246086</v>
       </c>
       <c r="AE64">
-        <v>1185126</v>
+        <v>1172926</v>
       </c>
       <c r="AF64">
-        <v>930563</v>
+        <v>947641</v>
       </c>
       <c r="AG64">
-        <v>650363</v>
+        <v>666777</v>
       </c>
       <c r="AH64">
-        <v>387519</v>
+        <v>389742</v>
       </c>
       <c r="AI64">
-        <v>214066</v>
+        <v>215291</v>
       </c>
       <c r="AJ64">
-        <v>158804</v>
+        <v>159891</v>
       </c>
       <c r="AK64">
-        <v>1527043</v>
+        <v>1517312</v>
       </c>
       <c r="AL64">
-        <v>1385347</v>
+        <v>1716620</v>
       </c>
       <c r="AM64">
-        <v>1339817</v>
+        <v>1697847</v>
       </c>
       <c r="AN64">
-        <v>1297116</v>
+        <v>1711950</v>
       </c>
       <c r="AO64">
-        <v>1368852</v>
+        <v>1677148</v>
       </c>
       <c r="AP64">
-        <v>1464605</v>
+        <v>1744172</v>
       </c>
       <c r="AQ64">
-        <v>1383603</v>
+        <v>1661132</v>
       </c>
       <c r="AR64">
-        <v>1280957</v>
+        <v>1550800</v>
       </c>
       <c r="AS64">
-        <v>1154451</v>
+        <v>1408512</v>
       </c>
       <c r="AT64">
-        <v>1438309</v>
+        <v>1723885</v>
       </c>
       <c r="AU64">
-        <v>1073286</v>
+        <v>1343972</v>
       </c>
       <c r="AV64">
-        <v>949590</v>
+        <v>1189935</v>
       </c>
       <c r="AW64">
-        <v>872027</v>
+        <v>1071299</v>
       </c>
       <c r="AX64">
-        <v>757268</v>
+        <v>911313</v>
       </c>
       <c r="AY64">
-        <v>600128</v>
+        <v>698241</v>
       </c>
       <c r="AZ64">
-        <v>395823</v>
+        <v>454192</v>
       </c>
       <c r="BA64">
-        <v>250987</v>
+        <v>282144</v>
       </c>
       <c r="BB64">
-        <v>260882</v>
+        <v>277324</v>
       </c>
       <c r="BC64">
-        <v>1361837</v>
+        <v>1670988</v>
       </c>
       <c r="BD64">
-        <v>1451024</v>
+        <v>1786214</v>
       </c>
       <c r="BE64">
-        <v>1378119</v>
+        <v>1746218</v>
       </c>
       <c r="BF64">
-        <v>1310835</v>
+        <v>1728438</v>
       </c>
       <c r="BG64">
-        <v>1351732</v>
+        <v>1660650</v>
       </c>
       <c r="BH64">
-        <v>1410216</v>
+        <v>1652660</v>
       </c>
       <c r="BI64">
-        <v>1312128</v>
+        <v>1532558</v>
       </c>
       <c r="BJ64">
-        <v>1182817</v>
+        <v>1391689</v>
       </c>
       <c r="BK64">
-        <v>1055079</v>
+        <v>1258687</v>
       </c>
       <c r="BL64">
-        <v>1511318</v>
+        <v>1800291</v>
       </c>
       <c r="BM64">
-        <v>980577</v>
+        <v>1190202</v>
       </c>
       <c r="BN64">
-        <v>853286</v>
+        <v>1041850</v>
       </c>
       <c r="BO64">
-        <v>762365</v>
+        <v>912049</v>
       </c>
       <c r="BP64">
-        <v>633088</v>
+        <v>746165</v>
       </c>
       <c r="BQ64">
-        <v>480158</v>
+        <v>548088</v>
       </c>
       <c r="BR64">
-        <v>315939</v>
+        <v>349196</v>
       </c>
       <c r="BS64">
-        <v>192203</v>
+        <v>207822</v>
       </c>
       <c r="BT64">
-        <v>163430</v>
+        <v>167033</v>
       </c>
       <c r="BU64">
-        <v>1431183</v>
+        <v>1748503</v>
       </c>
       <c r="BV64">
-        <v>7356992</v>
+        <v>6961511</v>
       </c>
       <c r="BW64">
-        <v>7741953</v>
+        <v>7339574</v>
       </c>
       <c r="BX64">
-        <v>7689210</v>
+        <v>7794721</v>
       </c>
       <c r="BY64">
-        <v>7835078</v>
+        <v>7508775</v>
       </c>
       <c r="BZ64">
-        <v>8287217</v>
+        <v>7961631</v>
       </c>
       <c r="CA64">
-        <v>8087644</v>
+        <v>7834491</v>
       </c>
       <c r="CB64">
-        <v>7881505</v>
+        <v>7607728</v>
       </c>
       <c r="CC64">
-        <v>7307866</v>
+        <v>7062433</v>
       </c>
       <c r="CD64">
-        <v>6941953</v>
+        <v>6540261</v>
       </c>
       <c r="CE64">
-        <v>7946345</v>
+        <v>7742469</v>
       </c>
       <c r="CF64">
-        <v>8295682</v>
+        <v>8166992</v>
       </c>
       <c r="CG64">
-        <v>8659593</v>
+        <v>8628035</v>
       </c>
       <c r="CH64">
-        <v>7917246</v>
+        <v>8003142</v>
       </c>
       <c r="CI64">
-        <v>6666002</v>
+        <v>6793663</v>
       </c>
       <c r="CJ64">
-        <v>4965371</v>
+        <v>5107957</v>
       </c>
       <c r="CK64">
-        <v>3141896</v>
+        <v>3273386</v>
       </c>
       <c r="CL64">
-        <v>3258757</v>
+        <v>3429046</v>
       </c>
       <c r="CM64">
-        <v>6300928</v>
+        <v>5977579</v>
       </c>
       <c r="CN64">
-        <v>7757405</v>
+        <v>7320287</v>
       </c>
       <c r="CO64">
-        <v>8126268</v>
+        <v>7727625</v>
       </c>
       <c r="CP64">
-        <v>7898714</v>
+        <v>7917058</v>
       </c>
       <c r="CQ64">
-        <v>8047652</v>
+        <v>7667598</v>
       </c>
       <c r="CR64">
-        <v>8513318</v>
+        <v>8072972</v>
       </c>
       <c r="CS64">
-        <v>8398982</v>
+        <v>7908391</v>
       </c>
       <c r="CT64">
-        <v>8169329</v>
+        <v>7631604</v>
       </c>
       <c r="CU64">
-        <v>7495021</v>
+        <v>7031172</v>
       </c>
       <c r="CV64">
-        <v>7289474</v>
+        <v>6863028</v>
       </c>
       <c r="CW64">
-        <v>8137461</v>
+        <v>7654921</v>
       </c>
       <c r="CX64">
-        <v>8266232</v>
+        <v>7915006</v>
       </c>
       <c r="CY64">
-        <v>8396779</v>
+        <v>8147485</v>
       </c>
       <c r="CZ64">
-        <v>7370679</v>
+        <v>7309092</v>
       </c>
       <c r="DA64">
-        <v>5935492</v>
+        <v>5990160</v>
       </c>
       <c r="DB64">
-        <v>4207648</v>
+        <v>4285358</v>
       </c>
       <c r="DC64">
-        <v>2391096</v>
+        <v>2485058</v>
       </c>
       <c r="DD64">
-        <v>1915046</v>
+        <v>2033273</v>
       </c>
       <c r="DE64">
-        <v>6603258</v>
+        <v>6265788</v>
       </c>
     </row>
     <row r="65" spans="1:109">
@@ -49318,328 +49539,328 @@
         <v>2023</v>
       </c>
       <c r="B65">
-        <v>1579250</v>
+        <v>1571755</v>
       </c>
       <c r="C65">
-        <v>1638947</v>
+        <v>1620523</v>
       </c>
       <c r="D65">
-        <v>1616643</v>
+        <v>1710074</v>
       </c>
       <c r="E65">
-        <v>1681752</v>
+        <v>1628857</v>
       </c>
       <c r="F65">
-        <v>1877189</v>
+        <v>1761922</v>
       </c>
       <c r="G65">
-        <v>1647409</v>
+        <v>1626023</v>
       </c>
       <c r="H65">
-        <v>1582410</v>
+        <v>1567260</v>
       </c>
       <c r="I65">
-        <v>1423334</v>
+        <v>1396645</v>
       </c>
       <c r="J65">
-        <v>1552676</v>
+        <v>1530738</v>
       </c>
       <c r="K65">
-        <v>1447130</v>
+        <v>1425602</v>
       </c>
       <c r="L65">
-        <v>1426787</v>
+        <v>1424162</v>
       </c>
       <c r="M65">
-        <v>1402809</v>
+        <v>1405882</v>
       </c>
       <c r="N65">
-        <v>1208154</v>
+        <v>1227145</v>
       </c>
       <c r="O65">
-        <v>923975</v>
+        <v>939391</v>
       </c>
       <c r="P65">
-        <v>611217</v>
+        <v>613535</v>
       </c>
       <c r="Q65">
-        <v>379103</v>
+        <v>380216</v>
       </c>
       <c r="R65">
-        <v>359118</v>
+        <v>358269</v>
       </c>
       <c r="S65">
-        <v>1485264</v>
+        <v>1476292</v>
       </c>
       <c r="T65">
-        <v>1632005</v>
+        <v>1623500</v>
       </c>
       <c r="U65">
-        <v>1681531</v>
+        <v>1677602</v>
       </c>
       <c r="V65">
-        <v>1613873</v>
+        <v>1700479</v>
       </c>
       <c r="W65">
-        <v>1666246</v>
+        <v>1575888</v>
       </c>
       <c r="X65">
-        <v>1837511</v>
+        <v>1622722</v>
       </c>
       <c r="Y65">
-        <v>1554409</v>
+        <v>1459511</v>
       </c>
       <c r="Z65">
-        <v>1446718</v>
+        <v>1389126</v>
       </c>
       <c r="AA65">
-        <v>1267448</v>
+        <v>1229394</v>
       </c>
       <c r="AB65">
-        <v>1590503</v>
+        <v>1571591</v>
       </c>
       <c r="AC65">
-        <v>1286225</v>
+        <v>1251529</v>
       </c>
       <c r="AD65">
-        <v>1248055</v>
+        <v>1225212</v>
       </c>
       <c r="AE65">
-        <v>1193849</v>
+        <v>1177820</v>
       </c>
       <c r="AF65">
-        <v>966956</v>
+        <v>979078</v>
       </c>
       <c r="AG65">
-        <v>672753</v>
+        <v>692400</v>
       </c>
       <c r="AH65">
-        <v>414671</v>
+        <v>417792</v>
       </c>
       <c r="AI65">
-        <v>226317</v>
+        <v>228557</v>
       </c>
       <c r="AJ65">
-        <v>166713</v>
+        <v>167805</v>
       </c>
       <c r="AK65">
-        <v>1527705</v>
+        <v>1517650</v>
       </c>
       <c r="AL65">
-        <v>1409942</v>
+        <v>1726472</v>
       </c>
       <c r="AM65">
-        <v>1390962</v>
+        <v>1749511</v>
       </c>
       <c r="AN65">
-        <v>1358510</v>
+        <v>1769028</v>
       </c>
       <c r="AO65">
-        <v>1420537</v>
+        <v>1744883</v>
       </c>
       <c r="AP65">
-        <v>1521494</v>
+        <v>1800631</v>
       </c>
       <c r="AQ65">
-        <v>1434039</v>
+        <v>1709512</v>
       </c>
       <c r="AR65">
-        <v>1337269</v>
+        <v>1609403</v>
       </c>
       <c r="AS65">
-        <v>1183613</v>
+        <v>1433080</v>
       </c>
       <c r="AT65">
-        <v>1462126</v>
+        <v>1745752</v>
       </c>
       <c r="AU65">
-        <v>1109786</v>
+        <v>1381978</v>
       </c>
       <c r="AV65">
-        <v>965314</v>
+        <v>1208992</v>
       </c>
       <c r="AW65">
-        <v>900570</v>
+        <v>1107321</v>
       </c>
       <c r="AX65">
-        <v>789039</v>
+        <v>954298</v>
       </c>
       <c r="AY65">
-        <v>629717</v>
+        <v>735247</v>
       </c>
       <c r="AZ65">
-        <v>433194</v>
+        <v>498625</v>
       </c>
       <c r="BA65">
-        <v>267917</v>
+        <v>303166</v>
       </c>
       <c r="BB65">
-        <v>279614</v>
+        <v>300007</v>
       </c>
       <c r="BC65">
-        <v>1378006</v>
+        <v>1696550</v>
       </c>
       <c r="BD65">
-        <v>1478385</v>
+        <v>1800200</v>
       </c>
       <c r="BE65">
-        <v>1440401</v>
+        <v>1806045</v>
       </c>
       <c r="BF65">
-        <v>1380189</v>
+        <v>1798673</v>
       </c>
       <c r="BG65">
-        <v>1396980</v>
+        <v>1726845</v>
       </c>
       <c r="BH65">
-        <v>1467029</v>
+        <v>1720120</v>
       </c>
       <c r="BI65">
-        <v>1367542</v>
+        <v>1590242</v>
       </c>
       <c r="BJ65">
-        <v>1245328</v>
+        <v>1454932</v>
       </c>
       <c r="BK65">
-        <v>1080155</v>
+        <v>1280930</v>
       </c>
       <c r="BL65">
-        <v>1536105</v>
+        <v>1822279</v>
       </c>
       <c r="BM65">
-        <v>1013363</v>
+        <v>1223395</v>
       </c>
       <c r="BN65">
-        <v>865431</v>
+        <v>1055532</v>
       </c>
       <c r="BO65">
-        <v>789129</v>
+        <v>946511</v>
       </c>
       <c r="BP65">
-        <v>662354</v>
+        <v>783568</v>
       </c>
       <c r="BQ65">
-        <v>503318</v>
+        <v>578297</v>
       </c>
       <c r="BR65">
-        <v>343970</v>
+        <v>381553</v>
       </c>
       <c r="BS65">
-        <v>205412</v>
+        <v>223714</v>
       </c>
       <c r="BT65">
-        <v>178834</v>
+        <v>184057</v>
       </c>
       <c r="BU65">
-        <v>1444428</v>
+        <v>1774144</v>
       </c>
       <c r="BV65">
-        <v>7231190</v>
+        <v>6852366</v>
       </c>
       <c r="BW65">
-        <v>7806292</v>
+        <v>7385791</v>
       </c>
       <c r="BX65">
-        <v>7761304</v>
+        <v>7802741</v>
       </c>
       <c r="BY65">
-        <v>7825119</v>
+        <v>7572146</v>
       </c>
       <c r="BZ65">
-        <v>8330381</v>
+        <v>7979431</v>
       </c>
       <c r="CA65">
-        <v>8128700</v>
+        <v>7879644</v>
       </c>
       <c r="CB65">
-        <v>8017712</v>
+        <v>7742849</v>
       </c>
       <c r="CC65">
-        <v>7363861</v>
+        <v>7109592</v>
       </c>
       <c r="CD65">
-        <v>6898111</v>
+        <v>6509212</v>
       </c>
       <c r="CE65">
-        <v>7848994</v>
+        <v>7633721</v>
       </c>
       <c r="CF65">
-        <v>8074306</v>
+        <v>7932771</v>
       </c>
       <c r="CG65">
-        <v>8628762</v>
+        <v>8573831</v>
       </c>
       <c r="CH65">
-        <v>8045592</v>
+        <v>8115202</v>
       </c>
       <c r="CI65">
-        <v>6777456</v>
+        <v>6896266</v>
       </c>
       <c r="CJ65">
-        <v>5176771</v>
+        <v>5318526</v>
       </c>
       <c r="CK65">
-        <v>3336808</v>
+        <v>3479137</v>
       </c>
       <c r="CL65">
-        <v>3295561</v>
+        <v>3482829</v>
       </c>
       <c r="CM65">
-        <v>6250439</v>
+        <v>5928911</v>
       </c>
       <c r="CN65">
-        <v>7612889</v>
+        <v>7200572</v>
       </c>
       <c r="CO65">
-        <v>8199992</v>
+        <v>7771087</v>
       </c>
       <c r="CP65">
-        <v>7992784</v>
+        <v>7959586</v>
       </c>
       <c r="CQ65">
-        <v>8036804</v>
+        <v>7743176</v>
       </c>
       <c r="CR65">
-        <v>8559725</v>
+        <v>8110615</v>
       </c>
       <c r="CS65">
-        <v>8427717</v>
+        <v>7962491</v>
       </c>
       <c r="CT65">
-        <v>8313744</v>
+        <v>7771696</v>
       </c>
       <c r="CU65">
-        <v>7561581</v>
+        <v>7083961</v>
       </c>
       <c r="CV65">
-        <v>7244532</v>
+        <v>6830240</v>
       </c>
       <c r="CW65">
-        <v>8023092</v>
+        <v>7536867</v>
       </c>
       <c r="CX65">
-        <v>8072545</v>
+        <v>7696748</v>
       </c>
       <c r="CY65">
-        <v>8370316</v>
+        <v>8098375</v>
       </c>
       <c r="CZ65">
-        <v>7509031</v>
+        <v>7411166</v>
       </c>
       <c r="DA65">
-        <v>6028411</v>
+        <v>6068975</v>
       </c>
       <c r="DB65">
-        <v>4400281</v>
+        <v>4474797</v>
       </c>
       <c r="DC65">
-        <v>2559737</v>
+        <v>2659629</v>
       </c>
       <c r="DD65">
-        <v>1974713</v>
+        <v>2101909</v>
       </c>
       <c r="DE65">
-        <v>6546555</v>
+        <v>6212990</v>
       </c>
     </row>
     <row r="66" spans="1:109">
@@ -49647,328 +49868,657 @@
         <v>2024</v>
       </c>
       <c r="B66">
-        <v>1579220</v>
+        <v>1563763</v>
       </c>
       <c r="C66">
-        <v>1663315</v>
+        <v>1641635</v>
       </c>
       <c r="D66">
-        <v>1629646</v>
+        <v>1701416</v>
       </c>
       <c r="E66">
-        <v>1673443</v>
+        <v>1657652</v>
       </c>
       <c r="F66">
-        <v>1896003</v>
+        <v>1770829</v>
       </c>
       <c r="G66">
-        <v>1712030</v>
+        <v>1673699</v>
       </c>
       <c r="H66">
-        <v>1598689</v>
+        <v>1584449</v>
       </c>
       <c r="I66">
-        <v>1458855</v>
+        <v>1432343</v>
       </c>
       <c r="J66">
-        <v>1556303</v>
+        <v>1534644</v>
       </c>
       <c r="K66">
-        <v>1444238</v>
+        <v>1417125</v>
       </c>
       <c r="L66">
-        <v>1406178</v>
+        <v>1399800</v>
       </c>
       <c r="M66">
-        <v>1412432</v>
+        <v>1413186</v>
       </c>
       <c r="N66">
-        <v>1241819</v>
+        <v>1258918</v>
       </c>
       <c r="O66">
-        <v>960339</v>
+        <v>976813</v>
       </c>
       <c r="P66">
-        <v>656428</v>
+        <v>660492</v>
       </c>
       <c r="Q66">
-        <v>397005</v>
+        <v>398810</v>
       </c>
       <c r="R66">
-        <v>372179</v>
+        <v>371700</v>
       </c>
       <c r="S66">
-        <v>1486059</v>
+        <v>1473738</v>
       </c>
       <c r="T66">
-        <v>1631979</v>
+        <v>1613703</v>
       </c>
       <c r="U66">
-        <v>1709605</v>
+        <v>1696824</v>
       </c>
       <c r="V66">
-        <v>1628378</v>
+        <v>1702428</v>
       </c>
       <c r="W66">
-        <v>1654728</v>
+        <v>1614432</v>
       </c>
       <c r="X66">
-        <v>1866531</v>
+        <v>1643525</v>
       </c>
       <c r="Y66">
-        <v>1627265</v>
+        <v>1509220</v>
       </c>
       <c r="Z66">
-        <v>1469688</v>
+        <v>1405261</v>
       </c>
       <c r="AA66">
-        <v>1302523</v>
+        <v>1260575</v>
       </c>
       <c r="AB66">
-        <v>1591074</v>
+        <v>1572306</v>
       </c>
       <c r="AC66">
-        <v>1277824</v>
+        <v>1241216</v>
       </c>
       <c r="AD66">
-        <v>1228670</v>
+        <v>1203491</v>
       </c>
       <c r="AE66">
-        <v>1200756</v>
+        <v>1182313</v>
       </c>
       <c r="AF66">
-        <v>999336</v>
+        <v>1004888</v>
       </c>
       <c r="AG66">
-        <v>701142</v>
+        <v>721395</v>
       </c>
       <c r="AH66">
-        <v>445087</v>
+        <v>450505</v>
       </c>
       <c r="AI66">
-        <v>238240</v>
+        <v>240907</v>
       </c>
       <c r="AJ66">
-        <v>175594</v>
+        <v>176828</v>
       </c>
       <c r="AK66">
-        <v>1531318</v>
+        <v>1517249</v>
       </c>
       <c r="AL66">
-        <v>1446993</v>
+        <v>1749708</v>
       </c>
       <c r="AM66">
-        <v>1432556</v>
+        <v>1786334</v>
       </c>
       <c r="AN66">
-        <v>1435426</v>
+        <v>1830106</v>
       </c>
       <c r="AO66">
-        <v>1488381</v>
+        <v>1830573</v>
       </c>
       <c r="AP66">
-        <v>1582962</v>
+        <v>1858199</v>
       </c>
       <c r="AQ66">
-        <v>1506265</v>
+        <v>1778436</v>
       </c>
       <c r="AR66">
-        <v>1393495</v>
+        <v>1662339</v>
       </c>
       <c r="AS66">
-        <v>1225019</v>
+        <v>1473706</v>
       </c>
       <c r="AT66">
-        <v>1486129</v>
+        <v>1772516</v>
       </c>
       <c r="AU66">
-        <v>1141832</v>
+        <v>1406618</v>
       </c>
       <c r="AV66">
-        <v>991289</v>
+        <v>1237457</v>
       </c>
       <c r="AW66">
-        <v>931462</v>
+        <v>1145451</v>
       </c>
       <c r="AX66">
-        <v>818004</v>
+        <v>992983</v>
       </c>
       <c r="AY66">
-        <v>661299</v>
+        <v>774730</v>
       </c>
       <c r="AZ66">
-        <v>473361</v>
+        <v>545799</v>
       </c>
       <c r="BA66">
-        <v>288433</v>
+        <v>327331</v>
       </c>
       <c r="BB66">
-        <v>300584</v>
+        <v>325594</v>
       </c>
       <c r="BC66">
-        <v>1397802</v>
+        <v>1718473</v>
       </c>
       <c r="BD66">
-        <v>1518628</v>
+        <v>1827084</v>
       </c>
       <c r="BE66">
-        <v>1491923</v>
+        <v>1852074</v>
       </c>
       <c r="BF66">
-        <v>1464593</v>
+        <v>1877686</v>
       </c>
       <c r="BG66">
-        <v>1459586</v>
+        <v>1818248</v>
       </c>
       <c r="BH66">
-        <v>1527298</v>
+        <v>1788681</v>
       </c>
       <c r="BI66">
-        <v>1442054</v>
+        <v>1669241</v>
       </c>
       <c r="BJ66">
-        <v>1309004</v>
+        <v>1520170</v>
       </c>
       <c r="BK66">
-        <v>1118370</v>
+        <v>1318251</v>
       </c>
       <c r="BL66">
-        <v>1559384</v>
+        <v>1847703</v>
       </c>
       <c r="BM66">
-        <v>1041639</v>
+        <v>1246887</v>
       </c>
       <c r="BN66">
-        <v>889072</v>
+        <v>1079475</v>
       </c>
       <c r="BO66">
-        <v>817035</v>
+        <v>981165</v>
       </c>
       <c r="BP66">
-        <v>688885</v>
+        <v>817387</v>
       </c>
       <c r="BQ66">
-        <v>529250</v>
+        <v>610907</v>
       </c>
       <c r="BR66">
-        <v>373815</v>
+        <v>416582</v>
       </c>
       <c r="BS66">
-        <v>220338</v>
+        <v>241049</v>
       </c>
       <c r="BT66">
-        <v>195753</v>
+        <v>203100</v>
       </c>
       <c r="BU66">
-        <v>1463187</v>
+        <v>1799695</v>
       </c>
       <c r="BV66">
-        <v>7173793</v>
+        <v>6798625</v>
       </c>
       <c r="BW66">
-        <v>7805446</v>
+        <v>7382613</v>
       </c>
       <c r="BX66">
-        <v>7850038</v>
+        <v>7783780</v>
       </c>
       <c r="BY66">
-        <v>7861138</v>
+        <v>7726819</v>
       </c>
       <c r="BZ66">
-        <v>8355022</v>
+        <v>7986169</v>
       </c>
       <c r="CA66">
-        <v>8227071</v>
+        <v>7977477</v>
       </c>
       <c r="CB66">
-        <v>8111908</v>
+        <v>7838249</v>
       </c>
       <c r="CC66">
-        <v>7476517</v>
+        <v>7219782</v>
       </c>
       <c r="CD66">
-        <v>6835598</v>
+        <v>6470059</v>
       </c>
       <c r="CE66">
-        <v>7706146</v>
+        <v>7471879</v>
       </c>
       <c r="CF66">
-        <v>7910029</v>
+        <v>7755434</v>
       </c>
       <c r="CG66">
-        <v>8594795</v>
+        <v>8519313</v>
       </c>
       <c r="CH66">
-        <v>8132063</v>
+        <v>8181847</v>
       </c>
       <c r="CI66">
-        <v>6931769</v>
+        <v>7040814</v>
       </c>
       <c r="CJ66">
-        <v>5427669</v>
+        <v>5569866</v>
       </c>
       <c r="CK66">
-        <v>3479986</v>
+        <v>3628543</v>
       </c>
       <c r="CL66">
-        <v>3348367</v>
+        <v>3553038</v>
       </c>
       <c r="CM66">
-        <v>6214410</v>
+        <v>5896171</v>
       </c>
       <c r="CN66">
-        <v>7550541</v>
+        <v>7139389</v>
       </c>
       <c r="CO66">
-        <v>8204566</v>
+        <v>7763395</v>
       </c>
       <c r="CP66">
-        <v>8103136</v>
+        <v>7983813</v>
       </c>
       <c r="CQ66">
-        <v>8073972</v>
+        <v>7905154</v>
       </c>
       <c r="CR66">
-        <v>8590078</v>
+        <v>8139777</v>
       </c>
       <c r="CS66">
-        <v>8518338</v>
+        <v>8075311</v>
       </c>
       <c r="CT66">
-        <v>8414236</v>
+        <v>7877160</v>
       </c>
       <c r="CU66">
-        <v>7685888</v>
+        <v>7198440</v>
       </c>
       <c r="CV66">
-        <v>7169184</v>
+        <v>6781387</v>
       </c>
       <c r="CW66">
-        <v>7864860</v>
+        <v>7374854</v>
       </c>
       <c r="CX66">
-        <v>7932179</v>
+        <v>7534883</v>
       </c>
       <c r="CY66">
-        <v>8344891</v>
+        <v>8048526</v>
       </c>
       <c r="CZ66">
-        <v>7609364</v>
+        <v>7476258</v>
       </c>
       <c r="DA66">
-        <v>6171692</v>
+        <v>6192166</v>
       </c>
       <c r="DB66">
-        <v>4616966</v>
+        <v>4688689</v>
       </c>
       <c r="DC66">
-        <v>2682485</v>
+        <v>2785965</v>
       </c>
       <c r="DD66">
-        <v>2042666</v>
+        <v>2178677</v>
       </c>
       <c r="DE66">
-        <v>6506538</v>
+        <v>6179409</v>
+      </c>
+    </row>
+    <row r="67" spans="1:109">
+      <c r="A67">
+        <v>2025</v>
+      </c>
+      <c r="B67">
+        <v>1560023</v>
+      </c>
+      <c r="C67">
+        <v>1648858</v>
+      </c>
+      <c r="D67">
+        <v>1665851</v>
+      </c>
+      <c r="E67">
+        <v>1703243</v>
+      </c>
+      <c r="F67">
+        <v>1748301</v>
+      </c>
+      <c r="G67">
+        <v>1719916</v>
+      </c>
+      <c r="H67">
+        <v>1591127</v>
+      </c>
+      <c r="I67">
+        <v>1474164</v>
+      </c>
+      <c r="J67">
+        <v>1527704</v>
+      </c>
+      <c r="K67">
+        <v>1399699</v>
+      </c>
+      <c r="L67">
+        <v>1388890</v>
+      </c>
+      <c r="M67">
+        <v>1412894</v>
+      </c>
+      <c r="N67">
+        <v>1284793</v>
+      </c>
+      <c r="O67">
+        <v>1013064</v>
+      </c>
+      <c r="P67">
+        <v>710846</v>
+      </c>
+      <c r="Q67">
+        <v>417311</v>
+      </c>
+      <c r="R67">
+        <v>388868</v>
+      </c>
+      <c r="S67">
+        <v>1467491</v>
+      </c>
+      <c r="T67">
+        <v>1607863</v>
+      </c>
+      <c r="U67">
+        <v>1701404</v>
+      </c>
+      <c r="V67">
+        <v>1678166</v>
+      </c>
+      <c r="W67">
+        <v>1665504</v>
+      </c>
+      <c r="X67">
+        <v>1636625</v>
+      </c>
+      <c r="Y67">
+        <v>1556677</v>
+      </c>
+      <c r="Z67">
+        <v>1414112</v>
+      </c>
+      <c r="AA67">
+        <v>1297378</v>
+      </c>
+      <c r="AB67">
+        <v>1563396</v>
+      </c>
+      <c r="AC67">
+        <v>1222445</v>
+      </c>
+      <c r="AD67">
+        <v>1195500</v>
+      </c>
+      <c r="AE67">
+        <v>1179602</v>
+      </c>
+      <c r="AF67">
+        <v>1025180</v>
+      </c>
+      <c r="AG67">
+        <v>752664</v>
+      </c>
+      <c r="AH67">
+        <v>485882</v>
+      </c>
+      <c r="AI67">
+        <v>253403</v>
+      </c>
+      <c r="AJ67">
+        <v>187251</v>
+      </c>
+      <c r="AK67">
+        <v>1512486</v>
+      </c>
+      <c r="AL67">
+        <v>1768816</v>
+      </c>
+      <c r="AM67">
+        <v>1799899</v>
+      </c>
+      <c r="AN67">
+        <v>1841138</v>
+      </c>
+      <c r="AO67">
+        <v>1893000</v>
+      </c>
+      <c r="AP67">
+        <v>1880799</v>
+      </c>
+      <c r="AQ67">
+        <v>1831622</v>
+      </c>
+      <c r="AR67">
+        <v>1698543</v>
+      </c>
+      <c r="AS67">
+        <v>1515532</v>
+      </c>
+      <c r="AT67">
+        <v>1781611</v>
+      </c>
+      <c r="AU67">
+        <v>1419314</v>
+      </c>
+      <c r="AV67">
+        <v>1274705</v>
+      </c>
+      <c r="AW67">
+        <v>1166518</v>
+      </c>
+      <c r="AX67">
+        <v>1025156</v>
+      </c>
+      <c r="AY67">
+        <v>814306</v>
+      </c>
+      <c r="AZ67">
+        <v>594707</v>
+      </c>
+      <c r="BA67">
+        <v>351400</v>
+      </c>
+      <c r="BB67">
+        <v>354274</v>
+      </c>
+      <c r="BC67">
+        <v>1719423</v>
+      </c>
+      <c r="BD67">
+        <v>1847355</v>
+      </c>
+      <c r="BE67">
+        <v>1868564</v>
+      </c>
+      <c r="BF67">
+        <v>1896866</v>
+      </c>
+      <c r="BG67">
+        <v>1889056</v>
+      </c>
+      <c r="BH67">
+        <v>1817052</v>
+      </c>
+      <c r="BI67">
+        <v>1728755</v>
+      </c>
+      <c r="BJ67">
+        <v>1564932</v>
+      </c>
+      <c r="BK67">
+        <v>1357789</v>
+      </c>
+      <c r="BL67">
+        <v>1856606</v>
+      </c>
+      <c r="BM67">
+        <v>1259003</v>
+      </c>
+      <c r="BN67">
+        <v>1112574</v>
+      </c>
+      <c r="BO67">
+        <v>1001050</v>
+      </c>
+      <c r="BP67">
+        <v>846483</v>
+      </c>
+      <c r="BQ67">
+        <v>644507</v>
+      </c>
+      <c r="BR67">
+        <v>453742</v>
+      </c>
+      <c r="BS67">
+        <v>258176</v>
+      </c>
+      <c r="BT67">
+        <v>224396</v>
+      </c>
+      <c r="BU67">
+        <v>1802334</v>
+      </c>
+      <c r="BV67">
+        <v>6751993</v>
+      </c>
+      <c r="BW67">
+        <v>7327381</v>
+      </c>
+      <c r="BX67">
+        <v>7657457</v>
+      </c>
+      <c r="BY67">
+        <v>7883906</v>
+      </c>
+      <c r="BZ67">
+        <v>7900311</v>
+      </c>
+      <c r="CA67">
+        <v>8048058</v>
+      </c>
+      <c r="CB67">
+        <v>7880818</v>
+      </c>
+      <c r="CC67">
+        <v>7349297</v>
+      </c>
+      <c r="CD67">
+        <v>6376887</v>
+      </c>
+      <c r="CE67">
+        <v>7283359</v>
+      </c>
+      <c r="CF67">
+        <v>7671649</v>
+      </c>
+      <c r="CG67">
+        <v>8388786</v>
+      </c>
+      <c r="CH67">
+        <v>8222525</v>
+      </c>
+      <c r="CI67">
+        <v>7205304</v>
+      </c>
+      <c r="CJ67">
+        <v>5818059</v>
+      </c>
+      <c r="CK67">
+        <v>3751791</v>
+      </c>
+      <c r="CL67">
+        <v>3631143</v>
+      </c>
+      <c r="CM67">
+        <v>5854961</v>
+      </c>
+      <c r="CN67">
+        <v>7084055</v>
+      </c>
+      <c r="CO67">
+        <v>7690043</v>
+      </c>
+      <c r="CP67">
+        <v>7890502</v>
+      </c>
+      <c r="CQ67">
+        <v>8056424</v>
+      </c>
+      <c r="CR67">
+        <v>8063986</v>
+      </c>
+      <c r="CS67">
+        <v>8149205</v>
+      </c>
+      <c r="CT67">
+        <v>7926955</v>
+      </c>
+      <c r="CU67">
+        <v>7335201</v>
+      </c>
+      <c r="CV67">
+        <v>6681517</v>
+      </c>
+      <c r="CW67">
+        <v>7185099</v>
+      </c>
+      <c r="CX67">
+        <v>7467077</v>
+      </c>
+      <c r="CY67">
+        <v>7927536</v>
+      </c>
+      <c r="CZ67">
+        <v>7517322</v>
+      </c>
+      <c r="DA67">
+        <v>6336847</v>
+      </c>
+      <c r="DB67">
+        <v>4896355</v>
+      </c>
+      <c r="DC67">
+        <v>2896229</v>
+      </c>
+      <c r="DD67">
+        <v>2255104</v>
+      </c>
+      <c r="DE67">
+        <v>6135172</v>
       </c>
     </row>
   </sheetData>
@@ -59165,7 +59715,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:HI26"/>
+  <dimension ref="A1:HI27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:217" s="1" customFormat="1">
@@ -72886,652 +73436,652 @@
         <v>2020</v>
       </c>
       <c r="B22">
-        <v>168983</v>
+        <v>258951</v>
       </c>
       <c r="C22">
-        <v>161887</v>
+        <v>255806</v>
       </c>
       <c r="D22">
-        <v>156598</v>
+        <v>234272</v>
       </c>
       <c r="E22">
-        <v>163532</v>
+        <v>236021</v>
       </c>
       <c r="F22">
-        <v>152651</v>
+        <v>235753</v>
       </c>
       <c r="G22">
-        <v>144411</v>
+        <v>234001</v>
       </c>
       <c r="H22">
-        <v>132773</v>
+        <v>221496</v>
       </c>
       <c r="I22">
-        <v>125193</v>
+        <v>203018</v>
       </c>
       <c r="J22">
-        <v>170023</v>
+        <v>242432</v>
       </c>
       <c r="K22">
-        <v>119668</v>
+        <v>185266</v>
       </c>
       <c r="L22">
-        <v>121906</v>
+        <v>172674</v>
       </c>
       <c r="M22">
-        <v>108686</v>
+        <v>146430</v>
       </c>
       <c r="N22">
-        <v>83576</v>
+        <v>109111</v>
       </c>
       <c r="O22">
-        <v>60405</v>
+        <v>75496</v>
       </c>
       <c r="P22">
-        <v>37632</v>
+        <v>46967</v>
       </c>
       <c r="Q22">
-        <v>23763</v>
+        <v>29371</v>
       </c>
       <c r="R22">
-        <v>21478</v>
+        <v>26320</v>
       </c>
       <c r="S22">
-        <v>171207</v>
+        <v>220610</v>
       </c>
       <c r="T22">
-        <v>176527</v>
+        <v>269659</v>
       </c>
       <c r="U22">
-        <v>168009</v>
+        <v>271315</v>
       </c>
       <c r="V22">
-        <v>160559</v>
+        <v>255813</v>
       </c>
       <c r="W22">
-        <v>169461</v>
+        <v>254994</v>
       </c>
       <c r="X22">
-        <v>166696</v>
+        <v>252051</v>
       </c>
       <c r="Y22">
-        <v>156391</v>
+        <v>245768</v>
       </c>
       <c r="Z22">
-        <v>142288</v>
+        <v>229518</v>
       </c>
       <c r="AA22">
-        <v>131604</v>
+        <v>207707</v>
       </c>
       <c r="AB22">
-        <v>176110</v>
+        <v>251659</v>
       </c>
       <c r="AC22">
-        <v>124310</v>
+        <v>188472</v>
       </c>
       <c r="AD22">
-        <v>120138</v>
+        <v>170211</v>
       </c>
       <c r="AE22">
-        <v>102343</v>
+        <v>138605</v>
       </c>
       <c r="AF22">
-        <v>75349</v>
+        <v>98483</v>
       </c>
       <c r="AG22">
-        <v>54068</v>
+        <v>65673</v>
       </c>
       <c r="AH22">
-        <v>31570</v>
+        <v>37270</v>
       </c>
       <c r="AI22">
-        <v>18169</v>
+        <v>20904</v>
       </c>
       <c r="AJ22">
-        <v>13084</v>
+        <v>15341</v>
       </c>
       <c r="AK22">
-        <v>178517</v>
+        <v>228779</v>
       </c>
       <c r="AL22">
-        <v>572055</v>
+        <v>598655</v>
       </c>
       <c r="AM22">
-        <v>596090</v>
+        <v>651096</v>
       </c>
       <c r="AN22">
-        <v>635625</v>
+        <v>750995</v>
       </c>
       <c r="AO22">
-        <v>782166</v>
+        <v>818605</v>
       </c>
       <c r="AP22">
-        <v>893738</v>
+        <v>899150</v>
       </c>
       <c r="AQ22">
-        <v>889007</v>
+        <v>892482</v>
       </c>
       <c r="AR22">
-        <v>813706</v>
+        <v>819053</v>
       </c>
       <c r="AS22">
-        <v>783730</v>
+        <v>809384</v>
       </c>
       <c r="AT22">
-        <v>589291</v>
+        <v>591284</v>
       </c>
       <c r="AU22">
-        <v>686393</v>
+        <v>721187</v>
       </c>
       <c r="AV22">
-        <v>628103</v>
+        <v>650165</v>
       </c>
       <c r="AW22">
-        <v>573566</v>
+        <v>592021</v>
       </c>
       <c r="AX22">
-        <v>496030</v>
+        <v>503546</v>
       </c>
       <c r="AY22">
-        <v>391246</v>
+        <v>393898</v>
       </c>
       <c r="AZ22">
-        <v>246703</v>
+        <v>247388</v>
       </c>
       <c r="BA22">
-        <v>164313</v>
+        <v>162892</v>
       </c>
       <c r="BB22">
-        <v>176216</v>
+        <v>166860</v>
       </c>
       <c r="BC22">
-        <v>566463</v>
+        <v>558806</v>
       </c>
       <c r="BD22">
-        <v>597873</v>
+        <v>622989</v>
       </c>
       <c r="BE22">
-        <v>601953</v>
+        <v>654592</v>
       </c>
       <c r="BF22">
-        <v>639448</v>
+        <v>759120</v>
       </c>
       <c r="BG22">
-        <v>764648</v>
+        <v>805470</v>
       </c>
       <c r="BH22">
-        <v>840630</v>
+        <v>821793</v>
       </c>
       <c r="BI22">
-        <v>816431</v>
+        <v>787681</v>
       </c>
       <c r="BJ22">
-        <v>721358</v>
+        <v>701430</v>
       </c>
       <c r="BK22">
-        <v>703556</v>
+        <v>698075</v>
       </c>
       <c r="BL22">
-        <v>624343</v>
+        <v>623019</v>
       </c>
       <c r="BM22">
-        <v>611597</v>
+        <v>618867</v>
       </c>
       <c r="BN22">
-        <v>550811</v>
+        <v>554915</v>
       </c>
       <c r="BO22">
-        <v>484700</v>
+        <v>486261</v>
       </c>
       <c r="BP22">
-        <v>397896</v>
+        <v>399986</v>
       </c>
       <c r="BQ22">
-        <v>309468</v>
+        <v>304938</v>
       </c>
       <c r="BR22">
-        <v>195775</v>
+        <v>192768</v>
       </c>
       <c r="BS22">
-        <v>126788</v>
+        <v>123961</v>
       </c>
       <c r="BT22">
-        <v>106296</v>
+        <v>97997</v>
       </c>
       <c r="BU22">
-        <v>602706</v>
+        <v>587934</v>
       </c>
       <c r="BV22">
-        <v>1623626</v>
+        <v>1611371</v>
       </c>
       <c r="BW22">
-        <v>1572382</v>
+        <v>1619412</v>
       </c>
       <c r="BX22">
-        <v>1602524</v>
+        <v>1637919</v>
       </c>
       <c r="BY22">
-        <v>1791749</v>
+        <v>1680846</v>
       </c>
       <c r="BZ22">
-        <v>1726634</v>
+        <v>1675685</v>
       </c>
       <c r="CA22">
-        <v>1581726</v>
+        <v>1571357</v>
       </c>
       <c r="CB22">
-        <v>1494207</v>
+        <v>1474043</v>
       </c>
       <c r="CC22">
-        <v>1443293</v>
+        <v>1416084</v>
       </c>
       <c r="CD22">
-        <v>1539983</v>
+        <v>1521668</v>
       </c>
       <c r="CE22">
-        <v>1432604</v>
+        <v>1424639</v>
       </c>
       <c r="CF22">
-        <v>1478806</v>
+        <v>1479614</v>
       </c>
       <c r="CG22">
-        <v>1362923</v>
+        <v>1377675</v>
       </c>
       <c r="CH22">
-        <v>1098096</v>
+        <v>1116825</v>
       </c>
       <c r="CI22">
-        <v>813232</v>
+        <v>819030</v>
       </c>
       <c r="CJ22">
-        <v>517957</v>
+        <v>520034</v>
       </c>
       <c r="CK22">
-        <v>341411</v>
+        <v>338333</v>
       </c>
       <c r="CL22">
-        <v>339782</v>
+        <v>341153</v>
       </c>
       <c r="CM22">
-        <v>1495727</v>
+        <v>1482812</v>
       </c>
       <c r="CN22">
-        <v>1676381</v>
+        <v>1669902</v>
       </c>
       <c r="CO22">
-        <v>1604820</v>
+        <v>1663777</v>
       </c>
       <c r="CP22">
-        <v>1597646</v>
+        <v>1612695</v>
       </c>
       <c r="CQ22">
-        <v>1783313</v>
+        <v>1582108</v>
       </c>
       <c r="CR22">
-        <v>1654999</v>
+        <v>1520300</v>
       </c>
       <c r="CS22">
-        <v>1466889</v>
+        <v>1401191</v>
       </c>
       <c r="CT22">
-        <v>1349423</v>
+        <v>1306689</v>
       </c>
       <c r="CU22">
-        <v>1289609</v>
+        <v>1256168</v>
       </c>
       <c r="CV22">
-        <v>1585782</v>
+        <v>1567854</v>
       </c>
       <c r="CW22">
-        <v>1286720</v>
+        <v>1259726</v>
       </c>
       <c r="CX22">
-        <v>1303736</v>
+        <v>1285247</v>
       </c>
       <c r="CY22">
-        <v>1162373</v>
+        <v>1162024</v>
       </c>
       <c r="CZ22">
-        <v>865802</v>
+        <v>887661</v>
       </c>
       <c r="DA22">
-        <v>600789</v>
+        <v>608612</v>
       </c>
       <c r="DB22">
-        <v>348458</v>
+        <v>351481</v>
       </c>
       <c r="DC22">
-        <v>203554</v>
+        <v>202217</v>
       </c>
       <c r="DD22">
-        <v>149722</v>
+        <v>152411</v>
       </c>
       <c r="DE22">
-        <v>1534848</v>
+        <v>1522684</v>
       </c>
       <c r="DF22">
-        <v>32147</v>
+        <v>34542</v>
       </c>
       <c r="DG22">
-        <v>29969</v>
+        <v>34886</v>
       </c>
       <c r="DH22">
-        <v>28335</v>
+        <v>36086</v>
       </c>
       <c r="DI22">
-        <v>32543</v>
+        <v>35535</v>
       </c>
       <c r="DJ22">
-        <v>34383</v>
+        <v>34183</v>
       </c>
       <c r="DK22">
-        <v>32944</v>
+        <v>32099</v>
       </c>
       <c r="DL22">
-        <v>28939</v>
+        <v>28644</v>
       </c>
       <c r="DM22">
-        <v>24954</v>
+        <v>25226</v>
       </c>
       <c r="DN22">
-        <v>33519</v>
+        <v>34844</v>
       </c>
       <c r="DO22">
-        <v>23767</v>
+        <v>23662</v>
       </c>
       <c r="DP22">
-        <v>22625</v>
+        <v>22289</v>
       </c>
       <c r="DQ22">
-        <v>18848</v>
+        <v>18373</v>
       </c>
       <c r="DR22">
-        <v>14665</v>
+        <v>14090</v>
       </c>
       <c r="DS22">
-        <v>10733</v>
+        <v>9620</v>
       </c>
       <c r="DT22">
-        <v>6512</v>
+        <v>6010</v>
       </c>
       <c r="DU22">
-        <v>4244</v>
+        <v>3692</v>
       </c>
       <c r="DV22">
-        <v>3918</v>
+        <v>3641</v>
       </c>
       <c r="DW22">
-        <v>34644</v>
+        <v>33290</v>
       </c>
       <c r="DX22">
-        <v>32996</v>
+        <v>36189</v>
       </c>
       <c r="DY22">
-        <v>30818</v>
+        <v>36156</v>
       </c>
       <c r="DZ22">
-        <v>29283</v>
+        <v>37430</v>
       </c>
       <c r="EA22">
-        <v>33150</v>
+        <v>36477</v>
       </c>
       <c r="EB22">
-        <v>37594</v>
+        <v>34907</v>
       </c>
       <c r="EC22">
-        <v>36458</v>
+        <v>32051</v>
       </c>
       <c r="ED22">
-        <v>31096</v>
+        <v>28392</v>
       </c>
       <c r="EE22">
-        <v>26517</v>
+        <v>24658</v>
       </c>
       <c r="EF22">
-        <v>34953</v>
+        <v>36538</v>
       </c>
       <c r="EG22">
-        <v>24070</v>
+        <v>22745</v>
       </c>
       <c r="EH22">
-        <v>22177</v>
+        <v>20571</v>
       </c>
       <c r="EI22">
-        <v>18561</v>
+        <v>16915</v>
       </c>
       <c r="EJ22">
-        <v>13360</v>
+        <v>12281</v>
       </c>
       <c r="EK22">
-        <v>10089</v>
+        <v>8578</v>
       </c>
       <c r="EL22">
-        <v>5726</v>
+        <v>4847</v>
       </c>
       <c r="EM22">
-        <v>3295</v>
+        <v>2589</v>
       </c>
       <c r="EN22">
-        <v>2594</v>
+        <v>2079</v>
       </c>
       <c r="EO22">
-        <v>36540</v>
+        <v>35367</v>
       </c>
       <c r="EP22">
-        <v>581203</v>
+        <v>815520</v>
       </c>
       <c r="EQ22">
-        <v>486994</v>
+        <v>715818</v>
       </c>
       <c r="ER22">
-        <v>421744</v>
+        <v>602552</v>
       </c>
       <c r="ES22">
-        <v>374844</v>
+        <v>550998</v>
       </c>
       <c r="ET22">
-        <v>307090</v>
+        <v>503069</v>
       </c>
       <c r="EU22">
-        <v>264925</v>
+        <v>450472</v>
       </c>
       <c r="EV22">
-        <v>227922</v>
+        <v>395418</v>
       </c>
       <c r="EW22">
-        <v>190504</v>
+        <v>352944</v>
       </c>
       <c r="EX22">
-        <v>602486</v>
+        <v>823623</v>
       </c>
       <c r="EY22">
-        <v>165161</v>
+        <v>324828</v>
       </c>
       <c r="EZ22">
-        <v>156209</v>
+        <v>311058</v>
       </c>
       <c r="FA22">
-        <v>136083</v>
+        <v>267963</v>
       </c>
       <c r="FB22">
-        <v>104126</v>
+        <v>200938</v>
       </c>
       <c r="FC22">
-        <v>76911</v>
+        <v>144924</v>
       </c>
       <c r="FD22">
-        <v>49530</v>
+        <v>87226</v>
       </c>
       <c r="FE22">
-        <v>31168</v>
+        <v>51650</v>
       </c>
       <c r="FF22">
-        <v>31243</v>
+        <v>46414</v>
       </c>
       <c r="FG22">
-        <v>604782</v>
+        <v>862256</v>
       </c>
       <c r="FH22">
-        <v>604727</v>
+        <v>840680</v>
       </c>
       <c r="FI22">
-        <v>500270</v>
+        <v>730605</v>
       </c>
       <c r="FJ22">
-        <v>424718</v>
+        <v>587624</v>
       </c>
       <c r="FK22">
-        <v>366911</v>
+        <v>513535</v>
       </c>
       <c r="FL22">
-        <v>286301</v>
+        <v>455110</v>
       </c>
       <c r="FM22">
-        <v>242381</v>
+        <v>402034</v>
       </c>
       <c r="FN22">
-        <v>207269</v>
+        <v>351094</v>
       </c>
       <c r="FO22">
-        <v>172401</v>
+        <v>313670</v>
       </c>
       <c r="FP22">
-        <v>631026</v>
+        <v>854751</v>
       </c>
       <c r="FQ22">
-        <v>151512</v>
+        <v>284320</v>
       </c>
       <c r="FR22">
-        <v>140970</v>
+        <v>266264</v>
       </c>
       <c r="FS22">
-        <v>122872</v>
+        <v>226240</v>
       </c>
       <c r="FT22">
-        <v>91567</v>
+        <v>163749</v>
       </c>
       <c r="FU22">
-        <v>65598</v>
+        <v>113397</v>
       </c>
       <c r="FV22">
-        <v>39632</v>
+        <v>64783</v>
       </c>
       <c r="FW22">
-        <v>23495</v>
+        <v>35983</v>
       </c>
       <c r="FX22">
-        <v>18478</v>
+        <v>26203</v>
       </c>
       <c r="FY22">
-        <v>632798</v>
+        <v>899143</v>
       </c>
       <c r="FZ22">
-        <v>7608532</v>
+        <v>7180842</v>
       </c>
       <c r="GA22">
-        <v>7673356</v>
+        <v>7462719</v>
       </c>
       <c r="GB22">
-        <v>7622404</v>
+        <v>7605004</v>
       </c>
       <c r="GC22">
-        <v>8033246</v>
+        <v>7657754</v>
       </c>
       <c r="GD22">
-        <v>8160272</v>
+        <v>7894093</v>
       </c>
       <c r="GE22">
-        <v>8073360</v>
+        <v>7796461</v>
       </c>
       <c r="GF22">
-        <v>7595580</v>
+        <v>7334016</v>
       </c>
       <c r="GG22">
-        <v>7589407</v>
+        <v>7341533</v>
       </c>
       <c r="GH22">
-        <v>6999605</v>
+        <v>6604685</v>
       </c>
       <c r="GI22">
-        <v>7981424</v>
+        <v>7812472</v>
       </c>
       <c r="GJ22">
-        <v>8766199</v>
+        <v>8664112</v>
       </c>
       <c r="GK22">
-        <v>8601794</v>
+        <v>8636571</v>
       </c>
       <c r="GL22">
-        <v>7646132</v>
+        <v>7739444</v>
       </c>
       <c r="GM22">
-        <v>6414135</v>
+        <v>6543336</v>
       </c>
       <c r="GN22">
-        <v>4443861</v>
+        <v>4596310</v>
       </c>
       <c r="GO22">
-        <v>2965525</v>
+        <v>3081096</v>
       </c>
       <c r="GP22">
-        <v>3314758</v>
+        <v>3447683</v>
       </c>
       <c r="GQ22">
-        <v>6558095</v>
+        <v>6200604</v>
       </c>
       <c r="GR22">
-        <v>8022075</v>
+        <v>7559123</v>
       </c>
       <c r="GS22">
-        <v>8039914</v>
+        <v>7793163</v>
       </c>
       <c r="GT22">
-        <v>7811627</v>
+        <v>7741941</v>
       </c>
       <c r="GU22">
-        <v>8252448</v>
+        <v>7798267</v>
       </c>
       <c r="GV22">
-        <v>8439355</v>
+        <v>7999132</v>
       </c>
       <c r="GW22">
-        <v>8394210</v>
+        <v>7858737</v>
       </c>
       <c r="GX22">
-        <v>7859397</v>
+        <v>7355069</v>
       </c>
       <c r="GY22">
-        <v>7810312</v>
+        <v>7319852</v>
       </c>
       <c r="GZ22">
-        <v>7360660</v>
+        <v>6936439</v>
       </c>
       <c r="HA22">
-        <v>8163657</v>
+        <v>7735333</v>
       </c>
       <c r="HB22">
-        <v>8715485</v>
+        <v>8397258</v>
       </c>
       <c r="HC22">
-        <v>8333984</v>
+        <v>8165156</v>
       </c>
       <c r="HD22">
-        <v>7109917</v>
+        <v>7094256</v>
       </c>
       <c r="HE22">
-        <v>5767338</v>
+        <v>5813002</v>
       </c>
       <c r="HF22">
-        <v>3737490</v>
+        <v>3842861</v>
       </c>
       <c r="HG22">
-        <v>2254607</v>
+        <v>2338618</v>
       </c>
       <c r="HH22">
-        <v>1890296</v>
+        <v>1991780</v>
       </c>
       <c r="HI22">
-        <v>6877962</v>
+        <v>6501642</v>
       </c>
     </row>
     <row r="23" spans="1:217">
@@ -73539,652 +74089,652 @@
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>168812</v>
+        <v>256803</v>
       </c>
       <c r="C23">
-        <v>164130</v>
+        <v>257834</v>
       </c>
       <c r="D23">
-        <v>158026</v>
+        <v>239784</v>
       </c>
       <c r="E23">
-        <v>161443</v>
+        <v>233060</v>
       </c>
       <c r="F23">
-        <v>156370</v>
+        <v>237573</v>
       </c>
       <c r="G23">
-        <v>145266</v>
+        <v>234015</v>
       </c>
       <c r="H23">
-        <v>135880</v>
+        <v>225936</v>
       </c>
       <c r="I23">
-        <v>124022</v>
+        <v>203971</v>
       </c>
       <c r="J23">
-        <v>171003</v>
+        <v>239846</v>
       </c>
       <c r="K23">
-        <v>121109</v>
+        <v>189073</v>
       </c>
       <c r="L23">
-        <v>120848</v>
+        <v>175006</v>
       </c>
       <c r="M23">
-        <v>111332</v>
+        <v>151736</v>
       </c>
       <c r="N23">
-        <v>87740</v>
+        <v>115189</v>
       </c>
       <c r="O23">
-        <v>64787</v>
+        <v>81501</v>
       </c>
       <c r="P23">
-        <v>39774</v>
+        <v>50104</v>
       </c>
       <c r="Q23">
-        <v>25039</v>
+        <v>31223</v>
       </c>
       <c r="R23">
-        <v>23034</v>
+        <v>28267</v>
       </c>
       <c r="S23">
-        <v>169618</v>
+        <v>213196</v>
       </c>
       <c r="T23">
-        <v>176180</v>
+        <v>267174</v>
       </c>
       <c r="U23">
-        <v>170414</v>
+        <v>271347</v>
       </c>
       <c r="V23">
-        <v>161812</v>
+        <v>260236</v>
       </c>
       <c r="W23">
-        <v>166173</v>
+        <v>252671</v>
       </c>
       <c r="X23">
-        <v>169575</v>
+        <v>254100</v>
       </c>
       <c r="Y23">
-        <v>157783</v>
+        <v>246404</v>
       </c>
       <c r="Z23">
-        <v>145283</v>
+        <v>234016</v>
       </c>
       <c r="AA23">
-        <v>130851</v>
+        <v>209268</v>
       </c>
       <c r="AB23">
-        <v>177162</v>
+        <v>249090</v>
       </c>
       <c r="AC23">
-        <v>125781</v>
+        <v>192026</v>
       </c>
       <c r="AD23">
-        <v>120031</v>
+        <v>173065</v>
       </c>
       <c r="AE23">
-        <v>105007</v>
+        <v>143464</v>
       </c>
       <c r="AF23">
-        <v>78994</v>
+        <v>104450</v>
       </c>
       <c r="AG23">
-        <v>57524</v>
+        <v>70888</v>
       </c>
       <c r="AH23">
-        <v>33282</v>
+        <v>39717</v>
       </c>
       <c r="AI23">
-        <v>19360</v>
+        <v>22429</v>
       </c>
       <c r="AJ23">
-        <v>14262</v>
+        <v>16490</v>
       </c>
       <c r="AK23">
-        <v>176868</v>
+        <v>221310</v>
       </c>
       <c r="AL23">
-        <v>573821</v>
+        <v>599074</v>
       </c>
       <c r="AM23">
-        <v>593013</v>
+        <v>626382</v>
       </c>
       <c r="AN23">
-        <v>631653</v>
+        <v>757890</v>
       </c>
       <c r="AO23">
-        <v>760277</v>
+        <v>809544</v>
       </c>
       <c r="AP23">
-        <v>898686</v>
+        <v>905588</v>
       </c>
       <c r="AQ23">
-        <v>899945</v>
+        <v>903454</v>
       </c>
       <c r="AR23">
-        <v>830240</v>
+        <v>835644</v>
       </c>
       <c r="AS23">
-        <v>790220</v>
+        <v>810402</v>
       </c>
       <c r="AT23">
-        <v>598036</v>
+        <v>593525</v>
       </c>
       <c r="AU23">
-        <v>711842</v>
+        <v>747490</v>
       </c>
       <c r="AV23">
-        <v>638299</v>
+        <v>663552</v>
       </c>
       <c r="AW23">
-        <v>580379</v>
+        <v>597702</v>
       </c>
       <c r="AX23">
-        <v>513631</v>
+        <v>524474</v>
       </c>
       <c r="AY23">
-        <v>416258</v>
+        <v>418538</v>
       </c>
       <c r="AZ23">
-        <v>261108</v>
+        <v>262237</v>
       </c>
       <c r="BA23">
-        <v>172798</v>
+        <v>171719</v>
       </c>
       <c r="BB23">
-        <v>185188</v>
+        <v>175968</v>
       </c>
       <c r="BC23">
-        <v>550976</v>
+        <v>548543</v>
       </c>
       <c r="BD23">
-        <v>602758</v>
+        <v>626163</v>
       </c>
       <c r="BE23">
-        <v>600560</v>
+        <v>633584</v>
       </c>
       <c r="BF23">
-        <v>635089</v>
+        <v>761315</v>
       </c>
       <c r="BG23">
-        <v>747424</v>
+        <v>804814</v>
       </c>
       <c r="BH23">
-        <v>847485</v>
+        <v>834965</v>
       </c>
       <c r="BI23">
-        <v>833084</v>
+        <v>803963</v>
       </c>
       <c r="BJ23">
-        <v>737403</v>
+        <v>716026</v>
       </c>
       <c r="BK23">
-        <v>706804</v>
+        <v>698110</v>
       </c>
       <c r="BL23">
-        <v>633656</v>
+        <v>624743</v>
       </c>
       <c r="BM23">
-        <v>634533</v>
+        <v>639939</v>
       </c>
       <c r="BN23">
-        <v>561707</v>
+        <v>567814</v>
       </c>
       <c r="BO23">
-        <v>491575</v>
+        <v>492167</v>
       </c>
       <c r="BP23">
-        <v>414805</v>
+        <v>416908</v>
       </c>
       <c r="BQ23">
-        <v>325090</v>
+        <v>321309</v>
       </c>
       <c r="BR23">
-        <v>205720</v>
+        <v>202688</v>
       </c>
       <c r="BS23">
-        <v>132875</v>
+        <v>130103</v>
       </c>
       <c r="BT23">
-        <v>113536</v>
+        <v>104909</v>
       </c>
       <c r="BU23">
-        <v>585903</v>
+        <v>578241</v>
       </c>
       <c r="BV23">
-        <v>1611447</v>
+        <v>1604031</v>
       </c>
       <c r="BW23">
-        <v>1574279</v>
+        <v>1584574</v>
       </c>
       <c r="BX23">
-        <v>1604252</v>
+        <v>1682543</v>
       </c>
       <c r="BY23">
-        <v>1737417</v>
+        <v>1640723</v>
       </c>
       <c r="BZ23">
-        <v>1779878</v>
+        <v>1705324</v>
       </c>
       <c r="CA23">
-        <v>1591000</v>
+        <v>1581120</v>
       </c>
       <c r="CB23">
-        <v>1526230</v>
+        <v>1508357</v>
       </c>
       <c r="CC23">
-        <v>1411143</v>
+        <v>1384867</v>
       </c>
       <c r="CD23">
-        <v>1539083</v>
+        <v>1516578</v>
       </c>
       <c r="CE23">
-        <v>1440086</v>
+        <v>1426333</v>
       </c>
       <c r="CF23">
-        <v>1465890</v>
+        <v>1466581</v>
       </c>
       <c r="CG23">
-        <v>1379872</v>
+        <v>1391844</v>
       </c>
       <c r="CH23">
-        <v>1129999</v>
+        <v>1148626</v>
       </c>
       <c r="CI23">
-        <v>866544</v>
+        <v>875123</v>
       </c>
       <c r="CJ23">
-        <v>531821</v>
+        <v>534775</v>
       </c>
       <c r="CK23">
-        <v>348507</v>
+        <v>347406</v>
       </c>
       <c r="CL23">
-        <v>342065</v>
+        <v>341725</v>
       </c>
       <c r="CM23">
-        <v>1483827</v>
+        <v>1473677</v>
       </c>
       <c r="CN23">
-        <v>1667055</v>
+        <v>1661813</v>
       </c>
       <c r="CO23">
-        <v>1606607</v>
+        <v>1634465</v>
       </c>
       <c r="CP23">
-        <v>1599593</v>
+        <v>1659879</v>
       </c>
       <c r="CQ23">
-        <v>1729638</v>
+        <v>1558318</v>
       </c>
       <c r="CR23">
-        <v>1715925</v>
+        <v>1551734</v>
       </c>
       <c r="CS23">
-        <v>1481558</v>
+        <v>1409994</v>
       </c>
       <c r="CT23">
-        <v>1382214</v>
+        <v>1335929</v>
       </c>
       <c r="CU23">
-        <v>1257526</v>
+        <v>1224520</v>
       </c>
       <c r="CV23">
-        <v>1580136</v>
+        <v>1559775</v>
       </c>
       <c r="CW23">
-        <v>1289000</v>
+        <v>1258066</v>
       </c>
       <c r="CX23">
-        <v>1289382</v>
+        <v>1269639</v>
       </c>
       <c r="CY23">
-        <v>1176773</v>
+        <v>1171459</v>
       </c>
       <c r="CZ23">
-        <v>894264</v>
+        <v>914206</v>
       </c>
       <c r="DA23">
-        <v>635718</v>
+        <v>646483</v>
       </c>
       <c r="DB23">
-        <v>356967</v>
+        <v>361447</v>
       </c>
       <c r="DC23">
-        <v>206791</v>
+        <v>206849</v>
       </c>
       <c r="DD23">
-        <v>153628</v>
+        <v>155205</v>
       </c>
       <c r="DE23">
-        <v>1525554</v>
+        <v>1515040</v>
       </c>
       <c r="DF23">
-        <v>32334</v>
+        <v>34963</v>
       </c>
       <c r="DG23">
-        <v>30546</v>
+        <v>34074</v>
       </c>
       <c r="DH23">
-        <v>28475</v>
+        <v>37051</v>
       </c>
       <c r="DI23">
-        <v>31613</v>
+        <v>35341</v>
       </c>
       <c r="DJ23">
-        <v>34651</v>
+        <v>34900</v>
       </c>
       <c r="DK23">
-        <v>33632</v>
+        <v>32667</v>
       </c>
       <c r="DL23">
-        <v>29894</v>
+        <v>29508</v>
       </c>
       <c r="DM23">
-        <v>25276</v>
+        <v>25553</v>
       </c>
       <c r="DN23">
-        <v>34338</v>
+        <v>34820</v>
       </c>
       <c r="DO23">
-        <v>24197</v>
+        <v>24050</v>
       </c>
       <c r="DP23">
-        <v>22907</v>
+        <v>22672</v>
       </c>
       <c r="DQ23">
-        <v>19575</v>
+        <v>19200</v>
       </c>
       <c r="DR23">
-        <v>15509</v>
+        <v>14842</v>
       </c>
       <c r="DS23">
-        <v>11407</v>
+        <v>10390</v>
       </c>
       <c r="DT23">
-        <v>7083</v>
+        <v>6533</v>
       </c>
       <c r="DU23">
-        <v>4433</v>
+        <v>3913</v>
       </c>
       <c r="DV23">
-        <v>4155</v>
+        <v>3793</v>
       </c>
       <c r="DW23">
-        <v>34085</v>
+        <v>32356</v>
       </c>
       <c r="DX23">
-        <v>33270</v>
+        <v>36436</v>
       </c>
       <c r="DY23">
-        <v>31508</v>
+        <v>35670</v>
       </c>
       <c r="DZ23">
-        <v>29151</v>
+        <v>37988</v>
       </c>
       <c r="EA23">
-        <v>31902</v>
+        <v>36332</v>
       </c>
       <c r="EB23">
-        <v>37526</v>
+        <v>35604</v>
       </c>
       <c r="EC23">
-        <v>36941</v>
+        <v>32722</v>
       </c>
       <c r="ED23">
-        <v>32671</v>
+        <v>29420</v>
       </c>
       <c r="EE23">
-        <v>26816</v>
+        <v>24769</v>
       </c>
       <c r="EF23">
-        <v>35690</v>
+        <v>36520</v>
       </c>
       <c r="EG23">
-        <v>24622</v>
+        <v>23305</v>
       </c>
       <c r="EH23">
-        <v>22458</v>
+        <v>20943</v>
       </c>
       <c r="EI23">
-        <v>19371</v>
+        <v>17728</v>
       </c>
       <c r="EJ23">
-        <v>14123</v>
+        <v>13017</v>
       </c>
       <c r="EK23">
-        <v>10508</v>
+        <v>9105</v>
       </c>
       <c r="EL23">
-        <v>6262</v>
+        <v>5239</v>
       </c>
       <c r="EM23">
-        <v>3522</v>
+        <v>2884</v>
       </c>
       <c r="EN23">
-        <v>2775</v>
+        <v>2149</v>
       </c>
       <c r="EO23">
-        <v>36166</v>
+        <v>34560</v>
       </c>
       <c r="EP23">
-        <v>590857</v>
+        <v>820334</v>
       </c>
       <c r="EQ23">
-        <v>504148</v>
+        <v>737651</v>
       </c>
       <c r="ER23">
-        <v>434195</v>
+        <v>624771</v>
       </c>
       <c r="ES23">
-        <v>383224</v>
+        <v>555448</v>
       </c>
       <c r="ET23">
-        <v>323137</v>
+        <v>517345</v>
       </c>
       <c r="EU23">
-        <v>269889</v>
+        <v>458164</v>
       </c>
       <c r="EV23">
-        <v>237828</v>
+        <v>409759</v>
       </c>
       <c r="EW23">
-        <v>192752</v>
+        <v>352042</v>
       </c>
       <c r="EX23">
-        <v>608517</v>
+        <v>834229</v>
       </c>
       <c r="EY23">
-        <v>171966</v>
+        <v>334634</v>
       </c>
       <c r="EZ23">
-        <v>156343</v>
+        <v>312068</v>
       </c>
       <c r="FA23">
-        <v>140112</v>
+        <v>278011</v>
       </c>
       <c r="FB23">
-        <v>109985</v>
+        <v>213022</v>
       </c>
       <c r="FC23">
-        <v>82078</v>
+        <v>156707</v>
       </c>
       <c r="FD23">
-        <v>52234</v>
+        <v>93155</v>
       </c>
       <c r="FE23">
-        <v>33070</v>
+        <v>56093</v>
       </c>
       <c r="FF23">
-        <v>33099</v>
+        <v>50648</v>
       </c>
       <c r="FG23">
-        <v>601055</v>
+        <v>863455</v>
       </c>
       <c r="FH23">
-        <v>616366</v>
+        <v>847282</v>
       </c>
       <c r="FI23">
-        <v>518590</v>
+        <v>754855</v>
       </c>
       <c r="FJ23">
-        <v>437842</v>
+        <v>614109</v>
       </c>
       <c r="FK23">
-        <v>379554</v>
+        <v>522795</v>
       </c>
       <c r="FL23">
-        <v>302292</v>
+        <v>468047</v>
       </c>
       <c r="FM23">
-        <v>247562</v>
+        <v>410336</v>
       </c>
       <c r="FN23">
-        <v>215974</v>
+        <v>362878</v>
       </c>
       <c r="FO23">
-        <v>174709</v>
+        <v>313357</v>
       </c>
       <c r="FP23">
-        <v>635932</v>
+        <v>866618</v>
       </c>
       <c r="FQ23">
-        <v>157330</v>
+        <v>293879</v>
       </c>
       <c r="FR23">
-        <v>140533</v>
+        <v>267173</v>
       </c>
       <c r="FS23">
-        <v>126584</v>
+        <v>234709</v>
       </c>
       <c r="FT23">
-        <v>96606</v>
+        <v>174241</v>
       </c>
       <c r="FU23">
-        <v>70110</v>
+        <v>122836</v>
       </c>
       <c r="FV23">
-        <v>41990</v>
+        <v>69671</v>
       </c>
       <c r="FW23">
-        <v>24939</v>
+        <v>38938</v>
       </c>
       <c r="FX23">
-        <v>20085</v>
+        <v>29167</v>
       </c>
       <c r="FY23">
-        <v>628379</v>
+        <v>899770</v>
       </c>
       <c r="FZ23">
-        <v>7491695</v>
+        <v>7077664</v>
       </c>
       <c r="GA23">
-        <v>7671093</v>
+        <v>7327193</v>
       </c>
       <c r="GB23">
-        <v>7644967</v>
+        <v>7732992</v>
       </c>
       <c r="GC23">
-        <v>7900700</v>
+        <v>7539071</v>
       </c>
       <c r="GD23">
-        <v>8212413</v>
+        <v>7917212</v>
       </c>
       <c r="GE23">
-        <v>8080945</v>
+        <v>7814331</v>
       </c>
       <c r="GF23">
-        <v>7745388</v>
+        <v>7478357</v>
       </c>
       <c r="GG23">
-        <v>7363109</v>
+        <v>7117642</v>
       </c>
       <c r="GH23">
-        <v>6973538</v>
+        <v>6568089</v>
       </c>
       <c r="GI23">
-        <v>8000939</v>
+        <v>7811099</v>
       </c>
       <c r="GJ23">
-        <v>8534068</v>
+        <v>8412815</v>
       </c>
       <c r="GK23">
-        <v>8665957</v>
+        <v>8675611</v>
       </c>
       <c r="GL23">
-        <v>7780808</v>
+        <v>7865745</v>
       </c>
       <c r="GM23">
-        <v>6706045</v>
+        <v>6832052</v>
       </c>
       <c r="GN23">
-        <v>4541992</v>
+        <v>4698333</v>
       </c>
       <c r="GO23">
-        <v>3029877</v>
+        <v>3154268</v>
       </c>
       <c r="GP23">
-        <v>3277910</v>
+        <v>3429420</v>
       </c>
       <c r="GQ23">
-        <v>6373721</v>
+        <v>6038914</v>
       </c>
       <c r="GR23">
-        <v>7902714</v>
+        <v>7445514</v>
       </c>
       <c r="GS23">
-        <v>8040389</v>
+        <v>7689989</v>
       </c>
       <c r="GT23">
-        <v>7831885</v>
+        <v>7844068</v>
       </c>
       <c r="GU23">
-        <v>8117877</v>
+        <v>7687047</v>
       </c>
       <c r="GV23">
-        <v>8458045</v>
+        <v>8020863</v>
       </c>
       <c r="GW23">
-        <v>8396599</v>
+        <v>7878179</v>
       </c>
       <c r="GX23">
-        <v>8022194</v>
+        <v>7501551</v>
       </c>
       <c r="GY23">
-        <v>7558584</v>
+        <v>7088221</v>
       </c>
       <c r="GZ23">
-        <v>7323207</v>
+        <v>6893275</v>
       </c>
       <c r="HA23">
-        <v>8195959</v>
+        <v>7732177</v>
       </c>
       <c r="HB23">
-        <v>8494299</v>
+        <v>8155780</v>
       </c>
       <c r="HC23">
-        <v>8404374</v>
+        <v>8197769</v>
       </c>
       <c r="HD23">
-        <v>7237355</v>
+        <v>7196203</v>
       </c>
       <c r="HE23">
-        <v>6004931</v>
+        <v>6045949</v>
       </c>
       <c r="HF23">
-        <v>3817568</v>
+        <v>3928650</v>
       </c>
       <c r="HG23">
-        <v>2301383</v>
+        <v>2390858</v>
       </c>
       <c r="HH23">
-        <v>1899313</v>
+        <v>2008983</v>
       </c>
       <c r="HI23">
-        <v>6686054</v>
+        <v>6334305</v>
       </c>
     </row>
     <row r="24" spans="1:217">
@@ -74192,652 +74742,652 @@
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>171055</v>
+        <v>255305</v>
       </c>
       <c r="C24">
-        <v>169829</v>
+        <v>263476</v>
       </c>
       <c r="D24">
-        <v>161673</v>
+        <v>248362</v>
       </c>
       <c r="E24">
-        <v>161571</v>
+        <v>233578</v>
       </c>
       <c r="F24">
-        <v>162760</v>
+        <v>241873</v>
       </c>
       <c r="G24">
-        <v>147474</v>
+        <v>234944</v>
       </c>
       <c r="H24">
-        <v>138766</v>
+        <v>229944</v>
       </c>
       <c r="I24">
-        <v>125049</v>
+        <v>207478</v>
       </c>
       <c r="J24">
-        <v>173246</v>
+        <v>239188</v>
       </c>
       <c r="K24">
-        <v>122265</v>
+        <v>193007</v>
       </c>
       <c r="L24">
-        <v>119236</v>
+        <v>176397</v>
       </c>
       <c r="M24">
-        <v>113662</v>
+        <v>156293</v>
       </c>
       <c r="N24">
-        <v>91943</v>
+        <v>122072</v>
       </c>
       <c r="O24">
-        <v>67292</v>
+        <v>85744</v>
       </c>
       <c r="P24">
-        <v>43965</v>
+        <v>55197</v>
       </c>
       <c r="Q24">
-        <v>26661</v>
+        <v>33502</v>
       </c>
       <c r="R24">
-        <v>24747</v>
+        <v>30575</v>
       </c>
       <c r="S24">
-        <v>170943</v>
+        <v>211799</v>
       </c>
       <c r="T24">
-        <v>178153</v>
+        <v>265313</v>
       </c>
       <c r="U24">
-        <v>177247</v>
+        <v>277373</v>
       </c>
       <c r="V24">
-        <v>166935</v>
+        <v>268574</v>
       </c>
       <c r="W24">
-        <v>166007</v>
+        <v>254878</v>
       </c>
       <c r="X24">
-        <v>175198</v>
+        <v>259326</v>
       </c>
       <c r="Y24">
-        <v>159961</v>
+        <v>247986</v>
       </c>
       <c r="Z24">
-        <v>149184</v>
+        <v>238616</v>
       </c>
       <c r="AA24">
-        <v>131933</v>
+        <v>212680</v>
       </c>
       <c r="AB24">
-        <v>179327</v>
+        <v>247980</v>
       </c>
       <c r="AC24">
-        <v>127250</v>
+        <v>195943</v>
       </c>
       <c r="AD24">
-        <v>118789</v>
+        <v>174822</v>
       </c>
       <c r="AE24">
-        <v>107057</v>
+        <v>147613</v>
       </c>
       <c r="AF24">
-        <v>83372</v>
+        <v>111436</v>
       </c>
       <c r="AG24">
-        <v>58769</v>
+        <v>74117</v>
       </c>
       <c r="AH24">
-        <v>37391</v>
+        <v>44629</v>
       </c>
       <c r="AI24">
-        <v>20813</v>
+        <v>24250</v>
       </c>
       <c r="AJ24">
-        <v>15675</v>
+        <v>18053</v>
       </c>
       <c r="AK24">
-        <v>178826</v>
+        <v>220614</v>
       </c>
       <c r="AL24">
-        <v>585817</v>
+        <v>606437</v>
       </c>
       <c r="AM24">
-        <v>610076</v>
+        <v>633850</v>
       </c>
       <c r="AN24">
-        <v>657678</v>
+        <v>776490</v>
       </c>
       <c r="AO24">
-        <v>780669</v>
+        <v>842557</v>
       </c>
       <c r="AP24">
-        <v>925650</v>
+        <v>934362</v>
       </c>
       <c r="AQ24">
-        <v>923453</v>
+        <v>924753</v>
       </c>
       <c r="AR24">
-        <v>863975</v>
+        <v>867251</v>
       </c>
       <c r="AS24">
-        <v>803465</v>
+        <v>815949</v>
       </c>
       <c r="AT24">
-        <v>615236</v>
+        <v>603228</v>
       </c>
       <c r="AU24">
-        <v>748352</v>
+        <v>783821</v>
       </c>
       <c r="AV24">
-        <v>651061</v>
+        <v>678324</v>
       </c>
       <c r="AW24">
-        <v>593748</v>
+        <v>608616</v>
       </c>
       <c r="AX24">
-        <v>533009</v>
+        <v>547491</v>
       </c>
       <c r="AY24">
-        <v>435937</v>
+        <v>438446</v>
       </c>
       <c r="AZ24">
-        <v>286026</v>
+        <v>286412</v>
       </c>
       <c r="BA24">
-        <v>184368</v>
+        <v>183469</v>
       </c>
       <c r="BB24">
-        <v>196291</v>
+        <v>187036</v>
       </c>
       <c r="BC24">
-        <v>551221</v>
+        <v>554212</v>
       </c>
       <c r="BD24">
-        <v>616004</v>
+        <v>635275</v>
       </c>
       <c r="BE24">
-        <v>622883</v>
+        <v>647083</v>
       </c>
       <c r="BF24">
-        <v>661522</v>
+        <v>778281</v>
       </c>
       <c r="BG24">
-        <v>760049</v>
+        <v>832496</v>
       </c>
       <c r="BH24">
-        <v>873750</v>
+        <v>870853</v>
       </c>
       <c r="BI24">
-        <v>859468</v>
+        <v>830760</v>
       </c>
       <c r="BJ24">
-        <v>774309</v>
+        <v>748199</v>
       </c>
       <c r="BK24">
-        <v>715165</v>
+        <v>702195</v>
       </c>
       <c r="BL24">
-        <v>652754</v>
+        <v>634826</v>
       </c>
       <c r="BM24">
-        <v>666090</v>
+        <v>669226</v>
       </c>
       <c r="BN24">
-        <v>571520</v>
+        <v>578362</v>
       </c>
       <c r="BO24">
-        <v>505612</v>
+        <v>504488</v>
       </c>
       <c r="BP24">
-        <v>432579</v>
+        <v>435211</v>
       </c>
       <c r="BQ24">
-        <v>338013</v>
+        <v>336000</v>
       </c>
       <c r="BR24">
-        <v>224568</v>
+        <v>219417</v>
       </c>
       <c r="BS24">
-        <v>140816</v>
+        <v>137839</v>
       </c>
       <c r="BT24">
-        <v>122690</v>
+        <v>113940</v>
       </c>
       <c r="BU24">
-        <v>584434</v>
+        <v>584509</v>
       </c>
       <c r="BV24">
-        <v>1595801</v>
+        <v>1589153</v>
       </c>
       <c r="BW24">
-        <v>1602211</v>
+        <v>1590576</v>
       </c>
       <c r="BX24">
-        <v>1610486</v>
+        <v>1709446</v>
       </c>
       <c r="BY24">
-        <v>1702090</v>
+        <v>1624414</v>
       </c>
       <c r="BZ24">
-        <v>1835047</v>
+        <v>1736590</v>
       </c>
       <c r="CA24">
-        <v>1611007</v>
+        <v>1598236</v>
       </c>
       <c r="CB24">
-        <v>1553583</v>
+        <v>1536309</v>
       </c>
       <c r="CC24">
-        <v>1408788</v>
+        <v>1383895</v>
       </c>
       <c r="CD24">
-        <v>1544117</v>
+        <v>1521563</v>
       </c>
       <c r="CE24">
-        <v>1446446</v>
+        <v>1428074</v>
       </c>
       <c r="CF24">
-        <v>1444813</v>
+        <v>1445001</v>
       </c>
       <c r="CG24">
-        <v>1389913</v>
+        <v>1396251</v>
       </c>
       <c r="CH24">
-        <v>1170606</v>
+        <v>1190378</v>
       </c>
       <c r="CI24">
-        <v>893117</v>
+        <v>905144</v>
       </c>
       <c r="CJ24">
-        <v>573392</v>
+        <v>574840</v>
       </c>
       <c r="CK24">
-        <v>360140</v>
+        <v>359947</v>
       </c>
       <c r="CL24">
-        <v>347328</v>
+        <v>346096</v>
       </c>
       <c r="CM24">
-        <v>1486705</v>
+        <v>1477760</v>
       </c>
       <c r="CN24">
-        <v>1649686</v>
+        <v>1643403</v>
       </c>
       <c r="CO24">
-        <v>1640385</v>
+        <v>1648469</v>
       </c>
       <c r="CP24">
-        <v>1607726</v>
+        <v>1690368</v>
       </c>
       <c r="CQ24">
-        <v>1692496</v>
+        <v>1558565</v>
       </c>
       <c r="CR24">
-        <v>1781682</v>
+        <v>1588425</v>
       </c>
       <c r="CS24">
-        <v>1509795</v>
+        <v>1430017</v>
       </c>
       <c r="CT24">
-        <v>1413999</v>
+        <v>1361267</v>
       </c>
       <c r="CU24">
-        <v>1252548</v>
+        <v>1219473</v>
       </c>
       <c r="CV24">
-        <v>1583646</v>
+        <v>1563810</v>
       </c>
       <c r="CW24">
-        <v>1291173</v>
+        <v>1256619</v>
       </c>
       <c r="CX24">
-        <v>1266145</v>
+        <v>1246086</v>
       </c>
       <c r="CY24">
-        <v>1185126</v>
+        <v>1172926</v>
       </c>
       <c r="CZ24">
-        <v>930563</v>
+        <v>947641</v>
       </c>
       <c r="DA24">
-        <v>650363</v>
+        <v>666777</v>
       </c>
       <c r="DB24">
-        <v>387519</v>
+        <v>389742</v>
       </c>
       <c r="DC24">
-        <v>214066</v>
+        <v>215291</v>
       </c>
       <c r="DD24">
-        <v>158804</v>
+        <v>159891</v>
       </c>
       <c r="DE24">
-        <v>1527043</v>
+        <v>1517312</v>
       </c>
       <c r="DF24">
-        <v>32656</v>
+        <v>35091</v>
       </c>
       <c r="DG24">
-        <v>31921</v>
+        <v>34611</v>
       </c>
       <c r="DH24">
-        <v>29450</v>
+        <v>37656</v>
       </c>
       <c r="DI24">
-        <v>31388</v>
+        <v>35878</v>
       </c>
       <c r="DJ24">
-        <v>34963</v>
+        <v>35546</v>
       </c>
       <c r="DK24">
-        <v>34084</v>
+        <v>33206</v>
       </c>
       <c r="DL24">
-        <v>31150</v>
+        <v>30501</v>
       </c>
       <c r="DM24">
-        <v>26158</v>
+        <v>26289</v>
       </c>
       <c r="DN24">
-        <v>35254</v>
+        <v>35052</v>
       </c>
       <c r="DO24">
-        <v>24525</v>
+        <v>24506</v>
       </c>
       <c r="DP24">
-        <v>23110</v>
+        <v>22805</v>
       </c>
       <c r="DQ24">
-        <v>20482</v>
+        <v>20100</v>
       </c>
       <c r="DR24">
-        <v>16343</v>
+        <v>15752</v>
       </c>
       <c r="DS24">
-        <v>12150</v>
+        <v>11218</v>
       </c>
       <c r="DT24">
-        <v>7784</v>
+        <v>7040</v>
       </c>
       <c r="DU24">
-        <v>4717</v>
+        <v>4214</v>
       </c>
       <c r="DV24">
-        <v>4473</v>
+        <v>4056</v>
       </c>
       <c r="DW24">
-        <v>34811</v>
+        <v>32337</v>
       </c>
       <c r="DX24">
-        <v>33698</v>
+        <v>36648</v>
       </c>
       <c r="DY24">
-        <v>32631</v>
+        <v>36169</v>
       </c>
       <c r="DZ24">
-        <v>29767</v>
+        <v>38275</v>
       </c>
       <c r="EA24">
-        <v>31469</v>
+        <v>36749</v>
       </c>
       <c r="EB24">
-        <v>37391</v>
+        <v>36202</v>
       </c>
       <c r="EC24">
-        <v>37278</v>
+        <v>33522</v>
       </c>
       <c r="ED24">
-        <v>34196</v>
+        <v>30360</v>
       </c>
       <c r="EE24">
-        <v>27644</v>
+        <v>25482</v>
       </c>
       <c r="EF24">
-        <v>36743</v>
+        <v>36853</v>
       </c>
       <c r="EG24">
-        <v>25081</v>
+        <v>23565</v>
       </c>
       <c r="EH24">
-        <v>22728</v>
+        <v>21245</v>
       </c>
       <c r="EI24">
-        <v>20100</v>
+        <v>18471</v>
       </c>
       <c r="EJ24">
-        <v>15101</v>
+        <v>13904</v>
       </c>
       <c r="EK24">
-        <v>10962</v>
+        <v>9639</v>
       </c>
       <c r="EL24">
-        <v>6980</v>
+        <v>5831</v>
       </c>
       <c r="EM24">
-        <v>3730</v>
+        <v>3113</v>
       </c>
       <c r="EN24">
-        <v>3039</v>
+        <v>2325</v>
       </c>
       <c r="EO24">
-        <v>36908</v>
+        <v>34481</v>
       </c>
       <c r="EP24">
-        <v>595819</v>
+        <v>819787</v>
       </c>
       <c r="EQ24">
-        <v>527991</v>
+        <v>765910</v>
       </c>
       <c r="ER24">
-        <v>448315</v>
+        <v>649442</v>
       </c>
       <c r="ES24">
-        <v>395224</v>
+        <v>565135</v>
       </c>
       <c r="ET24">
-        <v>341232</v>
+        <v>532391</v>
       </c>
       <c r="EU24">
-        <v>278592</v>
+        <v>468229</v>
       </c>
       <c r="EV24">
-        <v>247066</v>
+        <v>423104</v>
       </c>
       <c r="EW24">
-        <v>199779</v>
+        <v>358796</v>
       </c>
       <c r="EX24">
-        <v>614573</v>
+        <v>846417</v>
       </c>
       <c r="EY24">
-        <v>178144</v>
+        <v>342638</v>
       </c>
       <c r="EZ24">
-        <v>156183</v>
+        <v>312409</v>
       </c>
       <c r="FA24">
-        <v>144135</v>
+        <v>286290</v>
       </c>
       <c r="FB24">
-        <v>115973</v>
+        <v>225998</v>
       </c>
       <c r="FC24">
-        <v>84749</v>
+        <v>162833</v>
       </c>
       <c r="FD24">
-        <v>58048</v>
+        <v>105543</v>
       </c>
       <c r="FE24">
-        <v>35241</v>
+        <v>60959</v>
       </c>
       <c r="FF24">
-        <v>35371</v>
+        <v>55657</v>
       </c>
       <c r="FG24">
-        <v>604862</v>
+        <v>872640</v>
       </c>
       <c r="FH24">
-        <v>623169</v>
+        <v>848978</v>
       </c>
       <c r="FI24">
-        <v>545358</v>
+        <v>785593</v>
       </c>
       <c r="FJ24">
-        <v>452611</v>
+        <v>643308</v>
       </c>
       <c r="FK24">
-        <v>394207</v>
+        <v>536527</v>
       </c>
       <c r="FL24">
-        <v>323877</v>
+        <v>486279</v>
       </c>
       <c r="FM24">
-        <v>255421</v>
+        <v>420290</v>
       </c>
       <c r="FN24">
-        <v>225128</v>
+        <v>374514</v>
       </c>
       <c r="FO24">
-        <v>180337</v>
+        <v>318330</v>
       </c>
       <c r="FP24">
-        <v>642494</v>
+        <v>880632</v>
       </c>
       <c r="FQ24">
-        <v>162156</v>
+        <v>301468</v>
       </c>
       <c r="FR24">
-        <v>140249</v>
+        <v>267421</v>
       </c>
       <c r="FS24">
-        <v>129596</v>
+        <v>241477</v>
       </c>
       <c r="FT24">
-        <v>102036</v>
+        <v>185614</v>
       </c>
       <c r="FU24">
-        <v>72414</v>
+        <v>128332</v>
       </c>
       <c r="FV24">
-        <v>47000</v>
+        <v>79319</v>
       </c>
       <c r="FW24">
-        <v>26844</v>
+        <v>42620</v>
       </c>
       <c r="FX24">
-        <v>22026</v>
+        <v>32715</v>
       </c>
       <c r="FY24">
-        <v>631015</v>
+        <v>908899</v>
       </c>
       <c r="FZ24">
-        <v>7356992</v>
+        <v>6961511</v>
       </c>
       <c r="GA24">
-        <v>7741953</v>
+        <v>7339574</v>
       </c>
       <c r="GB24">
-        <v>7689210</v>
+        <v>7794721</v>
       </c>
       <c r="GC24">
-        <v>7835078</v>
+        <v>7508775</v>
       </c>
       <c r="GD24">
-        <v>8287217</v>
+        <v>7961631</v>
       </c>
       <c r="GE24">
-        <v>8087644</v>
+        <v>7834491</v>
       </c>
       <c r="GF24">
-        <v>7881505</v>
+        <v>7607728</v>
       </c>
       <c r="GG24">
-        <v>7307866</v>
+        <v>7062433</v>
       </c>
       <c r="GH24">
-        <v>6941953</v>
+        <v>6540261</v>
       </c>
       <c r="GI24">
-        <v>7946345</v>
+        <v>7742469</v>
       </c>
       <c r="GJ24">
-        <v>8295682</v>
+        <v>8166992</v>
       </c>
       <c r="GK24">
-        <v>8659593</v>
+        <v>8628035</v>
       </c>
       <c r="GL24">
-        <v>7917246</v>
+        <v>8003142</v>
       </c>
       <c r="GM24">
-        <v>6666002</v>
+        <v>6793663</v>
       </c>
       <c r="GN24">
-        <v>4965371</v>
+        <v>5107957</v>
       </c>
       <c r="GO24">
-        <v>3141896</v>
+        <v>3273386</v>
       </c>
       <c r="GP24">
-        <v>3258757</v>
+        <v>3429046</v>
       </c>
       <c r="GQ24">
-        <v>6300928</v>
+        <v>5977579</v>
       </c>
       <c r="GR24">
-        <v>7757405</v>
+        <v>7320287</v>
       </c>
       <c r="GS24">
-        <v>8126268</v>
+        <v>7727625</v>
       </c>
       <c r="GT24">
-        <v>7898714</v>
+        <v>7917058</v>
       </c>
       <c r="GU24">
-        <v>8047652</v>
+        <v>7667598</v>
       </c>
       <c r="GV24">
-        <v>8513318</v>
+        <v>8072972</v>
       </c>
       <c r="GW24">
-        <v>8398982</v>
+        <v>7908391</v>
       </c>
       <c r="GX24">
-        <v>8169329</v>
+        <v>7631604</v>
       </c>
       <c r="GY24">
-        <v>7495021</v>
+        <v>7031172</v>
       </c>
       <c r="GZ24">
-        <v>7289474</v>
+        <v>6863028</v>
       </c>
       <c r="HA24">
-        <v>8137461</v>
+        <v>7654921</v>
       </c>
       <c r="HB24">
-        <v>8266232</v>
+        <v>7915006</v>
       </c>
       <c r="HC24">
-        <v>8396779</v>
+        <v>8147485</v>
       </c>
       <c r="HD24">
-        <v>7370679</v>
+        <v>7309092</v>
       </c>
       <c r="HE24">
-        <v>5935492</v>
+        <v>5990160</v>
       </c>
       <c r="HF24">
-        <v>4207648</v>
+        <v>4285358</v>
       </c>
       <c r="HG24">
-        <v>2391096</v>
+        <v>2485058</v>
       </c>
       <c r="HH24">
-        <v>1915046</v>
+        <v>2033273</v>
       </c>
       <c r="HI24">
-        <v>6603258</v>
+        <v>6265788</v>
       </c>
     </row>
     <row r="25" spans="1:217">
@@ -74845,652 +75395,652 @@
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>174385</v>
+        <v>255330</v>
       </c>
       <c r="C25">
-        <v>177219</v>
+        <v>271515</v>
       </c>
       <c r="D25">
-        <v>168189</v>
+        <v>259726</v>
       </c>
       <c r="E25">
-        <v>165712</v>
+        <v>239741</v>
       </c>
       <c r="F25">
-        <v>170509</v>
+        <v>248714</v>
       </c>
       <c r="G25">
-        <v>151907</v>
+        <v>238621</v>
       </c>
       <c r="H25">
-        <v>143323</v>
+        <v>235282</v>
       </c>
       <c r="I25">
-        <v>127263</v>
+        <v>212180</v>
       </c>
       <c r="J25">
-        <v>178714</v>
+        <v>241078</v>
       </c>
       <c r="K25">
-        <v>123858</v>
+        <v>197640</v>
       </c>
       <c r="L25">
-        <v>118027</v>
+        <v>178062</v>
       </c>
       <c r="M25">
-        <v>115681</v>
+        <v>161129</v>
       </c>
       <c r="N25">
-        <v>96052</v>
+        <v>128826</v>
       </c>
       <c r="O25">
-        <v>70696</v>
+        <v>91137</v>
       </c>
       <c r="P25">
-        <v>47568</v>
+        <v>59885</v>
       </c>
       <c r="Q25">
-        <v>28723</v>
+        <v>36223</v>
       </c>
       <c r="R25">
-        <v>27046</v>
+        <v>33643</v>
       </c>
       <c r="S25">
-        <v>175476</v>
+        <v>217714</v>
       </c>
       <c r="T25">
-        <v>181443</v>
+        <v>265817</v>
       </c>
       <c r="U25">
-        <v>187005</v>
+        <v>286298</v>
       </c>
       <c r="V25">
-        <v>176497</v>
+        <v>282404</v>
       </c>
       <c r="W25">
-        <v>170943</v>
+        <v>262951</v>
       </c>
       <c r="X25">
-        <v>182230</v>
+        <v>268044</v>
       </c>
       <c r="Y25">
-        <v>165364</v>
+        <v>253578</v>
       </c>
       <c r="Z25">
-        <v>155546</v>
+        <v>246065</v>
       </c>
       <c r="AA25">
-        <v>134727</v>
+        <v>217538</v>
       </c>
       <c r="AB25">
-        <v>185642</v>
+        <v>249669</v>
       </c>
       <c r="AC25">
-        <v>128153</v>
+        <v>199507</v>
       </c>
       <c r="AD25">
-        <v>118177</v>
+        <v>176924</v>
       </c>
       <c r="AE25">
-        <v>109642</v>
+        <v>153340</v>
       </c>
       <c r="AF25">
-        <v>87044</v>
+        <v>117354</v>
       </c>
       <c r="AG25">
-        <v>61676</v>
+        <v>79115</v>
       </c>
       <c r="AH25">
-        <v>40719</v>
+        <v>49094</v>
       </c>
       <c r="AI25">
-        <v>22607</v>
+        <v>26628</v>
       </c>
       <c r="AJ25">
-        <v>17443</v>
+        <v>20025</v>
       </c>
       <c r="AK25">
-        <v>182538</v>
+        <v>226267</v>
       </c>
       <c r="AL25">
-        <v>602309</v>
+        <v>615827</v>
       </c>
       <c r="AM25">
-        <v>626698</v>
+        <v>649327</v>
       </c>
       <c r="AN25">
-        <v>694742</v>
+        <v>794242</v>
       </c>
       <c r="AO25">
-        <v>812905</v>
+        <v>888314</v>
       </c>
       <c r="AP25">
-        <v>955788</v>
+        <v>968032</v>
       </c>
       <c r="AQ25">
-        <v>958038</v>
+        <v>956217</v>
       </c>
       <c r="AR25">
-        <v>904456</v>
+        <v>905500</v>
       </c>
       <c r="AS25">
-        <v>820057</v>
+        <v>824610</v>
       </c>
       <c r="AT25">
-        <v>627740</v>
+        <v>611006</v>
       </c>
       <c r="AU25">
-        <v>777358</v>
+        <v>810302</v>
       </c>
       <c r="AV25">
-        <v>666593</v>
+        <v>694862</v>
       </c>
       <c r="AW25">
-        <v>615587</v>
+        <v>630942</v>
       </c>
       <c r="AX25">
-        <v>554405</v>
+        <v>570698</v>
       </c>
       <c r="AY25">
-        <v>456887</v>
+        <v>459733</v>
       </c>
       <c r="AZ25">
-        <v>314433</v>
+        <v>315288</v>
       </c>
       <c r="BA25">
-        <v>195712</v>
+        <v>194850</v>
       </c>
       <c r="BB25">
-        <v>209591</v>
+        <v>200366</v>
       </c>
       <c r="BC25">
-        <v>557990</v>
+        <v>564948</v>
       </c>
       <c r="BD25">
-        <v>634599</v>
+        <v>647038</v>
       </c>
       <c r="BE25">
-        <v>645485</v>
+        <v>667929</v>
       </c>
       <c r="BF25">
-        <v>702157</v>
+        <v>800648</v>
       </c>
       <c r="BG25">
-        <v>782644</v>
+        <v>869285</v>
       </c>
       <c r="BH25">
-        <v>901825</v>
+        <v>911327</v>
       </c>
       <c r="BI25">
-        <v>896634</v>
+        <v>868843</v>
       </c>
       <c r="BJ25">
-        <v>819087</v>
+        <v>789195</v>
       </c>
       <c r="BK25">
-        <v>727946</v>
+        <v>709767</v>
       </c>
       <c r="BL25">
-        <v>665160</v>
+        <v>641521</v>
       </c>
       <c r="BM25">
-        <v>692713</v>
+        <v>692509</v>
       </c>
       <c r="BN25">
-        <v>582904</v>
+        <v>588458</v>
       </c>
       <c r="BO25">
-        <v>526459</v>
+        <v>525712</v>
       </c>
       <c r="BP25">
-        <v>451846</v>
+        <v>454624</v>
       </c>
       <c r="BQ25">
-        <v>353787</v>
+        <v>352661</v>
       </c>
       <c r="BR25">
-        <v>244496</v>
+        <v>238683</v>
       </c>
       <c r="BS25">
-        <v>149478</v>
+        <v>146237</v>
       </c>
       <c r="BT25">
-        <v>133571</v>
+        <v>124378</v>
       </c>
       <c r="BU25">
-        <v>590095</v>
+        <v>596149</v>
       </c>
       <c r="BV25">
-        <v>1579250</v>
+        <v>1571755</v>
       </c>
       <c r="BW25">
-        <v>1638947</v>
+        <v>1620523</v>
       </c>
       <c r="BX25">
-        <v>1616643</v>
+        <v>1710074</v>
       </c>
       <c r="BY25">
-        <v>1681752</v>
+        <v>1628857</v>
       </c>
       <c r="BZ25">
-        <v>1877189</v>
+        <v>1761922</v>
       </c>
       <c r="CA25">
-        <v>1647409</v>
+        <v>1626023</v>
       </c>
       <c r="CB25">
-        <v>1582410</v>
+        <v>1567260</v>
       </c>
       <c r="CC25">
-        <v>1423334</v>
+        <v>1396645</v>
       </c>
       <c r="CD25">
-        <v>1552676</v>
+        <v>1530738</v>
       </c>
       <c r="CE25">
-        <v>1447130</v>
+        <v>1425602</v>
       </c>
       <c r="CF25">
-        <v>1426787</v>
+        <v>1424162</v>
       </c>
       <c r="CG25">
-        <v>1402809</v>
+        <v>1405882</v>
       </c>
       <c r="CH25">
-        <v>1208154</v>
+        <v>1227145</v>
       </c>
       <c r="CI25">
-        <v>923975</v>
+        <v>939391</v>
       </c>
       <c r="CJ25">
-        <v>611217</v>
+        <v>613535</v>
       </c>
       <c r="CK25">
-        <v>379103</v>
+        <v>380216</v>
       </c>
       <c r="CL25">
-        <v>359118</v>
+        <v>358269</v>
       </c>
       <c r="CM25">
-        <v>1485264</v>
+        <v>1476292</v>
       </c>
       <c r="CN25">
-        <v>1632005</v>
+        <v>1623500</v>
       </c>
       <c r="CO25">
-        <v>1681531</v>
+        <v>1677602</v>
       </c>
       <c r="CP25">
-        <v>1613873</v>
+        <v>1700479</v>
       </c>
       <c r="CQ25">
-        <v>1666246</v>
+        <v>1575888</v>
       </c>
       <c r="CR25">
-        <v>1837511</v>
+        <v>1622722</v>
       </c>
       <c r="CS25">
-        <v>1554409</v>
+        <v>1459511</v>
       </c>
       <c r="CT25">
-        <v>1446718</v>
+        <v>1389126</v>
       </c>
       <c r="CU25">
-        <v>1267448</v>
+        <v>1229394</v>
       </c>
       <c r="CV25">
-        <v>1590503</v>
+        <v>1571591</v>
       </c>
       <c r="CW25">
-        <v>1286225</v>
+        <v>1251529</v>
       </c>
       <c r="CX25">
-        <v>1248055</v>
+        <v>1225212</v>
       </c>
       <c r="CY25">
-        <v>1193849</v>
+        <v>1177820</v>
       </c>
       <c r="CZ25">
-        <v>966956</v>
+        <v>979078</v>
       </c>
       <c r="DA25">
-        <v>672753</v>
+        <v>692400</v>
       </c>
       <c r="DB25">
-        <v>414671</v>
+        <v>417792</v>
       </c>
       <c r="DC25">
-        <v>226317</v>
+        <v>228557</v>
       </c>
       <c r="DD25">
-        <v>166713</v>
+        <v>167805</v>
       </c>
       <c r="DE25">
-        <v>1527705</v>
+        <v>1517650</v>
       </c>
       <c r="DF25">
-        <v>33285</v>
+        <v>35508</v>
       </c>
       <c r="DG25">
-        <v>33097</v>
+        <v>35344</v>
       </c>
       <c r="DH25">
-        <v>30853</v>
+        <v>37893</v>
       </c>
       <c r="DI25">
-        <v>31475</v>
+        <v>36664</v>
       </c>
       <c r="DJ25">
-        <v>35259</v>
+        <v>36399</v>
       </c>
       <c r="DK25">
-        <v>34563</v>
+        <v>33840</v>
       </c>
       <c r="DL25">
-        <v>32617</v>
+        <v>31659</v>
       </c>
       <c r="DM25">
-        <v>27161</v>
+        <v>27105</v>
       </c>
       <c r="DN25">
-        <v>35931</v>
+        <v>34999</v>
       </c>
       <c r="DO25">
-        <v>24862</v>
+        <v>24907</v>
       </c>
       <c r="DP25">
-        <v>23490</v>
+        <v>23175</v>
       </c>
       <c r="DQ25">
-        <v>21229</v>
+        <v>20960</v>
       </c>
       <c r="DR25">
-        <v>17223</v>
+        <v>16566</v>
       </c>
       <c r="DS25">
-        <v>12779</v>
+        <v>11937</v>
       </c>
       <c r="DT25">
-        <v>8627</v>
+        <v>7758</v>
       </c>
       <c r="DU25">
-        <v>5052</v>
+        <v>4582</v>
       </c>
       <c r="DV25">
-        <v>4855</v>
+        <v>4326</v>
       </c>
       <c r="DW25">
-        <v>35944</v>
+        <v>32969</v>
       </c>
       <c r="DX25">
-        <v>34360</v>
+        <v>37044</v>
       </c>
       <c r="DY25">
-        <v>33909</v>
+        <v>36983</v>
       </c>
       <c r="DZ25">
-        <v>31093</v>
+        <v>38602</v>
       </c>
       <c r="EA25">
-        <v>31596</v>
+        <v>37559</v>
       </c>
       <c r="EB25">
-        <v>37121</v>
+        <v>37207</v>
       </c>
       <c r="EC25">
-        <v>38014</v>
+        <v>34429</v>
       </c>
       <c r="ED25">
-        <v>35657</v>
+        <v>31383</v>
       </c>
       <c r="EE25">
-        <v>28768</v>
+        <v>26257</v>
       </c>
       <c r="EF25">
-        <v>37617</v>
+        <v>37038</v>
       </c>
       <c r="EG25">
-        <v>25742</v>
+        <v>24095</v>
       </c>
       <c r="EH25">
-        <v>23176</v>
+        <v>21699</v>
       </c>
       <c r="EI25">
-        <v>20678</v>
+        <v>19084</v>
       </c>
       <c r="EJ25">
-        <v>15952</v>
+        <v>14694</v>
       </c>
       <c r="EK25">
-        <v>11533</v>
+        <v>10227</v>
       </c>
       <c r="EL25">
-        <v>7638</v>
+        <v>6415</v>
       </c>
       <c r="EM25">
-        <v>4037</v>
+        <v>3366</v>
       </c>
       <c r="EN25">
-        <v>3330</v>
+        <v>2555</v>
       </c>
       <c r="EO25">
-        <v>37999</v>
+        <v>34569</v>
       </c>
       <c r="EP25">
-        <v>599963</v>
+        <v>819807</v>
       </c>
       <c r="EQ25">
-        <v>553948</v>
+        <v>793325</v>
       </c>
       <c r="ER25">
-        <v>464726</v>
+        <v>677167</v>
       </c>
       <c r="ES25">
-        <v>410445</v>
+        <v>580164</v>
       </c>
       <c r="ET25">
-        <v>359938</v>
+        <v>547486</v>
       </c>
       <c r="EU25">
-        <v>289531</v>
+        <v>480834</v>
       </c>
       <c r="EV25">
-        <v>256873</v>
+        <v>436962</v>
       </c>
       <c r="EW25">
-        <v>209132</v>
+        <v>369185</v>
       </c>
       <c r="EX25">
-        <v>619741</v>
+        <v>858669</v>
       </c>
       <c r="EY25">
-        <v>183708</v>
+        <v>349129</v>
       </c>
       <c r="EZ25">
-        <v>157204</v>
+        <v>312893</v>
       </c>
       <c r="FA25">
-        <v>148073</v>
+        <v>294290</v>
       </c>
       <c r="FB25">
-        <v>121359</v>
+        <v>238208</v>
       </c>
       <c r="FC25">
-        <v>89355</v>
+        <v>172440</v>
       </c>
       <c r="FD25">
-        <v>62566</v>
+        <v>115694</v>
       </c>
       <c r="FE25">
-        <v>38430</v>
+        <v>67511</v>
       </c>
       <c r="FF25">
-        <v>38122</v>
+        <v>61672</v>
       </c>
       <c r="FG25">
-        <v>608596</v>
+        <v>880919</v>
       </c>
       <c r="FH25">
-        <v>627983</v>
+        <v>850301</v>
       </c>
       <c r="FI25">
-        <v>574002</v>
+        <v>814835</v>
       </c>
       <c r="FJ25">
-        <v>470442</v>
+        <v>677019</v>
       </c>
       <c r="FK25">
-        <v>411797</v>
+        <v>557050</v>
       </c>
       <c r="FL25">
-        <v>345853</v>
+        <v>503542</v>
       </c>
       <c r="FM25">
-        <v>267530</v>
+        <v>433392</v>
       </c>
       <c r="FN25">
-        <v>235038</v>
+        <v>388289</v>
       </c>
       <c r="FO25">
-        <v>188714</v>
+        <v>327368</v>
       </c>
       <c r="FP25">
-        <v>647686</v>
+        <v>894051</v>
       </c>
       <c r="FQ25">
-        <v>166755</v>
+        <v>307284</v>
       </c>
       <c r="FR25">
-        <v>141174</v>
+        <v>268451</v>
       </c>
       <c r="FS25">
-        <v>132350</v>
+        <v>248375</v>
       </c>
       <c r="FT25">
-        <v>107512</v>
+        <v>196896</v>
       </c>
       <c r="FU25">
-        <v>76322</v>
+        <v>136294</v>
       </c>
       <c r="FV25">
-        <v>51117</v>
+        <v>87361</v>
       </c>
       <c r="FW25">
-        <v>29290</v>
+        <v>47483</v>
       </c>
       <c r="FX25">
-        <v>24490</v>
+        <v>37099</v>
       </c>
       <c r="FY25">
-        <v>633796</v>
+        <v>917159</v>
       </c>
       <c r="FZ25">
-        <v>7231190</v>
+        <v>6852366</v>
       </c>
       <c r="GA25">
-        <v>7806292</v>
+        <v>7385791</v>
       </c>
       <c r="GB25">
-        <v>7761304</v>
+        <v>7802741</v>
       </c>
       <c r="GC25">
-        <v>7825119</v>
+        <v>7572146</v>
       </c>
       <c r="GD25">
-        <v>8330381</v>
+        <v>7979431</v>
       </c>
       <c r="GE25">
-        <v>8128700</v>
+        <v>7879644</v>
       </c>
       <c r="GF25">
-        <v>8017712</v>
+        <v>7742849</v>
       </c>
       <c r="GG25">
-        <v>7363861</v>
+        <v>7109592</v>
       </c>
       <c r="GH25">
-        <v>6898111</v>
+        <v>6509212</v>
       </c>
       <c r="GI25">
-        <v>7848994</v>
+        <v>7633721</v>
       </c>
       <c r="GJ25">
-        <v>8074306</v>
+        <v>7932771</v>
       </c>
       <c r="GK25">
-        <v>8628762</v>
+        <v>8573831</v>
       </c>
       <c r="GL25">
-        <v>8045592</v>
+        <v>8115202</v>
       </c>
       <c r="GM25">
-        <v>6777456</v>
+        <v>6896266</v>
       </c>
       <c r="GN25">
-        <v>5176771</v>
+        <v>5318526</v>
       </c>
       <c r="GO25">
-        <v>3336808</v>
+        <v>3479137</v>
       </c>
       <c r="GP25">
-        <v>3295561</v>
+        <v>3482829</v>
       </c>
       <c r="GQ25">
-        <v>6250439</v>
+        <v>5928911</v>
       </c>
       <c r="GR25">
-        <v>7612889</v>
+        <v>7200572</v>
       </c>
       <c r="GS25">
-        <v>8199992</v>
+        <v>7771087</v>
       </c>
       <c r="GT25">
-        <v>7992784</v>
+        <v>7959586</v>
       </c>
       <c r="GU25">
-        <v>8036804</v>
+        <v>7743176</v>
       </c>
       <c r="GV25">
-        <v>8559725</v>
+        <v>8110615</v>
       </c>
       <c r="GW25">
-        <v>8427717</v>
+        <v>7962491</v>
       </c>
       <c r="GX25">
-        <v>8313744</v>
+        <v>7771696</v>
       </c>
       <c r="GY25">
-        <v>7561581</v>
+        <v>7083961</v>
       </c>
       <c r="GZ25">
-        <v>7244532</v>
+        <v>6830240</v>
       </c>
       <c r="HA25">
-        <v>8023092</v>
+        <v>7536867</v>
       </c>
       <c r="HB25">
-        <v>8072545</v>
+        <v>7696748</v>
       </c>
       <c r="HC25">
-        <v>8370316</v>
+        <v>8098375</v>
       </c>
       <c r="HD25">
-        <v>7509031</v>
+        <v>7411166</v>
       </c>
       <c r="HE25">
-        <v>6028411</v>
+        <v>6068975</v>
       </c>
       <c r="HF25">
-        <v>4400281</v>
+        <v>4474797</v>
       </c>
       <c r="HG25">
-        <v>2559737</v>
+        <v>2659629</v>
       </c>
       <c r="HH25">
-        <v>1974713</v>
+        <v>2101909</v>
       </c>
       <c r="HI25">
-        <v>6546555</v>
+        <v>6212990</v>
       </c>
     </row>
     <row r="26" spans="1:217">
@@ -75498,652 +76048,1305 @@
         <v>2024</v>
       </c>
       <c r="B26">
-        <v>180238</v>
+        <v>258715</v>
       </c>
       <c r="C26">
-        <v>183161</v>
+        <v>278155</v>
       </c>
       <c r="D26">
-        <v>176535</v>
+        <v>273473</v>
       </c>
       <c r="E26">
-        <v>172066</v>
+        <v>251426</v>
       </c>
       <c r="F26">
-        <v>178113</v>
+        <v>256126</v>
       </c>
       <c r="G26">
-        <v>158507</v>
+        <v>246162</v>
       </c>
       <c r="H26">
-        <v>148049</v>
+        <v>240668</v>
       </c>
       <c r="I26">
-        <v>130438</v>
+        <v>218491</v>
       </c>
       <c r="J26">
-        <v>184930</v>
+        <v>243478</v>
       </c>
       <c r="K26">
-        <v>124871</v>
+        <v>200948</v>
       </c>
       <c r="L26">
-        <v>117337</v>
+        <v>180525</v>
       </c>
       <c r="M26">
-        <v>117521</v>
+        <v>165696</v>
       </c>
       <c r="N26">
-        <v>99786</v>
+        <v>135413</v>
       </c>
       <c r="O26">
-        <v>74580</v>
+        <v>97262</v>
       </c>
       <c r="P26">
-        <v>51478</v>
+        <v>64928</v>
       </c>
       <c r="Q26">
-        <v>31032</v>
+        <v>39301</v>
       </c>
       <c r="R26">
-        <v>29447</v>
+        <v>37026</v>
       </c>
       <c r="S26">
-        <v>179439</v>
+        <v>224201</v>
       </c>
       <c r="T26">
-        <v>187460</v>
+        <v>270242</v>
       </c>
       <c r="U26">
-        <v>195209</v>
+        <v>295212</v>
       </c>
       <c r="V26">
-        <v>188188</v>
+        <v>299695</v>
       </c>
       <c r="W26">
-        <v>179288</v>
+        <v>278381</v>
       </c>
       <c r="X26">
-        <v>189086</v>
+        <v>279329</v>
       </c>
       <c r="Y26">
-        <v>173263</v>
+        <v>263326</v>
       </c>
       <c r="Z26">
-        <v>161345</v>
+        <v>253261</v>
       </c>
       <c r="AA26">
-        <v>138813</v>
+        <v>224861</v>
       </c>
       <c r="AB26">
-        <v>192311</v>
+        <v>251922</v>
       </c>
       <c r="AC26">
-        <v>129147</v>
+        <v>203146</v>
       </c>
       <c r="AD26">
-        <v>118129</v>
+        <v>179150</v>
       </c>
       <c r="AE26">
-        <v>111980</v>
+        <v>158686</v>
       </c>
       <c r="AF26">
-        <v>90500</v>
+        <v>123789</v>
       </c>
       <c r="AG26">
-        <v>64867</v>
+        <v>84471</v>
       </c>
       <c r="AH26">
-        <v>44365</v>
+        <v>53951</v>
       </c>
       <c r="AI26">
-        <v>24552</v>
+        <v>29181</v>
       </c>
       <c r="AJ26">
-        <v>19340</v>
+        <v>22382</v>
       </c>
       <c r="AK26">
-        <v>186200</v>
+        <v>233467</v>
       </c>
       <c r="AL26">
-        <v>625056</v>
+        <v>628621</v>
       </c>
       <c r="AM26">
-        <v>640458</v>
+        <v>658727</v>
       </c>
       <c r="AN26">
-        <v>742109</v>
+        <v>812653</v>
       </c>
       <c r="AO26">
-        <v>857959</v>
+        <v>941309</v>
       </c>
       <c r="AP26">
-        <v>989711</v>
+        <v>1002418</v>
       </c>
       <c r="AQ26">
-        <v>1007526</v>
+        <v>999468</v>
       </c>
       <c r="AR26">
-        <v>946343</v>
+        <v>940779</v>
       </c>
       <c r="AS26">
-        <v>845986</v>
+        <v>844002</v>
       </c>
       <c r="AT26">
-        <v>642407</v>
+        <v>623164</v>
       </c>
       <c r="AU26">
-        <v>803073</v>
+        <v>827871</v>
       </c>
       <c r="AV26">
-        <v>690165</v>
+        <v>717155</v>
       </c>
       <c r="AW26">
-        <v>640174</v>
+        <v>656310</v>
       </c>
       <c r="AX26">
-        <v>573758</v>
+        <v>590036</v>
       </c>
       <c r="AY26">
-        <v>478661</v>
+        <v>481823</v>
       </c>
       <c r="AZ26">
-        <v>344997</v>
+        <v>345765</v>
       </c>
       <c r="BA26">
-        <v>210411</v>
+        <v>209104</v>
       </c>
       <c r="BB26">
-        <v>224557</v>
+        <v>215454</v>
       </c>
       <c r="BC26">
-        <v>568385</v>
+        <v>575404</v>
       </c>
       <c r="BD26">
-        <v>659666</v>
+        <v>661564</v>
       </c>
       <c r="BE26">
-        <v>664560</v>
+        <v>682348</v>
       </c>
       <c r="BF26">
-        <v>752359</v>
+        <v>827672</v>
       </c>
       <c r="BG26">
-        <v>817594</v>
+        <v>917559</v>
       </c>
       <c r="BH26">
-        <v>932062</v>
+        <v>949185</v>
       </c>
       <c r="BI26">
-        <v>945423</v>
+        <v>918437</v>
       </c>
       <c r="BJ26">
-        <v>867013</v>
+        <v>834554</v>
       </c>
       <c r="BK26">
-        <v>750010</v>
+        <v>726245</v>
       </c>
       <c r="BL26">
-        <v>678658</v>
+        <v>652438</v>
       </c>
       <c r="BM26">
-        <v>716261</v>
+        <v>709367</v>
       </c>
       <c r="BN26">
-        <v>603392</v>
+        <v>606159</v>
       </c>
       <c r="BO26">
-        <v>548796</v>
+        <v>547833</v>
       </c>
       <c r="BP26">
-        <v>468914</v>
+        <v>470264</v>
       </c>
       <c r="BQ26">
-        <v>371516</v>
+        <v>370701</v>
       </c>
       <c r="BR26">
-        <v>265537</v>
+        <v>259415</v>
       </c>
       <c r="BS26">
-        <v>159546</v>
+        <v>155732</v>
       </c>
       <c r="BT26">
-        <v>145660</v>
+        <v>136173</v>
       </c>
       <c r="BU26">
-        <v>600728</v>
+        <v>608148</v>
       </c>
       <c r="BV26">
-        <v>1579220</v>
+        <v>1563763</v>
       </c>
       <c r="BW26">
-        <v>1663315</v>
+        <v>1641635</v>
       </c>
       <c r="BX26">
-        <v>1629646</v>
+        <v>1701416</v>
       </c>
       <c r="BY26">
-        <v>1673443</v>
+        <v>1657652</v>
       </c>
       <c r="BZ26">
-        <v>1896003</v>
+        <v>1770829</v>
       </c>
       <c r="CA26">
-        <v>1712030</v>
+        <v>1673699</v>
       </c>
       <c r="CB26">
-        <v>1598689</v>
+        <v>1584449</v>
       </c>
       <c r="CC26">
-        <v>1458855</v>
+        <v>1432343</v>
       </c>
       <c r="CD26">
-        <v>1556303</v>
+        <v>1534644</v>
       </c>
       <c r="CE26">
-        <v>1444238</v>
+        <v>1417125</v>
       </c>
       <c r="CF26">
-        <v>1406178</v>
+        <v>1399800</v>
       </c>
       <c r="CG26">
-        <v>1412432</v>
+        <v>1413186</v>
       </c>
       <c r="CH26">
-        <v>1241819</v>
+        <v>1258918</v>
       </c>
       <c r="CI26">
-        <v>960339</v>
+        <v>976813</v>
       </c>
       <c r="CJ26">
-        <v>656428</v>
+        <v>660492</v>
       </c>
       <c r="CK26">
-        <v>397005</v>
+        <v>398810</v>
       </c>
       <c r="CL26">
-        <v>372179</v>
+        <v>371700</v>
       </c>
       <c r="CM26">
-        <v>1486059</v>
+        <v>1473738</v>
       </c>
       <c r="CN26">
-        <v>1631979</v>
+        <v>1613703</v>
       </c>
       <c r="CO26">
-        <v>1709605</v>
+        <v>1696824</v>
       </c>
       <c r="CP26">
-        <v>1628378</v>
+        <v>1702428</v>
       </c>
       <c r="CQ26">
-        <v>1654728</v>
+        <v>1614432</v>
       </c>
       <c r="CR26">
-        <v>1866531</v>
+        <v>1643525</v>
       </c>
       <c r="CS26">
-        <v>1627265</v>
+        <v>1509220</v>
       </c>
       <c r="CT26">
-        <v>1469688</v>
+        <v>1405261</v>
       </c>
       <c r="CU26">
-        <v>1302523</v>
+        <v>1260575</v>
       </c>
       <c r="CV26">
-        <v>1591074</v>
+        <v>1572306</v>
       </c>
       <c r="CW26">
-        <v>1277824</v>
+        <v>1241216</v>
       </c>
       <c r="CX26">
-        <v>1228670</v>
+        <v>1203491</v>
       </c>
       <c r="CY26">
-        <v>1200756</v>
+        <v>1182313</v>
       </c>
       <c r="CZ26">
-        <v>999336</v>
+        <v>1004888</v>
       </c>
       <c r="DA26">
-        <v>701142</v>
+        <v>721395</v>
       </c>
       <c r="DB26">
-        <v>445087</v>
+        <v>450505</v>
       </c>
       <c r="DC26">
-        <v>238240</v>
+        <v>240907</v>
       </c>
       <c r="DD26">
-        <v>175594</v>
+        <v>176828</v>
       </c>
       <c r="DE26">
-        <v>1531318</v>
+        <v>1517249</v>
       </c>
       <c r="DF26">
-        <v>34090</v>
+        <v>35884</v>
       </c>
       <c r="DG26">
-        <v>34241</v>
+        <v>36101</v>
       </c>
       <c r="DH26">
-        <v>32602</v>
+        <v>37945</v>
       </c>
       <c r="DI26">
-        <v>31798</v>
+        <v>37835</v>
       </c>
       <c r="DJ26">
-        <v>35561</v>
+        <v>37101</v>
       </c>
       <c r="DK26">
-        <v>35396</v>
+        <v>34712</v>
       </c>
       <c r="DL26">
-        <v>33665</v>
+        <v>32675</v>
       </c>
       <c r="DM26">
-        <v>28484</v>
+        <v>28126</v>
       </c>
       <c r="DN26">
-        <v>36525</v>
+        <v>35018</v>
       </c>
       <c r="DO26">
-        <v>25245</v>
+        <v>25299</v>
       </c>
       <c r="DP26">
-        <v>23917</v>
+        <v>23613</v>
       </c>
       <c r="DQ26">
-        <v>22077</v>
+        <v>21650</v>
       </c>
       <c r="DR26">
-        <v>17963</v>
+        <v>17314</v>
       </c>
       <c r="DS26">
-        <v>13475</v>
+        <v>12738</v>
       </c>
       <c r="DT26">
-        <v>9549</v>
+        <v>8489</v>
       </c>
       <c r="DU26">
-        <v>5437</v>
+        <v>4971</v>
       </c>
       <c r="DV26">
-        <v>5293</v>
+        <v>4687</v>
       </c>
       <c r="DW26">
-        <v>37108</v>
+        <v>33437</v>
       </c>
       <c r="DX26">
-        <v>35327</v>
+        <v>37323</v>
       </c>
       <c r="DY26">
-        <v>34893</v>
+        <v>37512</v>
       </c>
       <c r="DZ26">
-        <v>32718</v>
+        <v>38846</v>
       </c>
       <c r="EA26">
-        <v>32195</v>
+        <v>38808</v>
       </c>
       <c r="EB26">
-        <v>36704</v>
+        <v>37924</v>
       </c>
       <c r="EC26">
-        <v>39016</v>
+        <v>35516</v>
       </c>
       <c r="ED26">
-        <v>36879</v>
+        <v>32372</v>
       </c>
       <c r="EE26">
-        <v>30216</v>
+        <v>27609</v>
       </c>
       <c r="EF26">
-        <v>38587</v>
+        <v>37048</v>
       </c>
       <c r="EG26">
-        <v>26314</v>
+        <v>24512</v>
       </c>
       <c r="EH26">
-        <v>23617</v>
+        <v>22105</v>
       </c>
       <c r="EI26">
-        <v>21270</v>
+        <v>19598</v>
       </c>
       <c r="EJ26">
-        <v>16942</v>
+        <v>15537</v>
       </c>
       <c r="EK26">
-        <v>11991</v>
+        <v>10833</v>
       </c>
       <c r="EL26">
-        <v>8367</v>
+        <v>7083</v>
       </c>
       <c r="EM26">
-        <v>4453</v>
+        <v>3707</v>
       </c>
       <c r="EN26">
-        <v>3645</v>
+        <v>2771</v>
       </c>
       <c r="EO26">
-        <v>39060</v>
+        <v>34670</v>
       </c>
       <c r="EP26">
-        <v>607609</v>
+        <v>826488</v>
       </c>
       <c r="EQ26">
-        <v>574696</v>
+        <v>813351</v>
       </c>
       <c r="ER26">
-        <v>484180</v>
+        <v>706035</v>
       </c>
       <c r="ES26">
-        <v>426558</v>
+        <v>600003</v>
       </c>
       <c r="ET26">
-        <v>379577</v>
+        <v>562554</v>
       </c>
       <c r="EU26">
-        <v>304836</v>
+        <v>498094</v>
       </c>
       <c r="EV26">
-        <v>265438</v>
+        <v>448217</v>
       </c>
       <c r="EW26">
-        <v>220111</v>
+        <v>383087</v>
       </c>
       <c r="EX26">
-        <v>622267</v>
+        <v>870856</v>
       </c>
       <c r="EY26">
-        <v>188643</v>
+        <v>352500</v>
       </c>
       <c r="EZ26">
-        <v>159870</v>
+        <v>316164</v>
       </c>
       <c r="FA26">
-        <v>151690</v>
+        <v>301795</v>
       </c>
       <c r="FB26">
-        <v>126497</v>
+        <v>250220</v>
       </c>
       <c r="FC26">
-        <v>94583</v>
+        <v>182907</v>
       </c>
       <c r="FD26">
-        <v>67337</v>
+        <v>126617</v>
       </c>
       <c r="FE26">
-        <v>41553</v>
+        <v>73955</v>
       </c>
       <c r="FF26">
-        <v>41287</v>
+        <v>68427</v>
       </c>
       <c r="FG26">
-        <v>612870</v>
+        <v>885431</v>
       </c>
       <c r="FH26">
-        <v>636175</v>
+        <v>857955</v>
       </c>
       <c r="FI26">
-        <v>597261</v>
+        <v>837002</v>
       </c>
       <c r="FJ26">
-        <v>491328</v>
+        <v>711473</v>
       </c>
       <c r="FK26">
-        <v>430509</v>
+        <v>583500</v>
       </c>
       <c r="FL26">
-        <v>369446</v>
+        <v>522243</v>
       </c>
       <c r="FM26">
-        <v>284352</v>
+        <v>451962</v>
       </c>
       <c r="FN26">
-        <v>243767</v>
+        <v>399983</v>
       </c>
       <c r="FO26">
-        <v>199331</v>
+        <v>339536</v>
       </c>
       <c r="FP26">
-        <v>649828</v>
+        <v>906295</v>
       </c>
       <c r="FQ26">
-        <v>169917</v>
+        <v>309862</v>
       </c>
       <c r="FR26">
-        <v>143934</v>
+        <v>272061</v>
       </c>
       <c r="FS26">
-        <v>134989</v>
+        <v>255048</v>
       </c>
       <c r="FT26">
-        <v>112529</v>
+        <v>207797</v>
       </c>
       <c r="FU26">
-        <v>80876</v>
+        <v>144902</v>
       </c>
       <c r="FV26">
-        <v>55546</v>
+        <v>96133</v>
       </c>
       <c r="FW26">
-        <v>31787</v>
+        <v>52429</v>
       </c>
       <c r="FX26">
-        <v>27108</v>
+        <v>41774</v>
       </c>
       <c r="FY26">
-        <v>637199</v>
+        <v>923410</v>
       </c>
       <c r="FZ26">
-        <v>7173793</v>
+        <v>6798625</v>
       </c>
       <c r="GA26">
-        <v>7805446</v>
+        <v>7382613</v>
       </c>
       <c r="GB26">
-        <v>7850038</v>
+        <v>7783780</v>
       </c>
       <c r="GC26">
-        <v>7861138</v>
+        <v>7726819</v>
       </c>
       <c r="GD26">
-        <v>8355022</v>
+        <v>7986169</v>
       </c>
       <c r="GE26">
-        <v>8227071</v>
+        <v>7977477</v>
       </c>
       <c r="GF26">
-        <v>8111908</v>
+        <v>7838249</v>
       </c>
       <c r="GG26">
-        <v>7476517</v>
+        <v>7219782</v>
       </c>
       <c r="GH26">
-        <v>6835598</v>
+        <v>6470059</v>
       </c>
       <c r="GI26">
-        <v>7706146</v>
+        <v>7471879</v>
       </c>
       <c r="GJ26">
-        <v>7910029</v>
+        <v>7755434</v>
       </c>
       <c r="GK26">
-        <v>8594795</v>
+        <v>8519313</v>
       </c>
       <c r="GL26">
-        <v>8132063</v>
+        <v>8181847</v>
       </c>
       <c r="GM26">
-        <v>6931769</v>
+        <v>7040814</v>
       </c>
       <c r="GN26">
-        <v>5427669</v>
+        <v>5569866</v>
       </c>
       <c r="GO26">
-        <v>3479986</v>
+        <v>3628543</v>
       </c>
       <c r="GP26">
-        <v>3348367</v>
+        <v>3553038</v>
       </c>
       <c r="GQ26">
-        <v>6214410</v>
+        <v>5896171</v>
       </c>
       <c r="GR26">
-        <v>7550541</v>
+        <v>7139389</v>
       </c>
       <c r="GS26">
-        <v>8204566</v>
+        <v>7763395</v>
       </c>
       <c r="GT26">
-        <v>8103136</v>
+        <v>7983813</v>
       </c>
       <c r="GU26">
-        <v>8073972</v>
+        <v>7905154</v>
       </c>
       <c r="GV26">
-        <v>8590078</v>
+        <v>8139777</v>
       </c>
       <c r="GW26">
-        <v>8518338</v>
+        <v>8075311</v>
       </c>
       <c r="GX26">
-        <v>8414236</v>
+        <v>7877160</v>
       </c>
       <c r="GY26">
-        <v>7685888</v>
+        <v>7198440</v>
       </c>
       <c r="GZ26">
-        <v>7169184</v>
+        <v>6781387</v>
       </c>
       <c r="HA26">
-        <v>7864860</v>
+        <v>7374854</v>
       </c>
       <c r="HB26">
-        <v>7932179</v>
+        <v>7534883</v>
       </c>
       <c r="HC26">
-        <v>8344891</v>
+        <v>8048526</v>
       </c>
       <c r="HD26">
-        <v>7609364</v>
+        <v>7476258</v>
       </c>
       <c r="HE26">
-        <v>6171692</v>
+        <v>6192166</v>
       </c>
       <c r="HF26">
-        <v>4616966</v>
+        <v>4688689</v>
       </c>
       <c r="HG26">
-        <v>2682485</v>
+        <v>2785965</v>
       </c>
       <c r="HH26">
-        <v>2042666</v>
+        <v>2178677</v>
       </c>
       <c r="HI26">
-        <v>6506538</v>
+        <v>6179409</v>
+      </c>
+    </row>
+    <row r="27" spans="1:217">
+      <c r="A27">
+        <v>2025</v>
+      </c>
+      <c r="B27">
+        <v>259482</v>
+      </c>
+      <c r="C27">
+        <v>277997</v>
+      </c>
+      <c r="D27">
+        <v>279580</v>
+      </c>
+      <c r="E27">
+        <v>260018</v>
+      </c>
+      <c r="F27">
+        <v>256807</v>
+      </c>
+      <c r="G27">
+        <v>250392</v>
+      </c>
+      <c r="H27">
+        <v>241904</v>
+      </c>
+      <c r="I27">
+        <v>223658</v>
+      </c>
+      <c r="J27">
+        <v>240093</v>
+      </c>
+      <c r="K27">
+        <v>202926</v>
+      </c>
+      <c r="L27">
+        <v>183231</v>
+      </c>
+      <c r="M27">
+        <v>168376</v>
+      </c>
+      <c r="N27">
+        <v>141150</v>
+      </c>
+      <c r="O27">
+        <v>103784</v>
+      </c>
+      <c r="P27">
+        <v>70292</v>
+      </c>
+      <c r="Q27">
+        <v>42222</v>
+      </c>
+      <c r="R27">
+        <v>40653</v>
+      </c>
+      <c r="S27">
+        <v>227247</v>
+      </c>
+      <c r="T27">
+        <v>269999</v>
+      </c>
+      <c r="U27">
+        <v>295077</v>
+      </c>
+      <c r="V27">
+        <v>305647</v>
+      </c>
+      <c r="W27">
+        <v>287348</v>
+      </c>
+      <c r="X27">
+        <v>281708</v>
+      </c>
+      <c r="Y27">
+        <v>269179</v>
+      </c>
+      <c r="Z27">
+        <v>254893</v>
+      </c>
+      <c r="AA27">
+        <v>231348</v>
+      </c>
+      <c r="AB27">
+        <v>249346</v>
+      </c>
+      <c r="AC27">
+        <v>204332</v>
+      </c>
+      <c r="AD27">
+        <v>181806</v>
+      </c>
+      <c r="AE27">
+        <v>161997</v>
+      </c>
+      <c r="AF27">
+        <v>129406</v>
+      </c>
+      <c r="AG27">
+        <v>90554</v>
+      </c>
+      <c r="AH27">
+        <v>59118</v>
+      </c>
+      <c r="AI27">
+        <v>31482</v>
+      </c>
+      <c r="AJ27">
+        <v>25116</v>
+      </c>
+      <c r="AK27">
+        <v>236394</v>
+      </c>
+      <c r="AL27">
+        <v>638609</v>
+      </c>
+      <c r="AM27">
+        <v>657882</v>
+      </c>
+      <c r="AN27">
+        <v>795401</v>
+      </c>
+      <c r="AO27">
+        <v>972448</v>
+      </c>
+      <c r="AP27">
+        <v>1017435</v>
+      </c>
+      <c r="AQ27">
+        <v>1029868</v>
+      </c>
+      <c r="AR27">
+        <v>967054</v>
+      </c>
+      <c r="AS27">
+        <v>863545</v>
+      </c>
+      <c r="AT27">
+        <v>628495</v>
+      </c>
+      <c r="AU27">
+        <v>837710</v>
+      </c>
+      <c r="AV27">
+        <v>744457</v>
+      </c>
+      <c r="AW27">
+        <v>669637</v>
+      </c>
+      <c r="AX27">
+        <v>604439</v>
+      </c>
+      <c r="AY27">
+        <v>502263</v>
+      </c>
+      <c r="AZ27">
+        <v>377116</v>
+      </c>
+      <c r="BA27">
+        <v>223757</v>
+      </c>
+      <c r="BB27">
+        <v>232568</v>
+      </c>
+      <c r="BC27">
+        <v>573139</v>
+      </c>
+      <c r="BD27">
+        <v>673027</v>
+      </c>
+      <c r="BE27">
+        <v>684473</v>
+      </c>
+      <c r="BF27">
+        <v>812289</v>
+      </c>
+      <c r="BG27">
+        <v>953187</v>
+      </c>
+      <c r="BH27">
+        <v>962387</v>
+      </c>
+      <c r="BI27">
+        <v>954261</v>
+      </c>
+      <c r="BJ27">
+        <v>868018</v>
+      </c>
+      <c r="BK27">
+        <v>744376</v>
+      </c>
+      <c r="BL27">
+        <v>656312</v>
+      </c>
+      <c r="BM27">
+        <v>719295</v>
+      </c>
+      <c r="BN27">
+        <v>629077</v>
+      </c>
+      <c r="BO27">
+        <v>560167</v>
+      </c>
+      <c r="BP27">
+        <v>483517</v>
+      </c>
+      <c r="BQ27">
+        <v>387248</v>
+      </c>
+      <c r="BR27">
+        <v>281568</v>
+      </c>
+      <c r="BS27">
+        <v>165141</v>
+      </c>
+      <c r="BT27">
+        <v>149092</v>
+      </c>
+      <c r="BU27">
+        <v>606507</v>
+      </c>
+      <c r="BV27">
+        <v>1560023</v>
+      </c>
+      <c r="BW27">
+        <v>1648858</v>
+      </c>
+      <c r="BX27">
+        <v>1665851</v>
+      </c>
+      <c r="BY27">
+        <v>1703243</v>
+      </c>
+      <c r="BZ27">
+        <v>1748301</v>
+      </c>
+      <c r="CA27">
+        <v>1719916</v>
+      </c>
+      <c r="CB27">
+        <v>1591127</v>
+      </c>
+      <c r="CC27">
+        <v>1474164</v>
+      </c>
+      <c r="CD27">
+        <v>1527704</v>
+      </c>
+      <c r="CE27">
+        <v>1399699</v>
+      </c>
+      <c r="CF27">
+        <v>1388890</v>
+      </c>
+      <c r="CG27">
+        <v>1412894</v>
+      </c>
+      <c r="CH27">
+        <v>1284793</v>
+      </c>
+      <c r="CI27">
+        <v>1013064</v>
+      </c>
+      <c r="CJ27">
+        <v>710846</v>
+      </c>
+      <c r="CK27">
+        <v>417311</v>
+      </c>
+      <c r="CL27">
+        <v>388868</v>
+      </c>
+      <c r="CM27">
+        <v>1467491</v>
+      </c>
+      <c r="CN27">
+        <v>1607863</v>
+      </c>
+      <c r="CO27">
+        <v>1701404</v>
+      </c>
+      <c r="CP27">
+        <v>1678166</v>
+      </c>
+      <c r="CQ27">
+        <v>1665504</v>
+      </c>
+      <c r="CR27">
+        <v>1636625</v>
+      </c>
+      <c r="CS27">
+        <v>1556677</v>
+      </c>
+      <c r="CT27">
+        <v>1414112</v>
+      </c>
+      <c r="CU27">
+        <v>1297378</v>
+      </c>
+      <c r="CV27">
+        <v>1563396</v>
+      </c>
+      <c r="CW27">
+        <v>1222445</v>
+      </c>
+      <c r="CX27">
+        <v>1195500</v>
+      </c>
+      <c r="CY27">
+        <v>1179602</v>
+      </c>
+      <c r="CZ27">
+        <v>1025180</v>
+      </c>
+      <c r="DA27">
+        <v>752664</v>
+      </c>
+      <c r="DB27">
+        <v>485882</v>
+      </c>
+      <c r="DC27">
+        <v>253403</v>
+      </c>
+      <c r="DD27">
+        <v>187251</v>
+      </c>
+      <c r="DE27">
+        <v>1512486</v>
+      </c>
+      <c r="DF27">
+        <v>36070</v>
+      </c>
+      <c r="DG27">
+        <v>36545</v>
+      </c>
+      <c r="DH27">
+        <v>37526</v>
+      </c>
+      <c r="DI27">
+        <v>39107</v>
+      </c>
+      <c r="DJ27">
+        <v>37158</v>
+      </c>
+      <c r="DK27">
+        <v>35690</v>
+      </c>
+      <c r="DL27">
+        <v>33132</v>
+      </c>
+      <c r="DM27">
+        <v>29596</v>
+      </c>
+      <c r="DN27">
+        <v>34596</v>
+      </c>
+      <c r="DO27">
+        <v>25527</v>
+      </c>
+      <c r="DP27">
+        <v>23904</v>
+      </c>
+      <c r="DQ27">
+        <v>22269</v>
+      </c>
+      <c r="DR27">
+        <v>18135</v>
+      </c>
+      <c r="DS27">
+        <v>13682</v>
+      </c>
+      <c r="DT27">
+        <v>9174</v>
+      </c>
+      <c r="DU27">
+        <v>5381</v>
+      </c>
+      <c r="DV27">
+        <v>5099</v>
+      </c>
+      <c r="DW27">
+        <v>33945</v>
+      </c>
+      <c r="DX27">
+        <v>37460</v>
+      </c>
+      <c r="DY27">
+        <v>37661</v>
+      </c>
+      <c r="DZ27">
+        <v>38605</v>
+      </c>
+      <c r="EA27">
+        <v>39965</v>
+      </c>
+      <c r="EB27">
+        <v>38251</v>
+      </c>
+      <c r="EC27">
+        <v>36459</v>
+      </c>
+      <c r="ED27">
+        <v>33004</v>
+      </c>
+      <c r="EE27">
+        <v>29037</v>
+      </c>
+      <c r="EF27">
+        <v>36753</v>
+      </c>
+      <c r="EG27">
+        <v>24840</v>
+      </c>
+      <c r="EH27">
+        <v>22579</v>
+      </c>
+      <c r="EI27">
+        <v>20174</v>
+      </c>
+      <c r="EJ27">
+        <v>16275</v>
+      </c>
+      <c r="EK27">
+        <v>11580</v>
+      </c>
+      <c r="EL27">
+        <v>7715</v>
+      </c>
+      <c r="EM27">
+        <v>4041</v>
+      </c>
+      <c r="EN27">
+        <v>3061</v>
+      </c>
+      <c r="EO27">
+        <v>34899</v>
+      </c>
+      <c r="EP27">
+        <v>834655</v>
+      </c>
+      <c r="EQ27">
+        <v>827475</v>
+      </c>
+      <c r="ER27">
+        <v>728631</v>
+      </c>
+      <c r="ES27">
+        <v>621427</v>
+      </c>
+      <c r="ET27">
+        <v>569399</v>
+      </c>
+      <c r="EU27">
+        <v>515672</v>
+      </c>
+      <c r="EV27">
+        <v>456453</v>
+      </c>
+      <c r="EW27">
+        <v>398733</v>
+      </c>
+      <c r="EX27">
+        <v>878427</v>
+      </c>
+      <c r="EY27">
+        <v>353151</v>
+      </c>
+      <c r="EZ27">
+        <v>323113</v>
+      </c>
+      <c r="FA27">
+        <v>306236</v>
+      </c>
+      <c r="FB27">
+        <v>261432</v>
+      </c>
+      <c r="FC27">
+        <v>194577</v>
+      </c>
+      <c r="FD27">
+        <v>138125</v>
+      </c>
+      <c r="FE27">
+        <v>80040</v>
+      </c>
+      <c r="FF27">
+        <v>75954</v>
+      </c>
+      <c r="FG27">
+        <v>885092</v>
+      </c>
+      <c r="FH27">
+        <v>866869</v>
+      </c>
+      <c r="FI27">
+        <v>851353</v>
+      </c>
+      <c r="FJ27">
+        <v>740325</v>
+      </c>
+      <c r="FK27">
+        <v>608556</v>
+      </c>
+      <c r="FL27">
+        <v>534706</v>
+      </c>
+      <c r="FM27">
+        <v>468856</v>
+      </c>
+      <c r="FN27">
+        <v>409017</v>
+      </c>
+      <c r="FO27">
+        <v>353028</v>
+      </c>
+      <c r="FP27">
+        <v>914195</v>
+      </c>
+      <c r="FQ27">
+        <v>310536</v>
+      </c>
+      <c r="FR27">
+        <v>279112</v>
+      </c>
+      <c r="FS27">
+        <v>258712</v>
+      </c>
+      <c r="FT27">
+        <v>217285</v>
+      </c>
+      <c r="FU27">
+        <v>155125</v>
+      </c>
+      <c r="FV27">
+        <v>105341</v>
+      </c>
+      <c r="FW27">
+        <v>57512</v>
+      </c>
+      <c r="FX27">
+        <v>47127</v>
+      </c>
+      <c r="FY27">
+        <v>924534</v>
+      </c>
+      <c r="FZ27">
+        <v>6751993</v>
+      </c>
+      <c r="GA27">
+        <v>7327381</v>
+      </c>
+      <c r="GB27">
+        <v>7657457</v>
+      </c>
+      <c r="GC27">
+        <v>7883906</v>
+      </c>
+      <c r="GD27">
+        <v>7900311</v>
+      </c>
+      <c r="GE27">
+        <v>8048058</v>
+      </c>
+      <c r="GF27">
+        <v>7880818</v>
+      </c>
+      <c r="GG27">
+        <v>7349297</v>
+      </c>
+      <c r="GH27">
+        <v>6376887</v>
+      </c>
+      <c r="GI27">
+        <v>7283359</v>
+      </c>
+      <c r="GJ27">
+        <v>7671649</v>
+      </c>
+      <c r="GK27">
+        <v>8388786</v>
+      </c>
+      <c r="GL27">
+        <v>8222525</v>
+      </c>
+      <c r="GM27">
+        <v>7205304</v>
+      </c>
+      <c r="GN27">
+        <v>5818059</v>
+      </c>
+      <c r="GO27">
+        <v>3751791</v>
+      </c>
+      <c r="GP27">
+        <v>3631143</v>
+      </c>
+      <c r="GQ27">
+        <v>5854961</v>
+      </c>
+      <c r="GR27">
+        <v>7084055</v>
+      </c>
+      <c r="GS27">
+        <v>7690043</v>
+      </c>
+      <c r="GT27">
+        <v>7890502</v>
+      </c>
+      <c r="GU27">
+        <v>8056424</v>
+      </c>
+      <c r="GV27">
+        <v>8063986</v>
+      </c>
+      <c r="GW27">
+        <v>8149205</v>
+      </c>
+      <c r="GX27">
+        <v>7926955</v>
+      </c>
+      <c r="GY27">
+        <v>7335201</v>
+      </c>
+      <c r="GZ27">
+        <v>6681517</v>
+      </c>
+      <c r="HA27">
+        <v>7185099</v>
+      </c>
+      <c r="HB27">
+        <v>7467077</v>
+      </c>
+      <c r="HC27">
+        <v>7927536</v>
+      </c>
+      <c r="HD27">
+        <v>7517322</v>
+      </c>
+      <c r="HE27">
+        <v>6336847</v>
+      </c>
+      <c r="HF27">
+        <v>4896355</v>
+      </c>
+      <c r="HG27">
+        <v>2896229</v>
+      </c>
+      <c r="HH27">
+        <v>2255104</v>
+      </c>
+      <c r="HI27">
+        <v>6135172</v>
       </c>
     </row>
   </sheetData>
